--- a/validation/v3_validation_coding.xlsx
+++ b/validation/v3_validation_coding.xlsx
@@ -793,22 +793,18 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
+          <t>2022-05-28</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>16893</v>
+        <v>7637</v>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>💛 Особисте від редакції. Найдорожчі наші читачі, вас щодня більшає, а нас це дуже тішить. Давайте знайомитись 👋
-Times of Ukraine – це найважливіші, актуальні, цікаві та деколи кумедні новини України та світу. Якісно, швидко, перевірено. Ми – ЗМІ, створене професійними незалежними журналістами. 
-__Нам набридли фейки, треш, дописи російською в українських пабліках. Хочемо підняти якість новин в телеграмі на новий рівень. Та додати краплю інтелектуального гумору і корисностей.
-__Наша команда щодня (а іноді й ночами) працює для вас. Ми набираємо обертів. 😉
-Тож, надсилайте новини, спілкуйтесь у чаті [https://t.me/+P45BvBhjmTw3NGFi] (там весело, цікаво і гаряче), ставтесь з розумінням до реклами (вона дає нам можливість розвиватися), критикуйте та рекомендуйте. 
-Дякуємо за довіру. Будемо дружити 🍀
-• Чат [https://t.me/+P45BvBhjmTw3NGFi] • Головний канал [https://t.me/+bQKdtczFEn40YTE6] • Для рекламодавців [https://t.me/tu_reklama] • Відправити новину [https://t.me/TUnewsBot]</t>
+          <t>**❗️Сталі відомі подробиці чому Порошенко не зміг покинути Україну. Видання "Країна" з посиланням на джерела повідомляє, вчора, близько десятої вечора Порошенко в оточенні ще п'яти осіб, у тому числі охорони пробував перейти кордон на прикордонному переході Рава-Руська.
+Він надав копію розпорядження спікера Ради від 24 травня про відрядження для участі у парламентській асамблеї НАТО. Проте, прикордонники так і не змогли встановити справжність наданих документів, тому що не зчитувався Qr-код. Дві години Порошенко та делегацію протримали на кордоні, після чого вони самостійно поїхали у зворотному напрямку.
+****__Info Україна 🇺🇦__** [https://t.me/+SRWsVjpx0-dhYzMy]</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -908,16 +904,16 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>28958</v>
+        <v>52576</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -926,7 +922,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>**👀Я готовий дозволити путіну застосувати ядерну зброю, яку він розмістив у Білорусі,** – Лукашенко. [https://www.bbc.com/news/articles/c62938gl6q1o]</t>
+          <t>❗️Протягом 60 днів **очікується великий наступ рф**: його мета — повністю (!) окупувати Запорізьку, [https://t.me/+Ncfqxet00rE2MjM6] Херсонську, [https://t.me/+pIwrVDyugeU4MDAy] Донецьку й Луганську області. **Про це сам путін повідомив Трампу**, — Axios.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1028,11 +1024,11 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>5270</v>
+        <v>5650</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
@@ -1041,10 +1037,9 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>**Правительство хочет перевести крымскотатарский язык на латиницу**
-Кабмин утвердил алфавит крымскотатарского языка на основе латиницы. Об этом сообщается на сайте правительства.
-Переведение крымскотатарской письменности на латиницу будет осуществляться до 1 сентября 2025 года. Это значит, что до 2025 образовательный процесс должен быть переведен на использование латиницы, но ее применение для крымскотатарского языка в других сферах жизни будет стимулироваться уже сейчас. 
-По словам главы Минреинтеграции Алексея Резникова, это создаст дополнительные возможности для Украины по взаимодействию с тюркскими странами, среди которых наши стратегические партнеры.</t>
+          <t>**Полиция купила фальшивые Covid-сертификаты на имя больного Шустера**
+Первый замминистра внутренних дел Евгений Енин заявил, что полиция купила фальшивые Covid-сертификаты на имя известного журналиста Савика Шустера, чтобы разоблачить мошенников.
+Об этом Енин рассказал в эфире программы "Свобода слова Савика Шустера", сообщает сайт МВД [https://mvs.gov.ua/press-center/news/policiya-zamovila-falsivii-covid-sertifikat-na-imya-savika-sustera-shhob-vikriti-saxrayiv-jevgenii-jenin?fbclid=IwAR1vlNwLk7J1teEm51gTh8FMkMra5diu49LGfMZkJRTGn0Oo44fqWbEk1PQ]</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr"/>
@@ -1065,25 +1060,50 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>vanek_nikolaev</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>34792</v>
+        <v>39408</v>
       </c>
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>**❗️З 1 квітня 2025 року пропонують підвищити прожитковий мінімум, пенсію та «мінімалку»**, — законопроєкт [https://novyny.live/ekonomi/v-ukrayini-zaproponuvali-pidvishchiti-minimalnu-zarplatu-shcho-vidomo-232842.html]
-Згідно з документом, «мінімалку» можуть переглянути тричі:
-▪️з 1 квітня виплати зростуть — до 9 100 грн (55 грн за годину);
-▪️з 1 липня виплати зростуть ще на 1 000 грн — до 10 100 грн (61 грн за годину) ;
-▪️після фінального підвищення 1 жовтня, мінімальна зарплата в Україні становитиме — 11 184 грн (68 грн за годину).</t>
+          <t>в 15:30 будет 4ый сбор в этом году
+сбор будет на оборудование для дронщиков из 225 ОШП [https://t.me/OSHP_225]
+причем сразу будем помогать и FPVшникам, и операторам Вампиров
+всё необходимое оборудование бригада собрала в один запрос и попросила вас им помочь, учитывая что несколько позиций дронщиков просто уже не существует вместе со всем оборудованием, а воюют они под Гуляйполем
+обстановку под Гуляйполем сейчас думаю не нужно расписывать 
+текст и список оборудования от бригады:
+__Шановна спільнота телеграм каналу «Николаевский Ванёк»
+До вас звертаються пілоти 225 ОШП, яким ви неодноразово допомагали. Зараз ми воюємо на Гуляйпільському напрямку, і нам терміново потрібно закупити обладнання для двох розрахунків важких бомберів та FPV-дронів вартістю 2,5 млн гривень. Це суттєво посилить наші можливості у захисті нашої піхоти та в контратакуючих діях.
+Наша вдячність — це більше тисячі трупів окупантів щомісяця, якими наш полк встеляє поле бою.
+Список обладнання:
+Зарядна станція Bluetti AC180P - 4 шт.
+Starlink MINI - 4 шт.
+Wi-Fi Router - 4 шт.
+Генератор інверторний - 4 шт.
+Антена Avenger Booster - 4 шт.
+Планшети - 4 шт.
+Генератор інверторний - 5 шт.
+Мачта - 2 шт.
+Акумулятор VAMPIRE - 20 шт.
+Пропелери - 48 шт.
+Ноутбук - 1 шт.
+Пульт керування RadioMaster - 2 шт.
+FPV-окуляри - 2 шт.
+Передавачі - 4 шт.
+Ретранслятор на дрон-носій - 2 шт.
+DJI Matrice 30T - 2 шт.
+Комплект бліндажник - 2 шт.
+__Сумма сбора - 2 524 000 грн. 
+в 15:30 отдельным постом как всегда будет ссылка на банку и картку
+убедительная просьба особенно жителей Запорожской области отреагировать на сбор и помочь бойцам, которые сейчас там у вас и работают</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -1147,11 +1167,11 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>34249</v>
+        <v>28296</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1160,12 +1180,8 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>**❗️Виключення України з переговорного процесу США і рф – небезпечно для всіх,** – Зеленський. [https://apnews.com/article/russia-ukraine-war-trump-talks-ceasefire-00af5f61f1faf41e78a3b4e072c21a14]
-▫️рф не хоче брати участь у переговорах про припинення вогню чи обговорювати будь-які поступки, коли її війська мають перевагу на полі бою;
-▫️Трамп міг би змусити  путіна сісти за стіл переговорів, погрожуючи санкціями на енергетичний і банківський сектори, а також продовженням підтримки української армії;
-▫️Київ контактував з адміністрацією Трампа, але ці обговорення відбуваються на «загальному рівні»;
-▫️Після розмови з Трампом треба переходити до якогось формату розмови з росіянами. За столом переговорів мають бути США, Україна, росіяни та ЄС;
-▫️Інші пропозиції щодо гарантій безпеки мають бути підкріплені достатньою кількістю зброї з боку США та Європи та підтримкою Києва у розвитку власної оборонної промисловості.</t>
+          <t>**Ситуація на полі бою створює** **серйозну** **можливість покласти кінець** **війні у 2025 році,** — Зеленський [https://www.reuters.com/world/europe/zelenskiy-says-battlefield-situation-creates-opportunity-bring-an-end-war-2025-2024-10-09/]
+У жовтні, листопаді та грудні у нас є шанс закінчити це та зрушити справу до миру і стабільності.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
@@ -1228,23 +1244,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>2023-08-12</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>57911</v>
+        <v>78685</v>
       </c>
       <c r="E20" s="3" t="inlineStr"/>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>**З початку війни ЗСУ збили більше 3500 повітряних цілей, — Ігнат
-**Серед них: 
-📍1200 крилатих, 
-📍24 балістичні ракети 
-📍13 гіперзвукових «Кинджалів»
-📍більше 20 «Іскандерів» та С-400.
-На сьогодні українська система протиповітряної оборони є однією із найунікальніших в світі – змішана, оскільки в нас зосереджені засоби ППО від різних виробників, різного типу та від різних постачальників. Також і досі є радянські зразки, котрі теж збивають ворожі ракети.
-Стосовно статистики збиття крилатих ракет, то, за словами речника Повітряних сил ЗСУ, нині ППО збиває 70-80% ракет. Аналогічна ситуація по дронах.</t>
+          <t>**Кому довірили годувати українських військових — аферист та жулік Володський заборгував всьому світу — ****ЗМІ** [https://politeka.net/kompromat/433379-semya-aferistov-volodskih-kotoroy-doverili-kormit-ukrainskih-voennyh-zadolzhala-kuchu-deneg]
+На відео — той самий Владислав Володський, який на сьогодні є одним з основних постачальників продуктів до військових частин. Він на колінах просить пощади у невідомого кредитора, якому заборгував 500 тисяч. Важко повірити, але саме цьому бізнесмену з Запоріжжя довірили контракти на суми у мільярди гривень.  Деякі джерела вказують на вплив батька Владислава – Олексій Володський ще до анексії Крима очолював в Джанкої великий завод, з часів керівництва зберіг зв’язки з впливовими людьми.
+Вже в квітні ТОВ «Твій хліб», яке пов’язують з батьком Владислава Володського, виграє торги та стає єдиним постачальником до військових частин від Чернігова до Ужгорода. Тоді, навесні Володський повністю провалив контракти – протягом трьох тижнів близько п’ятдесяти відсотків військових частин в Україні не забезпечувалися замовленими  продуктами. Володському виставили штрафи, розірвали договір. Але саму справу зам’яли, проблему вирішили за рахунок державних резервів Міноборони. З липня стартує дія нового договору на постачання провіанту в армію. І Володський далі продовжує працювати в цій системі.
+Численні скандали навколо Володського та його неспроможність виконувати контракти досі не вплинули на рішення тих, хто відповідає за те, як годують військових. Сумнівні грошові оборудки Владислава Володського – вже давно не секрет та неодноразово висвітлювалися у ЗМІ. Зокрема, борги перед партнерами, суми там фігурують астрономічні. А Володський і далі продовжує брати продукти в борг. За попередніми даними, лише банкам він заборгував близько ста мільйонів гривень. Ще близько мільйона доларів – його борги в готівці. Та це не заважає ділку вести шикарний спосіб життя — пишіть ЗМІ. [https://politeka.net/kompromat/433379-semya-aferistov-volodskih-kotoroy-doverili-kormit-ukrainskih-voennyh-zadolzhala-kuchu-deneg]</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr"/>
@@ -1540,24 +1552,23 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>34755</v>
+        <v>19911</v>
       </c>
       <c r="E28" s="3" t="inlineStr"/>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>**Дениса Комарницького не викликали до правоохоронних органів та не оголошували в розшук, — **адвокат [https://ukranews.com/ua/news/1063741-denysa-komarnytskogo-ne-vyklykaly-do-pravoohoronnyh-organiv-ta-ne-ogoloshuvaly-v-rozshuk-advokat]**
-**Адвокат Тетяна Гончарюк повідомила, що її клієнта, Дениса Комарницького, станом на 10 лютого 2025 року не викликали до НАБУ чи САП, а також він не значився у розшуку, що підтверджують дані МВС.
-За її словами, вона неодноразово зверталася до правоохоронних органів, запитуючи про можливі процесуальні дії щодо Комарницького, і офіційно повідомила НАБУ та САП про відсутність викликів чи вручення документів. Однак 10 лютого 2025 року після 17:00 вона отримала відповідь на месенджер та електронну пошту, в якій зазначалося, що її клієнту направлено повідомлення та виклик до НАБУ.
-При цьому, за словами Гончарюк, ще до цього керівництво НАБУ під час пресконференції публічно оголосило Комарницького в розшук, хоча на той момент жодних викликів чи процесуальних документів йому не вручали. Адвокат вважає, що такі дії свідчать про порушення норм кримінального процесу та упередженість з боку детективів НАБУ.</t>
+          <t>З 1 вересня у школах з’явиться **новий вид дистанційки — змішана**, — прем’єр-міністр Денис Шмигаль. 
+Учні, які перебувають за межами країни, **будуть вивчати «український компонент»** по 6-8 годин на тиждень і отримуватимуть оцінки, а решту предметів їм зарахують автоматично з закордонного табеля. 
+Водночас **63% українців не підтримують дистанційне навчання в школах**, —** **опитування Фонду «Демократичні ініціативи» ім. Ілька Кучеріва. Соціологи вияснили, що негативне ставлення до онлайн-навчання не пов’язане з тим, чи є у школі повноцінне укриття.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr"/>
@@ -2179,11 +2190,11 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>2023-11-09</t>
+          <t>2022-04-03</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>63523</v>
+        <v>25056</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2192,9 +2203,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>**Найближчим часом ще будуть гарні новини з Криму — представник ГУР Юсов**💪
-«Наразі триває підготовка до цілої низки операцій, схожих на події в Керчі [https://t.me/UaOnlii/63218]. Носіїв "калібрів" у Чорноморського флоту РФ ще достатньо. Ми не єдиним "Аскольдом" маємо тішитися», - повідомив Юсов.
-Також він розповів, що ГУР використовує різну мотивацію спілкування з ворогом - ідейну й меркантильну в тому числі.</t>
+          <t>**США не соглашаются представить гарантии безопасности, о которых просит Украина **— заявил президент Владимир Зеленский в эфире американского телеканала CBS.</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
@@ -2370,16 +2379,17 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>27352</v>
+        <v>59170</v>
       </c>
       <c r="E49" s="3" t="inlineStr"/>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Доброго ранку, українці! Пʼятниця — це гарна нагода підбити підсумки тижня. Зокрема, і фінансового. Вдало зароблені гроші краще перевести у валюту в обміннику IFS, [https://t.me/ifs02020] де діє кращий курс.</t>
+          <t>❗️**Зараз світло може зникнути в будь-який момент**, у жодному разі не спускайтеся в ліфтах: **по Україні почалися екстрені відключення** — зокрема, на Полтавщині, [https://t.me/times_poltava] Харківщині [https://t.me/kharkov_times] та Сумщині. [https://t.me/times_sumy] Графіки — не діють. 
+__**Ваша область може стати наступною**, майте на увазі.</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr"/>
@@ -2638,16 +2648,16 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>59316</v>
+        <v>62146</v>
       </c>
       <c r="E56" s="3" t="inlineStr"/>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>⚡ Жах: **момент прильоту ракети просто біля автівки** сьогодні вранці в Києві [https://t.me/kyiv_times_official], — місцеві ЗМІ.</t>
+          <t>⚡️**Світло більше не вимикатимуть сьогодні на Заході**: відключення до кінця доби вже скасовано на Івано-Франківщина [https://t.me/ivano_frankivsk_times] та Львівщина [https://t.me/times_lviv], — місцеві обленерго.</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr"/>
@@ -3114,19 +3124,20 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
+          <t>2022-02-13</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>285</v>
+        <v>1000</v>
       </c>
       <c r="E68" s="3" t="inlineStr"/>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>США одобрили передачу Украине американского оружия странами Балтии – СМИ [https://www.politico.com/news/2022/01/19/us-allies-ukraine-weapons-russia-invasion-527375]
-21 декабря 2021 года министр национальной обороны Литвы Арвидас Анушаускас заявлял, что Литва, Латвия и Эстония при необходимости готовы оказать Киеву "очень быструю военную и невоенную поддержку" в случае эскалации РФ ситуации по отношению к Украине.
-В конце декабря стало известно, что минобороны Эстонии намерено предоставить Украине противотанковое вооружение, ракеты Javelin и 122-миллиметровые гаубицы. Однако перед принятием окончательного решения необходимо получить разрешение от страны происхождения ракет – США, а также от бывших владельцев гаубиц – Финляндии и Германии. Эстония уже начала этот процесс, сообщила телерадиокомпания ERR. 
-Братья прибалты 🤝</t>
+          <t>**Олигархи и бизнесмены покидают Украину чартерными рейсами
+**Украинские олигархи и бизнесмены покидают Украину чартерными рейсами, только в воскресенье из Киева вылетело около 20 чартеров и частных самолетов.
+Среди чартеров и частных самолетов, покинувших Украину в воскресенье – борты Рината Ахметова и Бориса Колесникова.
+Частный борт на 50 человек также заказал депутат ОПЗЖ, миллионер Игорь Абрамович.
+В то же время, по данным УП, хотя один из бортов Ахметова вылетел из Украины в воскресенье, сам олигарх покинул страну 30 января рейсом в Цюрих [https://www.pravda.com.ua/rus/news/2022/02/13/7323857/].</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr"/>
@@ -3734,21 +3745,27 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>59657</v>
+        <v>100703</v>
       </c>
       <c r="E85" s="3" t="inlineStr"/>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>У ніч 15 лютого при спробі перетину кордону затримали колишнього міністра енергетики Германа Галущенка — УП</t>
+          <t>**❗️Зустріч Трампа з путіним — найгірший кошмар України, Київ можуть поставити перед фактом катастрофічної угоди, — The Telegraph **
+📍Замість того, щоб продемонструвати своє бажання приєднатися до Європи у запровадженні набагато жорсткіших санкцій проти Москви, президент США вирішив **винагородити свого російського колегу зустріччю тет-а-тет, якої він так довго домагався.**
+📍В очах путіна переговори віч-на-віч з президентом США — **зустріч, на яку не буде запрошений Володимир Зеленський, — закріпили б за росією статус великої держави. Вона нагадала б саміти наддержав часів холодної війни**, коли Москва і Вашингтон зустрічалися на рівних, щоб обговорити долю планети.
+📍**Це також результат, якого найбільше бояться українські чиновники**. На такій зустрічі путін був би повністю прикутий до Трампа без жодного посередника, який би міг відстоювати їхні інтереси.
+📍Вони побоюються, що вразливий Трамп, чиї інстинкти часто здаються більш прихильними до росії, **погодиться на зведення рахунків, яке потім буде представлене Україні як доконаний факт.**
+📍Путін, без сумніву, в захваті від такого розвитку подій. Це не лише ще одна ознака поблажливості Трампа до нього, але й подальше приниження європейських лідерів, які очікували, що президент США відреагує на його неявку, схваливши жорсткіші санкції.
+📍За відсутності тиску, який би змусив піти на поступки, російська делегація на чолі з Мєдінскім розлютила українців, **висуваючи вимоги, які перетинали всі червоні лінії Києва.**</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr"/>
@@ -3846,23 +3863,22 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>21073</v>
+        <v>82838</v>
       </c>
       <c r="E88" s="3" t="inlineStr"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>**Звичайне побутове загорання**, — радник «очільника» тимчасового окупованого Криму Олег Крючков про пожежу на військовому об’єкті у Сімферополі. 
-Загорілася військова казарма. А перед цим було чути «хлопки», — місцеві пабліки про стовпи чорного диму на півострові. 
-**UPD**: силами ППО збито два БпЛА, — очільник окупаційної адміністрації Криму Сергій Аксьонов.</t>
+          <t>**У Москві посилено заходи безпеки, зокрема через загрози проникнення ДРГ до столиці та області. Посилено охорону в центрі та навколо Кремля, — російські ЗМІ
+**Що за паніка?😁</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr"/>
@@ -4003,21 +4019,20 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>2020-04-05</t>
+          <t>2021-12-12</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>44</v>
+        <v>6108</v>
       </c>
       <c r="E92" s="3" t="inlineStr"/>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>**На въездах в город установили 6 контрольно-пропускных пунктов
-**В Кропивницком из-за коронавируса и усиления карантинного режима установили контрольно-пропускные пункты на въездах в город для проведения температурного скрининга.
-По данным службы, на Знаменском, Криворожском, Бобринецком, Ровенском, Маловисковском и Александровском направлениях было установлено 6 блокпостов.
-На КПП полицейские, спасатели и представители санэпидемслужбы будут проводить температурный скрининг водителей и пассажиров и контролировать соблюдение норм карантина.
-"В случае необходимости - осуществлять санитарную обработку транспорта, направлять людей с признаками ОРВИ на обследование во временные пункты приема и медицинской сортировки больных коронавирусной болезнью и проводить разъяснительную работу относительно правил безопасности во время эпидемии", - отметили в ГСЧС.
-Інфо Україна 🇺🇦 [https://t.me/joinchat/AAAAAFVOFOW98pG_uuttaA]</t>
+          <t>**Папа Римский призвал к "серьезному диалогу" из-за Украины
+**Папа Римский Франциск 12 декабря во время воскресной проповеди призвал к серьезному международному диалогу для решения напряженной ситуации в Украине.
+"__Возношу молитвы за Украину, за все ее церкви и религиозные общины, ее возлюбленный народ и за разрешение напряженности посредством серьезного международного диалога__", — сказал Папа Римский.
+Понтифик также призвал избегать вооруженного конфликта.
+"__Оружие — это не путь. Пусть это Рождество принесет мир в Украину__", — добавил он.</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr"/>
@@ -4304,16 +4319,16 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>22360</v>
+        <v>104293</v>
       </c>
       <c r="E100" s="3" t="inlineStr">
         <is>
@@ -4322,8 +4337,8 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>У судді Верховного суду Валентини Сімоненко, яка в березні подала у відставку, виявили російський паспорт, — розслідування «Схеми». 
-Журналісти стверджують, що книжечку з двухголовим орлом представниця Феміди отримала 10 квітня 2003 року. Станом на зараз документ значиться «недійсним у звʼязку з закінченням терміну його дії». А ще Сімоненко повідомила, що отримує довічне грошове утримання від держави ~200 000 грн/міс.</t>
+          <t>**❗️Трамп пообіцяв Зеленському негайно надіслати 10 ракет-перехоплювачів для Patriot та допомогти у пошуку додаткових каналів постачання, — Axios**
+Також видання пише, що **Трамп не хоче давати свої батареї Patriot, **тому просить Німеччину продати Україні свою одну установку.</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr"/>
@@ -4416,28 +4431,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>vanek_nikolaev</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2023-01-22</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>39347</v>
+        <v>6012</v>
       </c>
       <c r="E103" s="3" t="inlineStr"/>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>сегодня в 16:00 будет сбор, который должен был быть ещё 2 недели назад, но по личным причинам все сборы пришлось перенести на конец месяца
-думаю всё равно до конца месяца 5 сборов сможем добить
-3ий сбор в этом году будет для подразделения НРК NOVA [https://t.me/NOVA_AB3] 3 ОШБр - они на Купянско-Лиманском направлении
-им нужны разные комплектующие для НРК а также разное оборудование для своей мастерской
-обращались они давно, раньше был сбор на 5 млн. грн., сейчас меньше, учитывая что бОльшую часть бойцы собрали своими силами
-Сумма сбора - 2 000 000 грн.
-Отчет обещают в течении марта
-в 16:00 как всегда отдельным постом будет ссылка на банку и картку</t>
+          <t>«Денис Кірєєв – співробітник ГУР, якого вбили в автівці СБУ, а тіло викинули на вулицю». 
+Інтерв'ю з [https://www.radiosvoboda.org/a/%D0%B2%D0%B1%D0%B8%D0%B2%D1%81%D1%82%D0%B2%D0%BE-%D0%BA%D1%96%D1%80%D1%94%D1%94%D0%B2%D0%B0/32233661.html] Кирилом Будановим.</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr"/>
@@ -4571,18 +4580,18 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>2022-03-28</t>
+          <t>2022-03-06</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>24352</v>
+        <v>20992</v>
       </c>
       <c r="E107" s="3" t="inlineStr"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>**Роман Абрамович выступает в роли «миротворца» в войне россии в Украине, — Daily Mail
-**По данным британского таблоида, Абрамович выступая в качестве посредника между Зеленским и Путиным. Он "летал между Стамбулом, Москвой и Киевом" и встретился с членом украинской переговорной группы Умеровым и пресс-серетарем Эрдогана Калыном, который выдвинул идею о том, что Крым и Донбасс должны находиться в долгосрочной аренде у РФ.
-После этого, по данным Daily Mail Абрамович и Умеров транзитом через Польшу прибыли в Киев, где встретились з Зеленским.</t>
+          <t>**6 марта, 14:00, россияне, выходите!
+Распространите
+🇺🇦**Украина Online [https://t.me/UkrainaOnlline] | Прислать новость [http://t.me/anonimnoua]</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr"/>
@@ -4608,17 +4617,26 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>51589</v>
+        <v>40809</v>
       </c>
       <c r="E108" s="3" t="inlineStr"/>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>**Украина уже использует против окупантов ракеты Storm Shadow, — CNN
-**Издание утверждает, что информацию об использовании Украиной ракет Storm Shadow подтвердили два американских чиновника и еще один западный. Когда именно и по каким целям Украина применила Storm Shadow - не уточняется.</t>
+          <t>**Ракетами и дронами в результате утренней атаки повреждено 18 объектов, большинство из которых энергетические, — премьер Шмыгаль
+**Сотни населенных пунктов в семи областях Украины обесточены.
+Экстренные отключения электроэнергии сегодня ввели в: 
+📍Киеве и области, 
+📍Черкасской области, 
+📍Кировоградской области, 
+📍Харьковской области, 
+📍Запорожской области, 
+📍Полтавской области.
+Для более быстрого восстановления сетей, всех украинцев просят экономить электроэнергию. 
+Ранее глава правления "Укренерго" сообщал, что режим экономии электроэнергии может продлиться до конца отопительного сезона.</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr"/>
@@ -5131,22 +5149,16 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>100703</v>
+        <v>112705</v>
       </c>
       <c r="E122" s="3" t="inlineStr"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>**❗️Зустріч Трампа з путіним — найгірший кошмар України, Київ можуть поставити перед фактом катастрофічної угоди, — The Telegraph **
-📍Замість того, щоб продемонструвати своє бажання приєднатися до Європи у запровадженні набагато жорсткіших санкцій проти Москви, президент США вирішив **винагородити свого російського колегу зустріччю тет-а-тет, якої він так довго домагався.**
-📍В очах путіна переговори віч-на-віч з президентом США — **зустріч, на яку не буде запрошений Володимир Зеленський, — закріпили б за росією статус великої держави. Вона нагадала б саміти наддержав часів холодної війни**, коли Москва і Вашингтон зустрічалися на рівних, щоб обговорити долю планети.
-📍**Це також результат, якого найбільше бояться українські чиновники**. На такій зустрічі путін був би повністю прикутий до Трампа без жодного посередника, який би міг відстоювати їхні інтереси.
-📍Вони побоюються, що вразливий Трамп, чиї інстинкти часто здаються більш прихильними до росії, **погодиться на зведення рахунків, яке потім буде представлене Україні як доконаний факт.**
-📍Путін, без сумніву, в захваті від такого розвитку подій. Це не лише ще одна ознака поблажливості Трампа до нього, але й подальше приниження європейських лідерів, які очікували, що президент США відреагує на його неявку, схваливши жорсткіші санкції.
-📍За відсутності тиску, який би змусив піти на поступки, російська делегація на чолі з Мєдінскім розлютила українців, **висуваючи вимоги, які перетинали всі червоні лінії Києва.**</t>
+          <t>**❗️В повітрі вже 3 МіГ-31К — реагуйте на тривогу,— монітори</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr"/>
@@ -5456,21 +5468,22 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>106041</v>
+        <v>1588</v>
       </c>
       <c r="E131" s="3" t="inlineStr"/>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>❗️**Уряд погодив звільнення Сергія Гайдая з Мукачівської РДА, — прем'єрка Свириденко**</t>
+          <t>Пушилин заявил, что в «ДНР» **не ожидали такую высокую явку на референдум 🤡
+Видео: **в Мариупольских дворах так никто и не вышел)</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr"/>
@@ -5859,22 +5872,22 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2024-01-06</t>
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>46172</v>
+        <v>26336</v>
       </c>
       <c r="E142" s="3" t="inlineStr"/>
       <c r="F142" s="3" t="inlineStr">
         <is>
-          <t>**❗️Російські війська, які намагалися просунутися до Добропілля опинилися в оточенні, **— речник ОСУВ «Дніпро»
-Підрозділи ворога, що формували так звані «клешні краба» біля Добропілля, відрізані та заблоковані. Їхнє перебування **там буде недовгим.**</t>
+          <t>⏺Вибухи у Дніпрі! [https://t.me/+qhJ6PFcuaSNhZDIy]
+ПС повідомляють, що біля міста є зграя «шахедів». Перебувайте в укритті.</t>
         </is>
       </c>
       <c r="G142" s="3" t="inlineStr"/>
@@ -6085,22 +6098,19 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>112401</v>
+        <v>74521</v>
       </c>
       <c r="E148" s="3" t="inlineStr"/>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>**Це жахливе відео з дороги у Покровськ, і вона під повним вогневим контролем ворога, кожна одиниця транспорту, що прямує у місто, зазнає атак, — Стерненко **
-📍Неможливо швидко вивозити поранених. Неможливо підвозити своєчасно провізію та БК. Основні втрати — не на позиціях, а на дорозі.
-📍Частково рятують НРК та дрони з вантажами, але ситуація загалом критична.
-📍Зараз ми бачимо те саме, що було в Суджі. **Оперативне оточення з нависанням над останніми логістичними шляхами** та постійне вибивання наших сил у вузькому коридорі. Надмірні втрати людей.
-📍Окремі наші піхотні позиції вже у тилу ворога. Висновків не буде. 
-📍Піхотинці армії РФ, які пробралися в міську забудову Покровська на Донеччині, намагають закріплюватися та облаштовувати спостережні пункти, — офіцер ЗСУ Сергій Цехоцький. 
-📍Ситуація дуже складна, її по-іншому не можна характеризувати. Ворог намагається просочуватися далі, — офіцер ЗСУ Сергій Цехоцький.</t>
+          <t>**Порошенко пропонує кошти з ЗСУ спрямувати на ремонт стадіонів та парків **— **експерт Валентин Гладких**
+Порошенко подав законопроєкт, яким прагне повернути місцевим депутатам частку податку на доходи фізичних осіб і фактично забрати ці кошти у Збройних Сил України — зазначає експерт.
+"Ці кошти місцеві депутати можуть освоїть за рахунок своїх суб'єктів господарювання, які й будуть займатися ремонтом стадіонів та парків. Це жодним чином не буде сприяти вирішенню суто мілітарних завдань, і тим більше поліпшенню матеріально-технічної бази для українських військовослужбовців. Сьогодні ж ці кошти витрачаються на потреби сил оборони. Втім, Петро Олексійович, звісно, про це не говорить. Натомість він продовжує займатися відвертими спекуляціями і маніпуляціями, що в принципі і не дивно", — політичний експерт.
+Як повідомлялося раніше, обидва сини Порошенка призовного віку виїхали з України за кордон незадовго до війни і так і не повернулися.</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -6121,25 +6131,23 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>2024-10-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>29095</v>
+        <v>37382</v>
       </c>
       <c r="E149" s="3" t="inlineStr"/>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>⚡️**Вибори будуть відразу після закінчення війни. Зеленський хоче, щоб і солдати, і біженці мали змогу голосувати**, — голова ОП Андрій Єрмак [https://www.corriere.it/esteri/24_ottobre_27/yermak-intervista-93e69859-37b9-4b67-9b0d-042e4e5cdxlk.shtml]
-Головні тези з інтервʼю:
-▪️Фактично, ми зараз перебуваємо у стані війни з Північною Кореєю. Північнокорейські солдати будуть перекинуті цими днями на Курський фронт і почнуть боротися проти наших військ.
-▪️Ми не боїмося перемоги Трампа на виборах. Жоден із двох кандидатів не бажає дозволити путіну виграти цю війну і військова підтримка продовжуватиметься.
-▪️Боротьбу важко вести три роки поспіль, тож ось чому ми працюємо над перемовинами.</t>
+          <t>**❗️Мобілізувати можуть і 18-річних**, — Одеський ТЦК з посиланням на чинне законодавство.  
+«Дійсно, чоловіки віком від 18 до 25 років зараховуються до категорії призовників. Проте є випадки, коли й таких осіб можуть мобілізувати».
+Така ймовірність є, якщо чоловік пройшов строкову службу у мирний час; закінчив вуз чи військову кафедру та отримав певну військово-облікову спеціальність.</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr"/>
@@ -6203,21 +6211,19 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2020-05-12</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>646</v>
+        <v>2693</v>
       </c>
       <c r="E151" s="3" t="inlineStr"/>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>#Политика | Інфо Україна 🇺🇦 [https://t.me/joinchat/AAAAAFVOFOW98pG_uuttaA]**
-Замглавы Одесской ОГА уволили за задержку надбавок медикам
-При этом президент ранее пригрозил увольнение именно главам ОГА**
-Заместителя главы Одесской облгосадминистрации Виталия Свичинского уволили за задержку надбавок у 300% медиков, которые работают с COVID-19. Об этом в Facebook сообщил глава Одесской ОГА Максим Куцый.
-По словам Куцого, решение об увольнении Свичинского было принято 4 дня назад.
-Поделиться [https://t.me/share/url?url=https://t.me/joinchat/AAAAAFVOFOW98pG_uuttaA] | Обсудить [https://t.me/joinchat/JthRp1KjDLcgijUS4PjYMg] в чате [https://t.me/joinchat/JthRp1KjDLcgijUS4PjYMg]</t>
+          <t>**🇺🇦**Info Украuна [https://t.me/ua_info_news]
+**В Офисе президента анонсировали визит Макрона в Украину**
+Президент Франции Эмманюэль Макрон может посетить Украину с официальным визитом в первой половине 2021 года. Об этом сообщил замглавы Офиса президента Игорь Жовк
+По словам Жовквы, во время визита Макрона пройдут переговоры на высшем уровне, в ходе которых будут предложены новые экономические проекты и продолжится взаимодействие стран в политической и экономической сферах.</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr"/>
@@ -6429,22 +6435,22 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>60802</v>
+        <v>91519</v>
       </c>
       <c r="E157" s="3" t="inlineStr"/>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>⚡ **Машини перекидаються на бік**: на дорогах Заходу — суцільний лід, — читачі Times of Ukraine. [https://t.me/+5ExU141LNUthYjU6]
-__На відео — **траса **__**__Львів-Луцьк__** [https://t.me/times_lviv]__.__ [https://t.me/times_lviv]</t>
+          <t>**❗️Якщо Укрпошта надішле у Viber** **повідомлення, що вам** **прийшла повістка, і ви її не заберете, то вона вважається врученою**, — адвокат [https://www.rbc.ua/rus/news/spovistili-povistku-cherez-vayber-chi-zakonniy-1734012696.html]
+Він додав, що у адресата є три дні, щоб забрати кореспонденцію. Через цей період часу, навіть у разі, якщо адресат не отримає листа, буде вважатись, що він проінформований належним чином.</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr"/>
@@ -6512,11 +6518,11 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>118734</v>
+        <v>79507</v>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
@@ -6525,18 +6531,7 @@
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>**Якщо бурулька впала на ваше авто та пошкодила його — ви маєте право на відшкодування збитків, — Міністерство юстиції**
-Якщо бурулька з даху будинку пошкодила припаркований автомобіль, слід діяти за таким алгоритмом:
-**📍Викличте поліцію**: Для фіксації факту події та складання документів із зазначенням місця, адреси й обставин.
-**📍Зробіть фото та відео**: Зафіксуйте пошкодження автомобіля та місце події з прив’язкою до будівлі.
-**📍Встановіть свідків**: Запишіть ПІБ і контактні дані осіб, які бачили момент падіння бурульки.
-📍**Перевірте наявність камер спостереження**: З’ясуйте, чи є поблизу камери або відеореєстратори, та за можливості отримайте копії записів.
-**📍Замовте оцінку майнової шкоди**: Зверніться до експерта і збережіть усі підтвердні документи (чеки, квитанції).
-**📍Визначте балансоутримувача будівлі**: За потреби зверніться до органу місцевого самоврядування із запитом щодо власника або балансоутримувача будинку.
-**📍Зверніться до балансоутримувача**: Подайте заяву про відшкодування збитків у добровільному порядку.
-📍Подайте позов до суду.
-Водночас, якщо авто було припарковане в забороненому місці або під попереджувальними знаками, відповідальність може нести власник автомобіля.
-Зберігайте на екстрений випадок 🙏</t>
+          <t>**Станом на сьогодні в Україні нараховується близько 11,1 млн чоловіків від 25 до 60 років, які потенційно підлягають мобілізації. З них заброньовано 565 тисяч, — нардеп ****Наталуха** [https://www.rbc.ua/rus/news/radi-nazvali-kilkist-cholovikiv-vid-25-60-1720091752.html?utm_source=telegram&amp;utm_medium=post]</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr"/>
@@ -6711,18 +6706,18 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>2024-03-20</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>30465</v>
+        <v>52089</v>
       </c>
       <c r="E164" s="3" t="inlineStr"/>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>**⚡️Жива, здорова, купує мʼясо: британець Нельсон Сільва стояв у черзі в магазині біля ****принцеси Кейт** [https://t.me/c/1431180517/30006]** ****Міддлтон, яка від початку року не зʼявлялась на публіці** [https://t.me/c/1431180517/30006], [https://t.me/c/1431180517/30006] — The Sun.
-Чоловік розповідає, що зустріч сталася у Віндзорі, де вона шопилась на фермерському ринку. Народний папарацці навіть встиг зробити відеопруф. Але прискіпливі фани королівської родини вважають, що це двійник, бо дружина принца Уельського не така висока. Також є версія, що кадри взагалі зняті у грудні, адже на фоні видніються різдвяні прикраси.
-Водночас приватна лондонська клініка, де у січні прооперували Кетрін, потрапила у скандал. Один з працівників медзакладу намагався отримати доступ до її особистих даних. Триває розслідування, — Daily Mail.</t>
+          <t>⏺**До 30 дронів ідуть на удар** на Київ. [https://t.me/+5s7ZDCzggiU2NjE6] Усе, що є в небі України — летить на Київщину [https://t.me/+5s7ZDCzggiU2NjE6] **з усіх сторін**, — монітори.
+UPD: **Уже є прильоти**. Зараз загроза для всіх районів: **найбільше заходитиме з Півдня й Сходу**. Наразі легше сказати, де в столиці [https://t.me/+5s7ZDCzggiU2NjE6] немає дронів, **ніж там, де є**, — монітори.
+**Підписатися на Times of Ukraine [https://t.me/+5ExU141LNUthYjU6]</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr"/>
@@ -6858,22 +6853,22 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2024-06-06</t>
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>106241</v>
+        <v>34469</v>
       </c>
       <c r="E168" s="3" t="inlineStr"/>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>**"Путін, ввєді воду": міс "днр" просить дати воду, бо їй нема куди поставити квіти**
-Як це немає води, а на вулицях в калюжах? 😂</t>
+          <t>❗️**4 людини загинули внаслідок зіткнення вантажного потяга із пасажирським, в якому перебували українці**, — «Укрзалізниця».
+Трагедія сталась на станції Пардубице у Чехії із поїздом, який виїхав із Праги в напрямку Чопу. У ньому перебували ~300 пасажирів, відомо про десятки постраждалих.</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr"/>
@@ -7228,24 +7223,22 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>4525</v>
+        <v>32475</v>
       </c>
       <c r="E178" s="3" t="inlineStr"/>
       <c r="F178" s="3" t="inlineStr">
         <is>
-          <t>**Дуже-дуже багато трупів росіян після удару по казармам в Мелітополі.** 
-Думаю відео вже всі бачили. Гарна робота розвідки в першу чергу. Але красиве тут інше:
-**путін**: Очєнь важно било сдєлать сухопутний корідор із Крима
-**ЗСУ**: *заряджає ракети і закриває коридор*</t>
+          <t>**❗️Польща готова допомогти Україні повернути чоловіків призовного віку, **— міністр оборони країни Владислав Косіняк-Камиш.
+«Я думаю, що багато поляків обурюються, коли бачать молодих українських чоловіків у готелях і кафе, і чують, скільки зусиль ми повинні докласти, щоб допомогти Україні».</t>
         </is>
       </c>
       <c r="G178" s="3" t="inlineStr"/>
@@ -7831,17 +7824,17 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023-12-24</t>
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>11950</v>
+        <v>25522</v>
       </c>
       <c r="E194" s="3" t="inlineStr"/>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>Вчора росія вперше атакувала [https://t.me/c/1431180517/11911] нас ракетами з Каспію, ворогу все складніше доставляти зброю ближче до України, – пресслужба Міноборони.
-У рф лишилося ракет лише на два масованих удари, – очільник ГУР Кирило Буданов.</t>
+          <t>**До САУ Caesar інтегрують штучний інтелект і одразу випробують на передовій**, — Defence Express.
+Планують це зробити вже наступного року. За словами заступника міністра оборони Івана Гаврилюка, така інтеграція дозволить скоротити витрати боєприпасів одразу на 30%. Caesar має відносно помірну ціну (до €5,5** **млн), а темпи виробництва розширились до 6 шт/місяць і має збільшитись до 8 шт/місяць.</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr"/>
@@ -8639,17 +8632,18 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>2023-12-26</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>66350</v>
+        <v>48469</v>
       </c>
       <c r="E215" s="3" t="inlineStr"/>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>**У столиці розгортатимуть тимчасові блокпости, встановлюватимуть обмежувальні знаки, інженерні загородження — КМВА
-Повідомляють, що це "навчання з безпеки", вони продовжуватимуться з 25 по 28 грудня.</t>
+          <t>❗️**Против Telegram-каналов, которые раскрывают движение ракет и БПЛА, будут приняты меры, — Юрий Игнат
+**"Вы видите какое количество Telegram-каналов на сегодня создано. Кто их контролирует - это чрезвычайно важный вопрос. Он в конце концов по состоянию на сейчас требует особого контроля... В ближайшее время будут приняты серьезные решения, возможно, будут открыты даже уголовные дела, потому что некоторые Telegram-каналы в режиме реального времени подают информацию о движении БПЛА или ракет", - сообщил представитель командования Воздушных Сил ВСУ.
+Админам каналов "Радары/Ракеты онлайн/ ППО" и т.д. приготовиться...</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr"/>
@@ -8826,11 +8820,11 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>31550</v>
+        <v>27723</v>
       </c>
       <c r="E220" s="3" t="inlineStr">
         <is>
@@ -8839,8 +8833,13 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>**❗️Ворог знову наніс удар КАБами по житловому району ****Харкова,** [https://t.me/times_of/31547]** — **мер міста Ігор Терехов. **
-Попередньо відомо про одного загиблого. Є пошкодження цивільної інфраструктури, загорання автомобіля.</t>
+          <t>💙 Сон вже ходить коло вікон. Але перш ніж лягти спати, перегляньте відеопідсумки дня. Нам є що вам розповісти. 
+• Обстріл Харківщини: [https://t.me/c/1431180517/27675] 4 поранених. 
+• «Ивановец» пішов на дно: на борту катера було ~40 моряків. [https://t.me/c/1431180517/27703] 
+• €50 млрд від ЄС: перший транш допомоги отримаємо за місяць. [https://t.me/c/1431180517/27702] 
+• Дубінський лишається в СІЗО: суд не змінив запобіжний захід. [https://t.me/c/1431180517/27706] 
+• Статки Умєрова: [https://t.me/c/1431180517/27693] міністр оборони у 2023-му заробив 5,5 млн грн. 
+• Рекорд Магучіх: стрибнула на 2,04 м.  [https://t.me/c/1431180517/27699]</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr"/>
@@ -8902,16 +8901,17 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>2022-04-24</t>
+          <t>2022-05-03</t>
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>9802</v>
+        <v>10616</v>
       </c>
       <c r="E222" s="3" t="inlineStr"/>
       <c r="F222" s="3" t="inlineStr">
         <is>
-          <t>Російська влада почала закривати [https://www.epravda.com.ua/news/2022/04/24/686171/] інформацію про основні економічні показники, щоб приховати проблеми, з якими РФ стикається через санкції, пише WSJ</t>
+          <t>Мэр Скадовска Александр Яковлев сообщил, что в городе появилась мобильная связь, пока без интернета. 
+Связь начала оживать и в Херсоне -  Шуменском и Таврийском микрорайонах, а также Степановке, сообщает "Суспільне".</t>
         </is>
       </c>
       <c r="G222" s="3" t="inlineStr"/>
@@ -9010,11 +9010,11 @@
       </c>
       <c r="C225" s="3" t="inlineStr">
         <is>
-          <t>2023-04-03</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>28247</v>
+        <v>50556</v>
       </c>
       <c r="E225" s="3" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="F225" s="3" t="inlineStr">
         <is>
-          <t>**В Одесі було чутно вибух**, — місцеві ЗМІ.</t>
+          <t>12 ударів по чотирьом районам Харкова. На місцях деяких прильотів — пожежі, є поранені, повідомив мер міста.</t>
         </is>
       </c>
       <c r="G225" s="3" t="inlineStr"/>
@@ -9080,16 +9080,16 @@
       </c>
       <c r="B227" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>vanek_nikolaev</t>
         </is>
       </c>
       <c r="C227" s="3" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2022-04-23</t>
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>99327</v>
+        <v>206</v>
       </c>
       <c r="E227" s="3" t="inlineStr">
         <is>
@@ -9098,7 +9098,15 @@
       </c>
       <c r="F227" s="3" t="inlineStr">
         <is>
-          <t>❗️**Україна і Росія разом мають сісти за стіл переговорів, — Трамп**</t>
+          <t>Перехоплення СБУ: для нових обстрілів окупанти пишуть на снарядах «Христос Воскрес!» 
+Окупанти у Великдень планують влаштувати ще більше обстрілів мирного населення та українських захисників. 
+Про це свідчать нові телефонні розмови рашистів, які перехопила СБУ. 
+«Наши пацаны пасхалки хохлам готовят. Танкисты на снарядах пишут «Христос воскрес!» Развлекаемся, как можем…» - розповідає окупант своїй дружині. 
+Хоча коли мова заходить про справи у його підрозділі, який стоїть у Миколаївській області, тон загарбника одразу стає іншим. Із 19 людей у його взводі залишилося лише 7. Інших – убили або втекли.
+«Тут никого не добавляют. Наоборот – все уезжают! Кого нам добавлять? Тут все бегут! У нас из бригады уволилось уже 600 человек… Тут  остались только самые стойкие и алкаши», - резюмує окупант.
+Не ясно, чому він так переживає… Це ж якраз ідеальний контингент для захисту «руZZкого міра». Але наші військові зроблять усе можливе, аби й ці рештки ворожої бригади «розформувалися» якомога швидше. 
+#СБУ
+#stoprussia</t>
         </is>
       </c>
       <c r="G227" s="3" t="inlineStr"/>
@@ -9849,22 +9857,22 @@
       </c>
       <c r="B247" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C247" s="3" t="inlineStr">
         <is>
-          <t>2025-04-19</t>
+          <t>2023-10-09</t>
         </is>
       </c>
       <c r="D247" s="3" t="n">
-        <v>38835</v>
+        <v>22360</v>
       </c>
       <c r="E247" s="3" t="inlineStr"/>
       <c r="F247" s="3" t="inlineStr">
         <is>
-          <t>**Погрози держсекретаря Рубіо щодо виходу США з мирних переговорів здебільшого спрямовані на Україну, **— Axios, [https://www.axios.com/2025/04/18/trump-russia-ukraine-rant-walking-away] посилаючись на євродипломатів
-Перед публічними заявами про відмову від російсько-української дипломатії, президент США Дональд Трамп у приватній розмові висловив розчарування через безрезультатність мирних переговорів.</t>
+          <t>У судді Верховного суду Валентини Сімоненко, яка в березні подала у відставку, виявили російський паспорт, — розслідування «Схеми». 
+Журналісти стверджують, що книжечку з двухголовим орлом представниця Феміди отримала 10 квітня 2003 року. Станом на зараз документ значиться «недійсним у звʼязку з закінченням терміну його дії». А ще Сімоненко повідомила, що отримує довічне грошове утримання від держави ~200 000 грн/міс.</t>
         </is>
       </c>
       <c r="G247" s="3" t="inlineStr"/>
@@ -10275,27 +10283,25 @@
       </c>
       <c r="B258" s="3" t="inlineStr">
         <is>
-          <t>vanek_nikolaev</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C258" s="3" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="D258" s="3" t="n">
-        <v>17241</v>
+        <v>69530</v>
       </c>
       <c r="E258" s="3" t="inlineStr"/>
       <c r="F258" s="3" t="inlineStr">
         <is>
-          <t>https://t.me/mykolaivskaODA/6031
-а автор сей замечательной работы 👉 Бодислав [https://t.me/khersondesigner]
-Бодислав [https://t.me/khersondesigner] - захерачу шедевр, матюкаясь, за пару часов
-__*это реклама работы просто талантливого человека, можете листать дальше__
-__**автор канала не получил за данную рекламу даже пивас, из-за чего весьма огорчен__
-__***вообще рекламой на канале не занимаюсь даже за 85 млн. $, можете даже не писать (даже пиво не рекламирую)
-****после войны рассмотрю любые предложения на рекламу пива с предварительной обязательной дегустацией__</t>
+          <t>**У Львові відкриють перший в Україні центр рекрутингу до армії, — ****РБК** [https://www.rbc.ua/rus/news/lvovi-vidkriyut-pershiy-ukrayini-tsentr-rekrutingu-1707489268.html?utm_source=telegram&amp;utm_medium=post]
+В центрі рекрутери:
+📍надаватимуть консультацію й інформацію щодо вакансій;
+📍допоможуть пройти профорієнтаційний тест;
+📍супроводжуватимуть кандидатів на шляху до призначення на обрану посаду в армії.</t>
         </is>
       </c>
       <c r="G258" s="3" t="inlineStr"/>
@@ -10552,18 +10558,16 @@
       </c>
       <c r="C265" s="3" t="inlineStr">
         <is>
-          <t>2022-11-25</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="D265" s="3" t="n">
-        <v>42188</v>
+        <v>40663</v>
       </c>
       <c r="E265" s="3" t="inlineStr"/>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>**Нет никакого полного блэкаута, — Подоляк 
-В результате российских обстрелов была разорвана энергетическая система. Ее восстановили в течение 24 часов. 
-Украина в любом случае будет проводить ремонты, а не кричать, что "все пропало". Также свою помощь в восстановлении и приобретении дополнительных частей для энергосистемы Украины предложили страны Евросоюза.</t>
+          <t>**Украинцы добровольно снизили потребление электроэнергии на 5-10%, — Андрей Герус</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr"/>
@@ -11873,18 +11877,16 @@
       </c>
       <c r="C300" s="3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>37382</v>
+        <v>56312</v>
       </c>
       <c r="E300" s="3" t="inlineStr"/>
       <c r="F300" s="3" t="inlineStr">
         <is>
-          <t>**❗️Мобілізувати можуть і 18-річних**, — Одеський ТЦК з посиланням на чинне законодавство.  
-«Дійсно, чоловіки віком від 18 до 25 років зараховуються до категорії призовників. Проте є випадки, коли й таких осіб можуть мобілізувати».
-Така ймовірність є, якщо чоловік пройшов строкову службу у мирний час; закінчив вуз чи військову кафедру та отримав певну військово-облікову спеціальність.</t>
+          <t>⚡ Перший сніг **почав йти** на Київщині [https://t.me/+P8JdleZKgWkwYWE6], —** **місцеві ЗМІ.</t>
         </is>
       </c>
       <c r="G300" s="3" t="inlineStr"/>
@@ -11942,23 +11944,22 @@
       </c>
       <c r="B302" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C302" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>101929</v>
+        <v>17893</v>
       </c>
       <c r="E302" s="3" t="inlineStr"/>
       <c r="F302" s="3" t="inlineStr">
         <is>
-          <t>**Російський "Яндекс" на своїх картах замалював військові об'єкти в Москві — таким чином фактично вказав їх точне розташування, — ЗМІ**
-Навіть через розмиття добре видно, де саме у столиці рф розташовані підприємства оборонно-промислового комплексу.
-Хотіли приховати, а вийшло — підсвітили 😏</t>
+          <t>Сумщина. Внаслідок обстрілу окупантами Білопілля **загинули батько та син,** – ОВА. Снаряд прилетів буквально за 3 метри від них, коли ті бігли в укриття.
+**UPD:** загинули старший лейтенант поліції та 4-річний хлопчик.</t>
         </is>
       </c>
       <c r="G302" s="3" t="inlineStr"/>
@@ -12293,20 +12294,16 @@
       </c>
       <c r="C311" s="3" t="inlineStr">
         <is>
-          <t>2022-02-17</t>
+          <t>2022-02-23</t>
         </is>
       </c>
       <c r="D311" s="3" t="n">
-        <v>1146</v>
+        <v>1680</v>
       </c>
       <c r="E311" s="3" t="inlineStr"/>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>**⚡️Верховная Рада вернула себе 100% надбавки к окладу
-**
-«За» – 305 голосов
-Так, оклад депутата составит 24 810 грн, плюс он может получить надбавку в такой же сумме за интенсивность труда, что в сумме составит **49 620 грн без учета других надбавок.
-**И компенсации аренды на жилье [https://ukranews.com/news/826902-kazhdyj-iz-145-deputatov-poluchaet-v-srednem-255-tys-griven-kompensatsii-na-zhile-v-god]</t>
+          <t>А ещё я настоятельно прошу кидать волонтерам для помощи нашей армии [https://t.me/korotkoiyasn/1326]</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr"/>
@@ -12327,22 +12324,24 @@
       </c>
       <c r="B312" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C312" s="3" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="D312" s="3" t="n">
-        <v>33745</v>
+        <v>110589</v>
       </c>
       <c r="E312" s="3" t="inlineStr"/>
       <c r="F312" s="3" t="inlineStr">
         <is>
-          <t>⏺Ціль через Сумщину на південь, — ПС. Курс на Полтавщину!
-⏺18:38 — відбій.</t>
+          <t>**Верховна Рада вже сьогодні може проголосувати за "тютюновий закон" №13628, який посилить корупцію та підвищить ціни на сигарети — ****економіст** [https://www.facebook.com/neskhod/posts/pfbid02rnHVxNpG9zrSqHcrARpbctey42RJbhMBWbEpNhD98kbzJWG3pJGzZsTF1bxXBfJKl]
+Депутати хочуть, щоб тютюнові компанії використовували в сигаретах український тютюн без жодних вимог до його якості та ціни. Економіст Ілля Несходовський вже охрестив законопроект "**економічний нонсенсом**, який призведе до **подорожчання сигарет, зниження якості та підвищення корупції**"
+"Коли держава гарантує комусь частку ринку, в Україні це перетворює на корупційні можливості. Створення "**залізної**" квоти, контроль за якою в руках чиновників— це **ідеальний інструмент для заробляння**", — написав Несходовський.
+Цей законопроект нагадує "**соєві правки**", коли речне регулювання і квоти підривають конкуренцію, **зупиняють економіку** та призводять до **вищих цін для споживачів**. Експерт закликав депутатів "**не наступати на соєві граблі знову**".</t>
         </is>
       </c>
       <c r="G312" s="3" t="inlineStr"/>
@@ -12633,11 +12632,11 @@
       </c>
       <c r="C320" s="3" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="D320" s="3" t="n">
-        <v>43336</v>
+        <v>4903</v>
       </c>
       <c r="E320" s="3" t="inlineStr">
         <is>
@@ -12646,13 +12645,7 @@
       </c>
       <c r="F320" s="3" t="inlineStr">
         <is>
-          <t>**АРМА відмовляється проводити нову оцінку активів IDS Ukraine. 
-⭕️Оцінка активів цієї компанії в 2023 році становила лише 1,4 млрд грн, тоді як поточна вартість **оцінюється в 4,6 млрд грн**. До того ж, чинність попередньої оцінки закінчилася ще у березні 2024 року.
-⭕️Проте **АРМА не погодилася** [https://www.unian.ua/economics/finance/ids-ukraine-publichno-zaklikala-arma-provesti-novu-ocinku-aktiviv-kompaniji-12833841.html]** провести нову оцінку активів IDS Ukraine** (ТМ «Моршинська», ТМ «Миргородська»), пояснюючи це тим, що компанія не оскаржувала попередню оцінку. 
-⭕️Але проблема в тому, що IDS Ukraine **не отримала жодного документу щодо оцінки 2022 року**, попри численні запити, відповідно не має шансу для звернення до суду. Виходить, замкнене коло, яке **створює додаткові ризики для держави**.
-⭕️«Ситуація виглядає вкрай загрозливою та створює умови для потенційного розкрадання. **Тільки на рахунках компанії — 1,2 млрд грн**, не враховуючи вартість устаткування та іншого майна», — коментує Вадим Вичка, директор з юридичних питань IDS Ukraine.
-⭕️Наразі активи перебувають в процесі передачі «правильній» компанії за заниженою вартістю. Це дозволить віртуозно швидко і безкарно витягнути з нею все можливе, **після чого державі повернуть знецінений актив**. 
-IDS Ukraine закликає діяти раціонально: вже триває розгляд у ВАКС, і після завершення процесу мільярди гривень можуть потрапити до державного бюджету. Інша альтернатива — **кошти та активи потраплять  в приватні руки**.</t>
+          <t>Зеленский, Ахметов, Коломойский и другие политики уже давно подписаны на Администрацию Президента, а ты еще нет? [https://t.me/AP_UA]</t>
         </is>
       </c>
       <c r="G320" s="3" t="inlineStr"/>
@@ -12678,16 +12671,26 @@
       </c>
       <c r="C321" s="3" t="inlineStr">
         <is>
-          <t>2022-09-04</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="D321" s="3" t="n">
-        <v>18426</v>
+        <v>1192</v>
       </c>
       <c r="E321" s="3" t="inlineStr"/>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>Підтримайте збір пана Стерненко на 100 коптерів [https://t.me/ssternenko/8232], вже більше половини суми є</t>
+          <t>Это уже говорит о том, что количество провокаций ночью будет в разы больше, чем сегодня.
+Как раз перед тем, как завтра **Россия проведет учения с баллистическими ракетами под **руководством Путина [https://www.rbc.ru/politics/18/02/2022/620f5d9d9a794768d56996bf]
+Сейчас идёт максимальный пик эскалации.
+Вчера мне подписчики показали, что большинство населения России выступило остро против признания "республик" (это можете найти под многими постами русс новостей),
+что стало для меня удивлением, ведь лучше бы с таким успехом хоть на один митинг против войны вышли. 
+Теперь они включают свои фейкометы на максимум, для создания картинки бедных и несчастных орков.
+Уже который день я вижу месседж в ру СМИ, что это Украина готовит нападение и обстреливает, создаёт эскалацию.
+Но пока Китай не эвакуирует своё посольство из Киева, то можете спокойно жить и не думать о полномасштабном наступлении.
+Китайское посольство будет реальным сигналом.
+А пока будут очень горячие деньки на Донбассе.
+#**МоёЕбучееМнение**</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr"/>
@@ -13005,16 +13008,16 @@
       </c>
       <c r="B330" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C330" s="3" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="D330" s="3" t="n">
-        <v>19649</v>
+        <v>14586</v>
       </c>
       <c r="E330" s="3" t="inlineStr">
         <is>
@@ -13023,8 +13026,10 @@
       </c>
       <c r="F330" s="3" t="inlineStr">
         <is>
-          <t>«Найближчим часом «Оленегорского горняка» ми не побачимо», — представник ГУР Андрій Юсов.
-Відновити десантний корабель досить проблематично. Адже ця конструкція робилась не на території рф і **пошкодження там дуже значні**.</t>
+          <t>🎬 **Фільм Любомира Левицького вийде за підтримки FAVBET та буде присвячений воїнам 3-ї ОШБр
+**Режисер Любомир Левицький готує до релізу стрічку «Ми були рекрутами» [https://www.instagram.com/reel/CyihAOztAm1/?utm_source=ig_web_copy_link] про бійців 3-ї окремої штурмової бригади. Жодних бюджетних коштів на стрічку не виділяли — фінансування зйомок взяла на себе українська компанія FAVBET. [https://www.favbet.ua/]
+«Ми були рекрутами» [https://youtu.be/0xn32QtrTNE?si=LyngT0G_OB9qPyxc] — фільм у жанрі мок’юментарі, що поєднує художній вимисел та реальні документальні кадри, зняті військовими 3-ї ОШБр в ході виконання реальних бойових завдань. В центрі сюжету — 19-річний на псевдо позивним «Журналіст», який приймає рішення стати до лав ЗСУ.
+__«Сьогодні мало просто зняти черговий фільм. Натомість важливо розповідати історію, яка болить кожному українцю та несе певну місію. Саме тому я і обрав жанр псевдодокументалістики з реальними фактами, що були доповнені видовищними постановочними сценами та ігровою частиною. Це новий для України жанр, який точно запам’ятають глядачі. Так само  як запам’ятають історію наших героїв»__, — розповідає Любомир Левицький.</t>
         </is>
       </c>
       <c r="G330" s="3" t="inlineStr"/>
@@ -13343,16 +13348,16 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="D339" s="3" t="n">
-        <v>102469</v>
+        <v>54616</v>
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
@@ -13361,9 +13366,10 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>**Держсекретар США Рубіо опублікував вітання з днем росії**
-"Від імені американського народу хочу привітати російський народ. Сполучені Штати**, як і раніше, віддані підтримці російського народу** в його прагненні до світлого майбутнього".
-😐</t>
+          <t>❗️Представлено умови виїзду з України** для хлопців 18-22 років**, — МВС.
+Для** перетину кордону** необхідно мати:
+⭕️паспорт та** військово-обліковий документ** (у тому числі в електронній формі).
+⭕️**Виключення: **норма не поширюється на осіб, які займають визначені посади в органах державної влади, державних органах та органах місцевого самоврядування. Ці особи можуть виїжджати за кордон **лише у службове відрядження.**</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr"/>
@@ -13538,17 +13544,16 @@
       </c>
       <c r="C344" s="3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-09-18</t>
         </is>
       </c>
       <c r="D344" s="3" t="n">
-        <v>53934</v>
+        <v>60299</v>
       </c>
       <c r="E344" s="3" t="inlineStr"/>
       <c r="F344" s="3" t="inlineStr">
         <is>
-          <t>**В Повітряних силах підтвердили **знищення складу боєприпасів [https://t.me/c/1233777422/53930]** окупантів на Херсонщині
-**"Ви бачили палаючі склади боєприпасів. Вже командувач подякував хлопцям за гарну роботу. Менше боєприпасів - більше вогню", — розповів речник командування Повітряних сил України Юрій Ігнат.</t>
+          <t>**США вважають заборону на ввезення зерна з України суверенним рішенням країн Європи — Білий дім</t>
         </is>
       </c>
       <c r="G344" s="3" t="inlineStr"/>
@@ -13611,16 +13616,16 @@
       </c>
       <c r="B346" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C346" s="3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="D346" s="3" t="n">
-        <v>316</v>
+        <v>19670</v>
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
@@ -13629,8 +13634,13 @@
       </c>
       <c r="F346" s="3" t="inlineStr">
         <is>
-          <t>**НБУ попередив про неминучість підвищення комунальних тарифів 🥲
-**Національний банк вказав на необхідність підвищення тарифів на житлово-комунальні послуги через збільшення світових цін на енергоносії [https://www.dsnews.ua/ukr/economics/nbu-poperediv-pro-neminuchist-pidvishchennya-komunalnih-tarifiv-20012022-448879]</t>
+          <t>Повітряна тривога в половині областей України через **три основні загрози**:
+• Стратегічні бомбардувальники ТУ-95М, що мають долетіти до пускових рубежів орієнтовно о 00:45-01:45.
+• Декілька хвилі «шахедів». Загроза атаки на Хмельницьку, Черкаську, Кіровоградську, Полтавську та Вінницьку області. 
+• Запуск «Калібрів» з моря, що направляються на південь країни. Зоркрема, ракетна небезпека на Одещині, — Повітряні сили ЗСУ. 
+**UPD**: загалом злетіло 13 ворожих бортів.  
+На Хмельниччині серія ударів, — ОВА. 
+**00:41 відбій повітрянної тривоги по країні** крім Хмельницької, Запорізької, Луганської області та Криму, — ПС.</t>
         </is>
       </c>
       <c r="G346" s="3" t="inlineStr"/>
@@ -13803,21 +13813,16 @@
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2022-02-03</t>
         </is>
       </c>
       <c r="D351" s="3" t="n">
-        <v>27201</v>
+        <v>744</v>
       </c>
       <c r="E351" s="3" t="inlineStr"/>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>**Разом із monobank, **Олегом Гороховським [https://t.me/OGoMono]** та платформою UNITED24 оголошуємо збір ₴60,000,000 на 300 дронів DJI Mavic 3T для ЗСУ.**
-Серед усіх учасників збору ми розіграємо партію йодованої «АРТЕМСОЛІ» із шахт Соледара тиражем 400 штук в спеціальному пакуванні з ілюстрацією художника Максима Паленко, а **10 пачок будуть підписані Марком Гемілом**, який грав Люка Скайвокера у “Зоряних війнах”.
-Кожні задоначені 5 гривень — це +1 шанс виграти сіль, тобто чим більше донат, тим більше шансів.
-100 першим учасникам, які задонатять від ₴100,000 однією транзакцією, отримають по пачці солі з автографом командувача Сухопутних військ ЗСУ Олександра Сирського.
-**Збір триватиме до 02.03.2023, 22:00.
-**Банка [https://send.monobank.ua/jar/5qHs7hHMWn]</t>
+          <t>⚡️**Розвідка США підтвердила дані щодо планів Росії сфабрикувати привід для **вторгнення [https://www.slovoidilo.ua/2022/02/03/novyna/svit/rozvidka-ssha-pidtverdyla-dani-shhodo-planiv-rosiyi-sfabrykuvaty-pryvid-vtorhnennya]</t>
         </is>
       </c>
       <c r="G351" s="3" t="inlineStr"/>
@@ -13993,24 +13998,24 @@
       </c>
       <c r="B356" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C356" s="3" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-01-14</t>
         </is>
       </c>
       <c r="D356" s="3" t="n">
-        <v>70214</v>
+        <v>26749</v>
       </c>
       <c r="E356" s="3" t="inlineStr"/>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>**За організацію побиття студентів на Майдані оголошено чергову підозру  заступнику секретаря РНБО часів Януковича Сівковичу, — ДБР
-Він був завербований росією ще наприкінці дев’яностих, коли був кадровим офіцером кдб срср та фсб.  
-Як повідомляє ДБР, у ніч з 29 на 30 листопада 2013 року Сівкович особисто контролював з кабінету начальника Київської міліції організований ним розгін та побиття студентів.
-Наразі підозрюваний переховується в рф та є одним з очільників антиукраїнського руху, створеного спецслужбами рф.</t>
+          <t>**Одразу три вулкани на планеті розпочали виверження**, — Reuters.
+• В Ісландії вже впʼяте за 3 роки вибухає вулкан на півострові Рейкʼянес. Звідки саме виходить лава досі не зрозуміло, але вона наближається до житлових будинків.
+• В Індонезії стовп попелу з вулкану Марапі піднявся на 1,3 км угору. Після цього пішов сріблястий дощ. Вже евакуювали ~100 людей. Марапі відомий своєю раптовістю, яку важко передбачити.
+• У Японії виверження триває на острові Суваносе. Місцевих попереджають про можливість викиду великих каменів у повітря в радіусі 2 км. На щастя, поки без постраждалих.</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr"/>
@@ -14146,17 +14151,18 @@
       </c>
       <c r="C360" s="3" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>2023-08-19</t>
         </is>
       </c>
       <c r="D360" s="3" t="n">
-        <v>14516</v>
+        <v>20219</v>
       </c>
       <c r="E360" s="3" t="inlineStr"/>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>«Час на користь Україні». Вже скоро третина української армії матиме озброєння за стандартами НАТО, –The Economist. Зі всієї військової допомоги, обіцяної Пентагоном, 40% надійшло за останніх три місяці. Наразі вся увага прикута до боїв на Бахмутському напрямку, але все може змінити контрнаступ ЗСУ. За даними ЗМІ, це може статися вже у квітні.
-__На відео Бахмут на Донеччині. __</t>
+          <t>**Святкування Дня Державного прапора та Незалежності: на 8 днів перекриють центр столиці**, — КМВА. 
+Автівкам заборонять рух з 23:00 20/08 до 23:30 28/08 на ділянці від Майдану Незалежності до вулиці Богдана Хмельницького.
+У Києві відбудеться кілька десятків різнопланових заходів: від урочистих, державних до місцевих, локальних. У цілях безпеки, великі масові збори не будуть проводитися, — начальник міської військової адміністрації Сергій Попко в коментарі УНН.</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr"/>
@@ -14435,21 +14441,18 @@
       </c>
       <c r="C368" s="3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2024-05-20</t>
         </is>
       </c>
       <c r="D368" s="3" t="n">
-        <v>109568</v>
+        <v>76253</v>
       </c>
       <c r="E368" s="3" t="inlineStr"/>
       <c r="F368" s="3" t="inlineStr">
         <is>
-          <t>**Партію Порошенка трясе: соратники «гетьмана» купаються в розкоші, осередки «Євросолідарності» віддають ОПЗЖистам**
-Структури «Євросолідарності» Порошенка на місцях **очолюють колишні представники забороненої ОПЗЖ**, а депутати продовжують **вести розкішне життя** навіть під час війни. Через це партія опинилась в епіцентрі гучних скандалів на місцевому рівні та переживає **політичну кризу**.  
-Так, обранці Порошенка з Дніпра, яких рік тому спіймали на Мальдівах у прикрасах на мільйони,не просто продовжили грабувати місто, а й в пику усім **закупилися автівками і нерухомістю**, а один з них – лідер Євросолідарності в міськраді Дніпра **Каміль Примаков** – на додачу ще й **купив годинник Patek Philippe за $50 тис**. «Гетьман» ніяк не відреагував на це і тому інша парторганізація в Кременчуці продала осередок депутату від забороненої ОПЗЖ – **Андрію Дрофі**. На це подивилися партійці Порошенка з Хмельниччини і **відпустили ситуацію з затриманням екс-кандидатки від Євросолідарності скандальної Тетяни Крупи**, яку затримали **з 6 млн доларів за схеми з ухиляння від мобілізації.** Сам Порошенко свого часу дав їй звання «Заслужений лікар України». 
-«Втім, чому депутати Порошенка мають не їздити на Мальдіви, якщо сам «гетьман» **літає до синів-ухилянтів у Лондон чи до кумів Свинарчуків на віллу в Іспанію**? Чому ОПЗЖисти не можуть очолювати осередки «ЄС», якщо **на чолі всієї партії стоїть один із батьків-засновників Партії регіонів Петро Порошенко**? Тому Порошенко і не міг нічого сказати своїм «армовіровцям», бо сам живе аналогічно, як усі згадані антигерої. Він для них – приклад для унаслідування»,
- — написав [https://www.facebook.com/share/p/1FrazqtYQs/?mibextid=wwXIfr] політичний [https://www.facebook.com/share/p/1FrazqtYQs/?mibextid=wwXIfr] експерт Валентин Гладких.
-Як повідомлялось [https://www.unian.ua/incidents/ohorona-poroshenka-vlashtuvala-seryozne-dtp-z-perekidannyam-v-odesi-foto-13131018.html], [https://www.unian.ua/incidents/ohorona-poroshenka-vlashtuvala-seryozne-dtp-z-perekidannyam-v-odesi-foto-13131018.html] охорона Порошенка **спричинила серйозну ДТП в Одесі**. Очевидці повідомляють, що начальник охорони Петра одразу **зняв номерні знаки з обох машин**, аби неможливо було ідентифікувати власників та **уникнути відповідальності**.</t>
+          <t>**Усі рішення про західну допомогу з запізненням приблизно на рік, що ускладнює становище ЗСУ, — Зеленський в інтерв'ю Reuters
+Зеленський описав постачання військової техніки Україні, зокрема, систем ППО, подібних до Patriot, як «один великий крок уперед, але до цього  — два кроки назад».
+Президент також заявив, що Україна завдає ударів по енергетичних об'єктах Росії, «бо вона залишає нас без енергії».</t>
         </is>
       </c>
       <c r="G368" s="3" t="inlineStr"/>
@@ -15026,16 +15029,17 @@
       </c>
       <c r="C383" s="3" t="inlineStr">
         <is>
-          <t>2022-03-13</t>
+          <t>2023-05-04</t>
         </is>
       </c>
       <c r="D383" s="3" t="n">
-        <v>22414</v>
+        <v>50774</v>
       </c>
       <c r="E383" s="3" t="inlineStr"/>
       <c r="F383" s="3" t="inlineStr">
         <is>
-          <t>**В **Мариуполь снова не попал гуманитарный груз [https://t.me/UkrainaOnlline/22313]**. Колонна для эвакуации осталась в Бердянске. Это произошло потому, что россияне обстреливали гуманитарный коридор из воздуха. Есть много погибших среди гражданских**, – министерша реинтеграции Верещук.</t>
+          <t>**❗️Взрывы и пожар в Соломенском районе столицы. Вероятно попадание обломков БПЛА, — Кличко
+**"В Соломенском районе спасатели локализуют пожар в 4 этажном здании. Площадь возгорания – 50 м кв",— сообщил мэр Киева.</t>
         </is>
       </c>
       <c r="G383" s="3" t="inlineStr"/>
@@ -15138,18 +15142,16 @@
       </c>
       <c r="C386" s="3" t="inlineStr">
         <is>
-          <t>2022-01-24</t>
+          <t>2022-01-22</t>
         </is>
       </c>
       <c r="D386" s="3" t="n">
-        <v>427</v>
+        <v>373</v>
       </c>
       <c r="E386" s="3" t="inlineStr"/>
       <c r="F386" s="3" t="inlineStr">
         <is>
-          <t>**Великобритания выводит некоторых сотрудников посольства из Киева
-**
-Чиновники заявили, что никаких конкретных угроз британским дипломатам не было, но около половины сотрудников, работающих в Киеве, вернутся в Великобританию. [https://www.bbc.com/news/world-europe-60106416]</t>
+          <t>**⚡️США повідомили Україну про плани евакуювати сім'ї дипломатів наступного тижня – **CNN [https://www.cnn.com/2022/01/21/politics/us-embassy-ukraine-nonessential-personnel/index.html]</t>
         </is>
       </c>
       <c r="G386" s="3" t="inlineStr"/>
@@ -15175,17 +15177,16 @@
       </c>
       <c r="C387" s="3" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D387" s="3" t="n">
-        <v>29851</v>
+        <v>55890</v>
       </c>
       <c r="E387" s="3" t="inlineStr"/>
       <c r="F387" s="3" t="inlineStr">
         <is>
-          <t>**❗️Не всі освітяни отримають надбавку у 1000 грн, **— міністр освіти і науки Лісовий 
-Рішення уряду не розповсюджується на вихователів дитячих садків, викладачів закладів професійної-технічної та коледжів.</t>
+          <t>**Машини масово втрачають колеса на трасі** Київ - Одеса через 30-сантиметрові ями: одна з головних доріг країни —** у критичному стані**, — «Главком».</t>
         </is>
       </c>
       <c r="G387" s="3" t="inlineStr"/>
@@ -15206,23 +15207,22 @@
       </c>
       <c r="B388" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C388" s="3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2025-04-19</t>
         </is>
       </c>
       <c r="D388" s="3" t="n">
-        <v>23564</v>
+        <v>38835</v>
       </c>
       <c r="E388" s="3" t="inlineStr"/>
       <c r="F388" s="3" t="inlineStr">
         <is>
-          <t>Ще новини з освітнього фронту: [https://t.me/Timess_ua/23561] нардепи проголосували за **скасування заочної та вечірньої форми навчання**, — парламентар Ярослав Железняк. 
-З 2024 року набір на бакалавра та магістра буде лише на «стаціонар» та дистанційну форму. 
-**UPD**: ухваленим законом скасовується «заочний» набір лише на молодшого бакалавра, — голова освітнього комітету ВРУ Сергій Бабак.</t>
+          <t>**Погрози держсекретаря Рубіо щодо виходу США з мирних переговорів здебільшого спрямовані на Україну, **— Axios, [https://www.axios.com/2025/04/18/trump-russia-ukraine-rant-walking-away] посилаючись на євродипломатів
+Перед публічними заявами про відмову від російсько-української дипломатії, президент США Дональд Трамп у приватній розмові висловив розчарування через безрезультатність мирних переговорів.</t>
         </is>
       </c>
       <c r="G388" s="3" t="inlineStr"/>
@@ -15729,16 +15729,16 @@
       </c>
       <c r="C401" s="3" t="inlineStr">
         <is>
-          <t>2023-02-13</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="D401" s="3" t="n">
-        <v>13662</v>
+        <v>14608</v>
       </c>
       <c r="E401" s="3" t="inlineStr"/>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>Донеччина. ЗСУ спростували заяви Міноборони рф про захоплення селища Красна Гора під Бахмутом. Там тривають бої, – речник Східного угруповання військ Сергій Череватий.</t>
+          <t>Затримано ексдиректора заводу «Антонов» Сергія Бичкова та начальника служби безпеки підприємства Олексія Нетьосова, – СБУ. На початку 2022 вони не пустили на Гостомельський аеродром Нацгвардію, щоб підготувати оборону. Через це загинули рятувальники ДСНС і була знищена «Мрія», – «УП». Керівникам загрожує 15 років позбавлення волі.</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr"/>
@@ -15993,21 +15993,23 @@
       </c>
       <c r="B408" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C408" s="3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-12-25</t>
         </is>
       </c>
       <c r="D408" s="3" t="n">
-        <v>71071</v>
+        <v>6210</v>
       </c>
       <c r="E408" s="3" t="inlineStr"/>
       <c r="F408" s="3" t="inlineStr">
         <is>
-          <t>**Начальник штабу оборони Франції генерал Тьєррі Буркхард написав половині своїх колег по НАТО, досліджуючи можливість створення коаліції бажаючих взяти на себе виконання певних завдань від України, зокрема укомплектування оборонних систем, навчання сил у країні, початок кібероперацій, та пропонує допомогу в розмінуванні — ****Politico** [https://www.politico.eu/article/macron-the-grand-master-of-grandstanding/]</t>
+          <t>**В МОЗ сообщили, что вскоре «красную зону» покинут 2 последние области **
+Глава Минздрава заявил, что «красную зону» покинут Волынская и Запорожская области. Эти регионы вышли по индикаторам из красного уровня эпидемиологической опасности. 
+При этом следующую Covid-волну в Украине прогнозируют на середину февраля 2022.</t>
         </is>
       </c>
       <c r="G408" s="3" t="inlineStr"/>
@@ -16782,17 +16784,18 @@
       </c>
       <c r="C429" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2022-03-22</t>
         </is>
       </c>
       <c r="D429" s="3" t="n">
-        <v>56405</v>
+        <v>23631</v>
       </c>
       <c r="E429" s="3" t="inlineStr"/>
       <c r="F429" s="3" t="inlineStr">
         <is>
-          <t>**На Кримському мосту оголосили повітряну тривогу, — росЗМі
-**"Внимание, воздушная тревога! Всем покинуть мост!", — звучить на кадрах, знятих очевидцями.</t>
+          <t>**Politico ****назвало** [https://www.politico.eu/article/ukraine-zelenskyy-europe-most-powerful-person-politico28-2022-poll/]** президента Зеленского самым влиятельным человеком Европы** – это выбор читателей издания
+«Важно, что его сообщения (регулярные видео в соцсетях и видеоречи в парламентах многих стран) помогли изменить характер дебатов в европейских столицах, повлекшие такие изменения в правительственной политике, которые были немыслимы всего несколько месяцев назад», - говорится в сообщении издания.
+Гордость Украины!</t>
         </is>
       </c>
       <c r="G429" s="3" t="inlineStr"/>
@@ -17710,11 +17713,11 @@
       </c>
       <c r="C454" s="3" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="D454" s="3" t="n">
-        <v>93427</v>
+        <v>91106</v>
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
@@ -17723,8 +17726,9 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>**Група банкірів на Львівщині привласнювала кошти клієнтів "Ощадбанка**"**, — Поліція та СБУ викрили схему**
-Працівники банку за вказівкою керівника змінювали фінансові номери клієнтів та перевипускали картки,** отримавши доступ до 50 рахунків і завдавши збитків понад 5 млн грн. **Фігурантам загрожує **до 6 років ув'язнення.**</t>
+          <t>**На 20 тисяч зросла середня зарплата українських чиновників від початку цього року, — ****Мінфін** [https://www.rbc.ua/rus/news/serednya-zarplata-chinovnikiv-pochatku-roku-1733476185.html]
+Зазначається, що у жовтні середня зарплата у держорганах становила 57,5 тисяч грн, а на початку 2024-го вона становила 38,6 тисяч грн.
+Виходить, що зарплата чиновників більш ніж втричі перевищує середній рівень по України.</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr"/>
@@ -17865,21 +17869,22 @@
       </c>
       <c r="B458" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C458" s="3" t="inlineStr">
         <is>
-          <t>2022-02-22</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="D458" s="3" t="n">
-        <v>1542</v>
+        <v>33348</v>
       </c>
       <c r="E458" s="3" t="inlineStr"/>
       <c r="F458" s="3" t="inlineStr">
         <is>
-          <t>Напоминаю, что прямо сейчас лучшее, что вы можете сделать, это не паниковать, а поддержать наших военных [https://t.me/korotkoiyasn/1326]</t>
+          <t>**Завершення війни у 2025 році означатиме, що Україна програла, тому нам краще воювати і у наступні роки, аж до повного програшу росії, — ****Дикий.** [https://www.unian.ua/war/viyna-maye-pereyti-u-2026-rik-dikiy-zrobiv-nespodiniy-prognoz-12885237.html]**
+Сподіваюсь Дикий покаже приклад?</t>
         </is>
       </c>
       <c r="G458" s="3" t="inlineStr"/>
@@ -18092,18 +18097,18 @@
       </c>
       <c r="C463" s="3" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="D463" s="3" t="n">
-        <v>970</v>
+        <v>301</v>
       </c>
       <c r="E463" s="3" t="inlineStr"/>
       <c r="F463" s="3" t="inlineStr">
         <is>
-          <t>**"Welcome to hell!" ВСУ обещают дать отпор агрессору Стингерами, Джавелинами и NLAW
-**Министр обороны Украины Алексей Резников и главнокомандующий ВСУ Валерий Залужный на фоне российской угрозы заверили украинцев, что Вооруженные силы дадут достойный отпор оккупантам, если они отважатся на наступление [https://www.pravda.com.ua/rus/news/2022/02/12/7323765/].
-**повторения 2014 года не будет, агрессору не взять ни Киев, ни Одессу, ни Харьков, ни любой другой город. Не сомневайтесь — ВСУ полностью готовы дать отпор** и не отдадут украинские земли!".</t>
+          <t>Федеральная служба безопасности убедила главу российского ЦБ Эльвиру Набиуллину поддержать полный запрет на операции с криптовалютами в России.
+ЦБ хочет полностью запретить выпуск, майнинг и обращение криптовалют, а также ввести ответственность для российских физических и юридических лиц за нарушение запрета на использование криптовалюты в качестве средства платежа. 
+Вот это прикол [https://www.bbc.com/russian/news-60064826.amp]</t>
         </is>
       </c>
       <c r="G463" s="3" t="inlineStr"/>
@@ -18330,19 +18335,18 @@
       </c>
       <c r="C469" s="3" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
+          <t>2023-12-25</t>
         </is>
       </c>
       <c r="D469" s="3" t="n">
-        <v>26749</v>
+        <v>25556</v>
       </c>
       <c r="E469" s="3" t="inlineStr"/>
       <c r="F469" s="3" t="inlineStr">
         <is>
-          <t>**Одразу три вулкани на планеті розпочали виверження**, — Reuters.
-• В Ісландії вже впʼяте за 3 роки вибухає вулкан на півострові Рейкʼянес. Звідки саме виходить лава досі не зрозуміло, але вона наближається до житлових будинків.
-• В Індонезії стовп попелу з вулкану Марапі піднявся на 1,3 км угору. Після цього пішов сріблястий дощ. Вже евакуювали ~100 людей. Марапі відомий своєю раптовістю, яку важко передбачити.
-• У Японії виверження триває на острові Суваносе. Місцевих попереджають про можливість викиду великих каменів у повітря в радіусі 2 км. На щастя, поки без постраждалих.</t>
+          <t>«Вони мають здихати від отаких от штучок», — військовий ЗСУ з позивним D2 для DW про російських штурмовиків, яких атакують FPV-дронами.
+**Вартість одного БПЛА з бойовою частиною ~$1000. Тому 3-4 дрони будуть коштувати як 1 артснаряд.** Бійці з Авдіївському напрямку розповідають, що рекордно за день одна група використовувала 35 штук.
+Одна з головних проблем — це робота РЕБ ворога. Вона «глушить» сигнал «пташки». Інша проблема — мороз. Іноді бійцям доводиться зігрівати БПЛА за допомогою хімічних грілок.</t>
         </is>
       </c>
       <c r="G469" s="3" t="inlineStr"/>
@@ -18483,16 +18487,17 @@
       </c>
       <c r="C473" s="3" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D473" s="3" t="n">
-        <v>43537</v>
+        <v>49456</v>
       </c>
       <c r="E473" s="3" t="inlineStr"/>
       <c r="F473" s="3" t="inlineStr">
         <is>
-          <t>Розбився російський Су-34 у Волгоградській області під час виконання навчального польоту. Пишуть, що екіпаж катапультувався.</t>
+          <t>Харків в ці хвилини. Місто під ударом шахедів, пролунало щонайменше три вибухи.
+Є влучання уламків безпілотника у житловий будинок, додали в ОВА.</t>
         </is>
       </c>
       <c r="G473" s="3" t="inlineStr"/>
@@ -18702,17 +18707,17 @@
       </c>
       <c r="C479" s="3" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-06-13</t>
         </is>
       </c>
       <c r="D479" s="3" t="n">
-        <v>39142</v>
+        <v>17738</v>
       </c>
       <c r="E479" s="3" t="inlineStr"/>
       <c r="F479" s="3" t="inlineStr">
         <is>
-          <t>❗️**Росіяни окупували Птиче та просунулись на Донеччині,** — DeepState. 
-Загарбники тиснуть біля Піщаного, Калинового, у Карлівці, Мемрику, Красному Яру, Михайлівці, Північному, Новогродівці та на околицях.</t>
+          <t>10 загиблих у Кривому Розі. З-під завалів підприємства дістали тіла 6 осіб. Там шукають ще одну людину. 4 загинули у багатоповерхівці, – ОВА.
+**UPD:** завтра у місті оголошено День жалоби, – голова ВЦА.</t>
         </is>
       </c>
       <c r="G479" s="3" t="inlineStr"/>
@@ -18846,18 +18851,18 @@
       </c>
       <c r="C483" s="3" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="D483" s="3" t="n">
-        <v>19911</v>
+        <v>38991</v>
       </c>
       <c r="E483" s="3" t="inlineStr"/>
       <c r="F483" s="3" t="inlineStr">
         <is>
-          <t>З 1 вересня у школах з’явиться **новий вид дистанційки — змішана**, — прем’єр-міністр Денис Шмигаль. 
-Учні, які перебувають за межами країни, **будуть вивчати «український компонент»** по 6-8 годин на тиждень і отримуватимуть оцінки, а решту предметів їм зарахують автоматично з закордонного табеля. 
-Водночас **63% українців не підтримують дистанційне навчання в школах**, —** **опитування Фонду «Демократичні ініціативи» ім. Ілька Кучеріва. Соціологи вияснили, що негативне ставлення до онлайн-навчання не пов’язане з тим, чи є у школі повноцінне укриття.</t>
+          <t>⚡ **Ого! На ****Полтавщині** [https://t.me/+lMD1Y11V9TkxM2Yy]** сьогодні помітили смерч**, — очевидці.
+Місцеві кажуть, що міні-торнадо гуляло полем, згодом пройшлось по дорозі і вже з меншою силою почало кружляти над іншою ділянкою.
+Метеорологи зазначають, пилові вихори виникають влітку, коли сонце досить добре прогріває земну поверхню. Саме за таких умов утворюються висхідні потоки повітря.</t>
         </is>
       </c>
       <c r="G483" s="3" t="inlineStr"/>
@@ -19111,17 +19116,26 @@
       </c>
       <c r="C490" s="3" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="D490" s="3" t="n">
-        <v>17133</v>
+        <v>55346</v>
       </c>
       <c r="E490" s="3" t="inlineStr"/>
       <c r="F490" s="3" t="inlineStr">
         <is>
-          <t>Мінськ і москва підписали документ про розміщення ядерної зброї в Білорусі: [https://t.me/c/1431180517/15758] росія планує побудувати сховище. Контролює «червону кнопку» рф, – DW.
-__Лукашенко: «Я нічого не чув, але подякував». __</t>
+          <t>❗️Це була одна з **найбільших атак за останні місяці**: гігантські табуни дронів били по **Заходу України** та **Києву** [https://t.me/+5s7ZDCzggiU2NjE6], під ранок рф випустила ще й ракети — **які наслідки ударів**?
+⭕️**Вінниччина** [https://t.me/+-OsopRCAAN5mODZi]: влучання в цивільні** промислові обʼєкти**, також відомо про одного постраждалого, — ОВА.
+⭕️**Черкащина** [https://t.me/+vdi7Pu5pzJE3NTc6]:** **пошкоджено **лінію електропередач**, також понівечені житлові будинки, — ОВА.
+⭕️**Житомирщина** [https://t.me/+yvxVyrmSne9lYTYy]: одна **людина загинула**, ще одна — дістала поранення. Регіон сьогодні також був атакований і БПЛА, і ракетами. Пошкоджено **кілька підприємств та приватні будинки**, — ОВА.
+⭕️**Львівщина** [https://t.me/+7hFTk0dk_mxmYjli]: це була одна із **найгірших ночей для **Львова [https://t.me/+7hFTk0dk_mxmYjli] — рф била по місту і дронами, і ракетами. Системи життєзабезпечення області працюють у **штатному режимі**, — ОВА.
+⭕️**Волинь** [https://t.me/+jWWOBqRnhK9jODYy]: регіон масово атакували БПЛА — є **падіння уламків на кількох локаціях**. Зафіксовано безліч пожеж. Без постраждалих та загиблих, — ОВА.
+⭕️**Хмельниччина** [https://t.me/+n1sBnWk3V1BkNDM6]: травмовано 3-є людей. У Волочиську є **влучання у складські приміщення**, — ОВА.
+⭕️Вибухи також лунали в Києві [https://t.me/+5s7ZDCzggiU2NjE6], Рівному [https://t.me/+JyUisNPbKyVjYzAy], на Івано-Франківщині [https://t.me/+qrMsA-AAlZFjZjhi] та Буковині [https://t.me/+p-6zY7YgwF4xNjUy] — там **посилено працювала ППО** по ворожих цілях.
+⭕️Уночі над Україною **збито** **413/458 цілей** **рф**: серед них — 386/415 БПЛА та 27/43 ракет. Зафіксовано влучання **на 17 локаціях**, — ПС.
+⭕️Дрони рф **долетіли до НАТО** — безліч БПЛА вночі атакували прикордонні **регіони Польщі**, подекуди в країні закривали аеропорти. Підіймалась і авіація для ураження цілей.
+⭕️Під ранок у Польщі оголосили **пришвидшений виклик резервістів тероборони** через атаку російських БПЛА, пише Reuters.</t>
         </is>
       </c>
       <c r="G490" s="3" t="inlineStr"/>
@@ -19335,11 +19349,11 @@
       </c>
       <c r="C496" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="D496" s="3" t="n">
-        <v>117639</v>
+        <v>90057</v>
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
@@ -19348,10 +19362,12 @@
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
-          <t>**❗️❗️В енергетиці України буде запроваджено режим надзвичайної ситуації, — Зеленський **
-📍Окрема увага — ситуації в Києві. Буде утворений штаб щодо координації ситуації в місті, який діятиме постійно. 
-📍«Дистанційки» стане більше: Зеленський доручив МОН і місцевій владі підготувати формат навчального процесу на час надзвичайної ситуації в енергетиці.
-📍Акцент на злагодженій роботі держави, бізнесу та місцевої влади для забезпечення безперебійної підтримки людей.</t>
+          <t>**❗️Завтра знову діятимуть графіки відключень, — Укренерго **
+📍6:00 - 7:00 – одна черга відключень.
+📍7:00 – 9:00 – дві черги відключень.
+📍9:00 – 14:00 – одна черга відключень.
+📍14:00 – 18:00 – дві черги відключень.
+📍18:00 – 23:00 – одна черга відключень.</t>
         </is>
       </c>
       <c r="G496" s="3" t="inlineStr"/>
@@ -19639,25 +19655,22 @@
       </c>
       <c r="B504" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C504" s="3" t="inlineStr">
         <is>
-          <t>2021-08-02</t>
+          <t>2023-12-17</t>
         </is>
       </c>
       <c r="D504" s="3" t="n">
-        <v>4664</v>
+        <v>16497</v>
       </c>
       <c r="E504" s="3" t="inlineStr"/>
       <c r="F504" s="3" t="inlineStr">
         <is>
-          <t>**СБУ нейтрализовала "пророссийскую силовую ячейку"**
-Сотрудники Службы безопасности Украины нейтрализовали "силовую ячейку" пророссийского общественного объединения, которое контролировал народный депутат Украины. 
-Утверждается, что были предотвращены попытки расшатывания общественно-политической ситуации в восточных регионах Украины.
-"Во время спецоперации в Харькове, Северодонецке и Лисичанске блокирована деятельность группировки, причастной к совершению тяжких преступлений на идеологической почве", – говорится в сообщении.
-Как сообщает РБК-Украина со ссылкой на информированный источник, речь идет о нардепе Илье Киве и организации Патриоты – За жизнь.</t>
+          <t>❗️**ДТП у Карпатах: четверо загиблих, серед них – один з керівників Держспецтрансслужби**.
+Віктор Жигунов **перебував** [https://news.liga.net/ua/incidents/news/dtp-v-karpatakh-chetvero-zahyblykh-sered-nykh-odyn-z-kerivnykiv-derzhspetstransluzhby] у легковому автомобілі Ford Focus на військових номерах, який під час обгону зіткнувся з вантажівкою Volvo.</t>
         </is>
       </c>
       <c r="G504" s="3" t="inlineStr"/>
@@ -19766,17 +19779,23 @@
       </c>
       <c r="C507" s="3" t="inlineStr">
         <is>
-          <t>2023-12-17</t>
+          <t>2023-11-07</t>
         </is>
       </c>
       <c r="D507" s="3" t="n">
-        <v>16497</v>
+        <v>15185</v>
       </c>
       <c r="E507" s="3" t="inlineStr"/>
       <c r="F507" s="3" t="inlineStr">
         <is>
-          <t>❗️**ДТП у Карпатах: четверо загиблих, серед них – один з керівників Держспецтрансслужби**.
-Віктор Жигунов **перебував** [https://news.liga.net/ua/incidents/news/dtp-v-karpatakh-chetvero-zahyblykh-sered-nykh-odyn-z-kerivnykiv-derzhspetstransluzhby] у легковому автомобілі Ford Focus на військових номерах, який під час обгону зіткнувся з вантажівкою Volvo.</t>
+          <t>**Найвищі виплати українським біженцям серед країн Європи за ****даними** [https://news.finance.ua/ru/ne-men-she-zarplaty-v-kakih-stranah-evropy-ukrainskie-bezhency-poluchayut-samye-vysokie-vyplaty]** швейцарського фонду EnableMe:**
+🇧🇪Бельгія - 1140 євро на місяць
+🇮🇪Ірландія - 824 євро
+🇳🇴Норвегія - 650 євро
+🇩🇪Німеччина - 502 євро
+🇫🇷Франція - 426 євро
+🇨🇭Швейцарія - 350-500 євро
+🇬🇧Великобританія - 300 євро</t>
         </is>
       </c>
       <c r="G507" s="3" t="inlineStr"/>
@@ -19868,22 +19887,22 @@
       </c>
       <c r="B510" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C510" s="3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="D510" s="3" t="n">
-        <v>95978</v>
+        <v>12769</v>
       </c>
       <c r="E510" s="3" t="inlineStr"/>
       <c r="F510" s="3" t="inlineStr">
         <is>
-          <t>**- Я можу сказати, містере президент?** — Зеленський 
-- Ні, ти і так багато сказав! **— Трамп 👀</t>
+          <t>❗️**Група крилатих ракет заходять у повітряний простір України** **через  Сумську область**
+Напрямок руху – на захід, – ПС.</t>
         </is>
       </c>
       <c r="G510" s="3" t="inlineStr"/>
@@ -20049,16 +20068,16 @@
       </c>
       <c r="B515" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C515" s="3" t="inlineStr">
         <is>
-          <t>2023-04-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="D515" s="3" t="n">
-        <v>8659</v>
+        <v>59722</v>
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
@@ -20067,8 +20086,10 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>**Вийти на кордони 1991 року – цілком досяжне завдання цього року** - Буданов. [https://www.rbc.ua/rus/news/kirilo-budanov-viyti-kordoni-1991-roku-tsilkom-1682282231.html]
-«Ми підходимо до знакової битви для новітньої історії України. Це факт, усі це розуміють. Коли вона почнеться, це є таємницею. Але всі розуміють, що ми до цього наближаємось» - каже голова ГУР.</t>
+          <t>МОЗ виніс на громадське обговорення проєкт змін [https://www.drs.gov.ua/wp-content/uploads/2026/02/947.pdf], які можуть суттєво змінити правила проведення клінічних випробувань в Україні. Згідно з пропозицією, дослідження планують проводити переважно на базі університетських клінік, наукових установ та навчальних закладів — перелік таких установ визначатиме МОЗ.
+Представники бізнесу та експертної спільноти попереджають: якщо дозволити клінічні дослідження лише на таких майданчиках, Україна може втратити значну частину ринку — до 75% досліджень — і стати [https://eba.com.ua/ukrayina-ryzykuye-vtratyty-do-75-rynku-klinichnyh-doslidzhen-u-razi-zaprovadzhennya-zmin-do-poryadku-provedennya-klinichnyh-doslidzhen] менш привабливою для міжнародних інвесторів.
+За оцінками, це може призвести до втрати $100–150 млн щорічно та скорочення податкових надходжень.
+Найважливіше — наслідки для пацієнтів. Для людей з онкологічними та аутоімунними захворюваннями клінічні дослідження часто є шансом отримати доступ до сучасного лікування. Менша кількість центрів означає менше можливостей для таких пацієнтів.</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr"/>
@@ -20624,21 +20645,21 @@
       </c>
       <c r="B530" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C530" s="3" t="inlineStr">
         <is>
-          <t>2022-06-23</t>
+          <t>2023-02-07</t>
         </is>
       </c>
       <c r="D530" s="3" t="n">
-        <v>14312</v>
+        <v>13448</v>
       </c>
       <c r="E530" s="3" t="inlineStr"/>
       <c r="F530" s="3" t="inlineStr">
         <is>
-          <t>Біля будівлі Ради Євросоюзу в Брусселі зібрався мітинг на підтримку надання статусу кандитата для України, повідомляє Суспільне.</t>
+          <t>Жіночий батальйон снайперки з позивним «Жанна д’Арк». Ювелірка Євгенія Емеральд, яка добровільно пішла на війну, зараз вагітна та чекає на другу дівчинку. На фронті вона зустріла коханого, з яким одружилася. «Зброю почала тримати з 9 років завдяки татові-мисливцю. Пізніше стала колекціонувати її. Пальба з гвинтівки була антистресом, коли займалася бізнесом», – каже Женя «Радіо Свобода». Наразі вона у тилу й готується до пологів.</t>
         </is>
       </c>
       <c r="G530" s="3" t="inlineStr"/>
@@ -20731,22 +20752,22 @@
       </c>
       <c r="B533" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C533" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="D533" s="3" t="n">
-        <v>49637</v>
+        <v>42512</v>
       </c>
       <c r="E533" s="3" t="inlineStr"/>
       <c r="F533" s="3" t="inlineStr">
         <is>
-          <t>Ми ще ніколи не були так близькі до миру. Ми обговоримо поширення режиму припинення вогню на Чорне море, — Білий дім.
-Американська команда вирушить до Саудівської Аравії наприкінці цього тижня для подальших переговорів.</t>
+          <t>❗️**Наступні 4-5 місяців стануть вирішальними у війні**, — Reuters цитує високопоставленого українського чиновника.
+«Ця зима — критичний момент... Війна наближається до кінця, сподіваюсь. Саме зараз ми **визначимо позиції для обох сторін на переговорах**, стартові позиції».</t>
         </is>
       </c>
       <c r="G533" s="3" t="inlineStr"/>
@@ -20846,20 +20867,18 @@
       </c>
       <c r="C536" s="3" t="inlineStr">
         <is>
-          <t>2021-07-18</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="D536" s="3" t="n">
-        <v>4533</v>
+        <v>56224</v>
       </c>
       <c r="E536" s="3" t="inlineStr"/>
       <c r="F536" s="3" t="inlineStr">
         <is>
-          <t>**Модный укол - это путь в никуда **
-Основатель и руководитель клиники «ГЕНЕЗИС ДНЕПР»  Игорь Перелыгин жестко раскритиковал вакцинацию против COVID-19 , назвав ее путём в никуда.
-Его пост в фейсбуке [https://www.facebook.com/100009642480197/posts/1503677309963671/?d=n] вызвал бурный поток эмоций: как в поддержку, так и в негатив.
-Не удержался и городской голова Борис Филатов: __«Ну что Перелыгин, теперь ты наслаждаешься ебанариумом упоротых, которых ты собрал с просторов всего бывшего СССР? Купаешься в лучах славы ? Пора тобой заняться , ещё с первой каденции есть за тобой должок.»__
-ЙАД &gt; Подписаться [https://t.me/Yad_OK]</t>
+          <t>Підвищення тарифів на вантажні перевезення УЗ **зруйнує економіку й оборону**. 
+⭕️Нацасоціація добувної промисловості закликала парламент **дати Укрзалізниці бюджетне фінансування на «пасажирку»** — інакше проблеми [https://www.dsnews.ua/ukr/economics/pidvishchennya-tarifiv-na-vantazhni-perevezennya-zgubne-dlya-ekonomiki-i-samoji-ukrzaliznici-nadpu-29092025-529354] будуть і в економіки, **і в оборонного сектору**. 
+За прогнозами, збитки пасажирського сегмента УЗ у 2026 році **сягнуть 24 млрд грн**. Покрити їх за рахунок вантажних перевезень, як робили до цього, не вийде — **промисловість почне просто закриватися**. А це означає менше робочих місць — і менше грошей в бюджет. Власне, це також означає, **що** **УЗ отримає збитки замість грошей, на які розраховує**. І покривати пасажирку стане зовсім нічим.</t>
         </is>
       </c>
       <c r="G536" s="3" t="inlineStr"/>
@@ -21647,22 +21666,24 @@
       </c>
       <c r="B557" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C557" s="3" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="D557" s="3" t="n">
-        <v>33348</v>
+        <v>776</v>
       </c>
       <c r="E557" s="3" t="inlineStr"/>
       <c r="F557" s="3" t="inlineStr">
         <is>
-          <t>**Завершення війни у 2025 році означатиме, що Україна програла, тому нам краще воювати і у наступні роки, аж до повного програшу росії, — ****Дикий.** [https://www.unian.ua/war/viyna-maye-pereyti-u-2026-rik-dikiy-zrobiv-nespodiniy-prognoz-12885237.html]**
-Сподіваюсь Дикий покаже приклад?</t>
+          <t>**Россия находится на финальном этапе подготовки к вторжению в Украину**
+С таким заголовком вышла [https://www.nytimes.com/2022/02/04/world/europe/russian-troops-ukraine-crimean-peninsula.html] статья на сайте издания New York Times. Журналисты с ссылкой на источники в украинском командовании собщают, что Россия пока не готова к вторжению на украинскую территорию, но находится на финальном этапе подготовки к военной операции.
+В частности, собеседники издания отметили переброску в Крым за последние две недели около 10 тысяч российских военных и приведение некоторых размещённых на полуострове подразделений в состояние повышенной боевой готовности.
+Закончить подготовку к военной операции, по оценкам экспертов, РФ может в течение нескольких недель. Пока, отмечают они, у России возле границ достаточное количество военнослужащих, но не полностью выстроены линии снабжения и другая инфраструктура.</t>
         </is>
       </c>
       <c r="G557" s="3" t="inlineStr"/>
@@ -22053,17 +22074,16 @@
       </c>
       <c r="C568" s="3" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D568" s="3" t="n">
-        <v>38532</v>
+        <v>63370</v>
       </c>
       <c r="E568" s="3" t="inlineStr"/>
       <c r="F568" s="3" t="inlineStr">
         <is>
-          <t>**Українські військові не змогли повторити «курський прорив» у Бєлгородській області, **— ISW.**
-**Вони змушені були покинути її через гарну підготовленість росіян до відбиття транскордонних атак. За даними аналітиків, українські війська більше не утримують позиції на Бєлгородщині.</t>
+          <t>❗️**Кінцем війни навіть не пахне**: про це мені повідомили учасники переговорів. **Росіяни впевнені, що скоро дійдуть до ****Запоріжжя** [https://t.me/zaporizhzhia_times]** і захоплять усю Донеччину**, — «Миколаївський Ваньок».</t>
         </is>
       </c>
       <c r="G568" s="3" t="inlineStr"/>
@@ -22157,22 +22177,26 @@
       </c>
       <c r="B571" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C571" s="3" t="inlineStr">
         <is>
-          <t>2022-01-29</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D571" s="3" t="n">
-        <v>595</v>
+        <v>59863</v>
       </c>
       <c r="E571" s="3" t="inlineStr"/>
       <c r="F571" s="3" t="inlineStr">
         <is>
-          <t>За даними [https://www.wsj.com/articles/biden-sanctions-plan-targets-russian-banks-companies-and-imports-if-ukraine-is-attacked-11643387219?mod=hp_lead_pos8] **«The Wall Street Journal»**, якщо росіяни нападуть на Україну, США **не** відключить Росію від системи SWIFT. Також під санкції не підпаде експорт нафти і газу. Єдине, що загрожує Росії — це пакет санкцій щодо низки російських банків, конкретних державних посадовців і держборгу РФ. 
-Як то кажуть, підтримка України — підтримкою України, але 20$ це завжди 20$.</t>
+          <t>💙 Замість того, щоб закрити корупційні схеми й тіньові потоки, **усе знову перекладається на плечі малого бізнесу та простих людей**, — Дмитро Разумков.
+За словами політика, замість реального посилення оборони в бюджеті на 2026 рік у нас:
+⭕️**Немає боротьби з контрабандою**, яка щороку з’їдає десятки мільярдів гривень бюджету.
+⭕️**Готуються нові податкові удари по ФОПах**: зокрема, запровадження ПДВ уже з першого мільйона обороту.
+⭕️**Плануються податки на посилки з-за кордону та на OLX**, а також — безстроковий військовий збір.
+Детально про те, чому **Держбюджет-2026 є незбалансованим**, які корупційні схеми в ньому закладені, а також **про контрабанду і підвищення податків для ФОПів** — в інтерв’ю Дмитра Разумкова каналу Times of Ukraine. [https://youtu.be/UVsxCiHQ0Z8]</t>
         </is>
       </c>
       <c r="G571" s="3" t="inlineStr"/>
@@ -22228,23 +22252,29 @@
       </c>
       <c r="B573" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C573" s="3" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="D573" s="3" t="n">
-        <v>22978</v>
+        <v>685</v>
       </c>
       <c r="E573" s="3" t="inlineStr"/>
       <c r="F573" s="3" t="inlineStr">
         <is>
-          <t>**22 загиблих, ~55 поранених: в Льюїстоні (штат Мен, США) чоловік влаштував хаотичну масову стрілянину**. Злочинець досі на волі, — NBC. 
-За попередніми даними, стрілка звати Роберт Кард (40 років). Він озброєний рушницею та відкрив вогонь посеред вулиць, в кафе, боулінгу, супермаркеті тощо.
-На початку року він лежав 2 тижні у психіатричній лікарні, бо має проблеми та «чує голоси». Кард — інструктор із вогнепальної зброї та офіцер у відставці. Раніше погрожував розстріляти базу Національної гвардії та був заарештований за домашнє насильство, — АP.</t>
+          <t>**"Это мой кент. Никаких претензий не будет!": **УП обнародовало видео с Трухиным после ДТП [https://youtu.be/86uzoruHMgM]
+__- Дай, я тихонечко в лес уйду. 
+- Не получится
+- Я с Денисом поговорю
+- Каким?
+- Монастырским
+- Принеси мне сумку из багажника. Обычная спортивная сумка. Там 150 тысяч
+__По данным СМИ, 23 августа народный депутат фракции "Слуга народа" Александр Трухин, будучи выпившим, создал ДТП по дороге из Полтавы в Киев.
+Впоследствии около 30 медиа почистили [https://www.pravda.com.ua/news/2021/08/30/7305437/] сообщение об этой аварии, в которой пострадали шесть человек.</t>
         </is>
       </c>
       <c r="G573" s="3" t="inlineStr"/>
@@ -22608,11 +22638,11 @@
       </c>
       <c r="C583" s="3" t="inlineStr">
         <is>
-          <t>2022-05-28</t>
+          <t>2022-07-15</t>
         </is>
       </c>
       <c r="D583" s="3" t="n">
-        <v>7637</v>
+        <v>7925</v>
       </c>
       <c r="E583" s="3" t="inlineStr">
         <is>
@@ -22621,9 +22651,8 @@
       </c>
       <c r="F583" s="3" t="inlineStr">
         <is>
-          <t>**❗️Сталі відомі подробиці чому Порошенко не зміг покинути Україну. Видання "Країна" з посиланням на джерела повідомляє, вчора, близько десятої вечора Порошенко в оточенні ще п'яти осіб, у тому числі охорони пробував перейти кордон на прикордонному переході Рава-Руська.
-Він надав копію розпорядження спікера Ради від 24 травня про відрядження для участі у парламентській асамблеї НАТО. Проте, прикордонники так і не змогли встановити справжність наданих документів, тому що не зчитувався Qr-код. Дві години Порошенко та делегацію протримали на кордоні, після чого вони самостійно поїхали у зворотному напрямку.
-****__Info Україна 🇺🇦__** [https://t.me/+SRWsVjpx0-dhYzMy]</t>
+          <t>**Послаблення для росії не буде:** за словами глави німецької дипломатії Анналени Бербок: "пом'якшення санкцій тому, хто жорстко порушує міжнародне право, буде означати "запрошення" повторювати дії РФ усім, хто зневажає права людини, свободу й демократію", — Deutsche Welle.
+**__Info Україна 🇺🇦__** [https://t.me/+SRWsVjpx0-dhYzMy]</t>
         </is>
       </c>
       <c r="G583" s="3" t="inlineStr"/>
@@ -22908,16 +22937,16 @@
       </c>
       <c r="B591" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C591" s="3" t="inlineStr">
         <is>
-          <t>2022-12-12</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="D591" s="3" t="n">
-        <v>4558</v>
+        <v>2696</v>
       </c>
       <c r="E591" s="3" t="inlineStr">
         <is>
@@ -22926,8 +22955,12 @@
       </c>
       <c r="F591" s="3" t="inlineStr">
         <is>
-          <t>**До перемоги я буду президентом, а потім не знаю. Хочу на море і пива**, — Зеленський.
-«До нашої перемоги я точно буду президентом. А там – навіть не думаю. Поки що не думаю, не готовий. Просто хочеться на море, коли ми вже перемогли, і випити пива дуже хочу».</t>
+          <t>**🇺🇦**Info Украuна [https://t.me/ua_info_news]**
+В Украине хотят зарегистрировать российскую вакцину от COVID-19**
+Харьковская компания "Биолек" якобы подала на регистрацию в Украине российскую вакцину от коронавируса "Спутник V".
+Об этом заявил народный депутат от ОПЗЖ Виктор Медведчук
+Указано, что заявление компания подала еще 30 декабря в Министерство здравоохранения Украины и Государственный экспертный центр Минздрава.
+В Верховной раде сомневаются в регистрации российской вакцины "Спутник V" в Украине. Глава комитета ВР по вопросам здоровья нации Михаил Радуцкий заявил, что ему пока ничего неизвестно о такой заявке.</t>
         </is>
       </c>
       <c r="G591" s="3" t="inlineStr"/>
@@ -23784,16 +23817,19 @@
       </c>
       <c r="C614" s="3" t="inlineStr">
         <is>
-          <t>2023-06-27</t>
+          <t>2023-05-07</t>
         </is>
       </c>
       <c r="D614" s="3" t="n">
-        <v>54824</v>
+        <v>50976</v>
       </c>
       <c r="E614" s="3" t="inlineStr"/>
       <c r="F614" s="3" t="inlineStr">
         <is>
-          <t>**Справу про збройний заколот припинено 27 червня, оскільки учасники припинили дії, безпосередньо спрямовані на вчинення злочину, — ФСБ</t>
+          <t>**❗️Угроза ракетного удара чрезвычайно высока на фоне активности стратегической авиации, — ОК "Південь"
+**В Черном море продолжают находиться четыре ракетоносителя: суммарный залп составляет 32 "Калибра". В общей сложности корабельная группировка насчитывает 17 единиц.
+Также есть угроза налета БПЛА типа "Шахид" из Брянской области.
+**UPD:** Сообщают о взрыве в Одессе — корреспонденты "Суспільного"</t>
         </is>
       </c>
       <c r="G614" s="3" t="inlineStr"/>
@@ -23934,22 +23970,24 @@
       </c>
       <c r="B618" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C618" s="3" t="inlineStr">
         <is>
-          <t>2022-02-23</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="D618" s="3" t="n">
-        <v>1656</v>
+        <v>122169</v>
       </c>
       <c r="E618" s="3" t="inlineStr"/>
       <c r="F618" s="3" t="inlineStr">
         <is>
-          <t>‼️Чрезвычайное положение подразумевает** усиление охраны общественного порядка, возможное ограничение движения транспорта и его осмотр, проверка тех или иных документов у физических лиц, **заявил** **Алексей Данилов.
-Также секретарь СНБО объяснил, что ЧП не вводится в Донецкой и Луганской областях, т.к. там оно действует с 2014 года.</t>
+          <t>**Українці труяться пельменями з АТБ "Мішутка", — соцмережі**
+Жінка пише, що з’їла пів порції цих дитячих пельменів, куплених в АТБ, після чого почалося сильне отруєння, вона не може нормально ні їсти, ні пити.
+За цей період **на лікування вже витратила близько 1500 грн, якщо ліки не допоможуть — можлива госпіталізація.** Інші користувачі теж підтверджують подібні випадки, пов'язані з дитячими пельменями "Мішутка".
+Жах...дитячі пельмені...😢</t>
         </is>
       </c>
       <c r="G618" s="3" t="inlineStr"/>
@@ -24047,22 +24085,21 @@
       </c>
       <c r="B621" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C621" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="D621" s="3" t="n">
-        <v>111625</v>
+        <v>36343</v>
       </c>
       <c r="E621" s="3" t="inlineStr"/>
       <c r="F621" s="3" t="inlineStr">
         <is>
-          <t>**❗️Україна готова до переговорів, але не на умовах віддачі незахоплених територій, — Зеленський **
-Путін не хоче переговорів — він тягне час.</t>
+          <t>**США оголосили новий пакет військової допомоги у $100 мільйонів**, — міністр оборони США у Києві.</t>
         </is>
       </c>
       <c r="G621" s="3" t="inlineStr"/>
@@ -24210,17 +24247,17 @@
       </c>
       <c r="C625" s="3" t="inlineStr">
         <is>
-          <t>2023-09-21</t>
+          <t>2023-09-11</t>
         </is>
       </c>
       <c r="D625" s="3" t="n">
-        <v>60526</v>
+        <v>59843</v>
       </c>
       <c r="E625" s="3" t="inlineStr"/>
       <c r="F625" s="3" t="inlineStr">
         <is>
-          <t>**Пілотну версію 5G у Києві можуть запустити вже 2024 року, — **[**Михайло Федоров
-**](https://forbes.ua/innovations/armiya-rebu-mask-dosi-dopomogae-derzhupravlinnya-z-elementami-gri-vsi-shkolyari-v-odniy-mrii-i-pershiy-test-5g-fedorov-rozpoviv-pro-plani-mintsifri-na-2024-y-rik-18092023-16066)Україна Online | Підписатись [https://t.me/+PrLok3ySBnljZWMy]</t>
+          <t>**Після спецоперації з ****російським Мі-8** [https://t.me/UaOnlii/59416]** на 70% зросла кількість військових РФ, охочих здатися у полон, — представник ГУР Юсов
+**«Є дуже стрибок по лінії «Хочу жить» окремо і по інших каналах зв’язку. Після успішної операції «Синиця» з Мі-8 і пілотом, скажімо, збільшилась кількість військовослужбовців армії РФ, які розглядають для себе подібний сценарій. Звернення на державний проєкт «Хочу жить» – стрибок відбувся приблизно на 70 відсотків за день», – заявив Андрій Юсов.</t>
         </is>
       </c>
       <c r="G625" s="3" t="inlineStr"/>
@@ -24282,16 +24319,17 @@
       </c>
       <c r="C627" s="3" t="inlineStr">
         <is>
-          <t>2022-05-07</t>
+          <t>2024-03-01</t>
         </is>
       </c>
       <c r="D627" s="3" t="n">
-        <v>10993</v>
+        <v>39718</v>
       </c>
       <c r="E627" s="3" t="inlineStr"/>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>Снова бабахи в Белгороде пишут местные тг</t>
+          <t>**Президентські вибори в США: **Трамп випереджає Байдена в семи ключових штатах, які, ймовірно, визначатимуть результат виборів, — опитування Bloomberg News/Morning Consult [https://www.bloomberg.com/news/articles/2024-02-29/biden-age-worries-swing-state-voters-trump-seen-as-dangerous-poll-shows?embedded-checkout=true].
+Загалом у цих семи штатах 48% виборців заявили, що підтримають Трампа, а 43% – Байдена.</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr"/>
@@ -24321,15 +24359,20 @@
         </is>
       </c>
       <c r="D628" s="3" t="n">
-        <v>776</v>
+        <v>786</v>
       </c>
       <c r="E628" s="3" t="inlineStr"/>
       <c r="F628" s="3" t="inlineStr">
         <is>
-          <t>**Россия находится на финальном этапе подготовки к вторжению в Украину**
-С таким заголовком вышла [https://www.nytimes.com/2022/02/04/world/europe/russian-troops-ukraine-crimean-peninsula.html] статья на сайте издания New York Times. Журналисты с ссылкой на источники в украинском командовании собщают, что Россия пока не готова к вторжению на украинскую территорию, но находится на финальном этапе подготовки к военной операции.
-В частности, собеседники издания отметили переброску в Крым за последние две недели около 10 тысяч российских военных и приведение некоторых размещённых на полуострове подразделений в состояние повышенной боевой готовности.
-Закончить подготовку к военной операции, по оценкам экспертов, РФ может в течение нескольких недель. Пока, отмечают они, у России возле границ достаточное количество военнослужащих, но не полностью выстроены линии снабжения и другая инфраструктура.</t>
+          <t>**8 угод, що були підписані між Україною та **Туреччиною [https://t.me/DeepStateUA/8101]**
+**1. Угода про вільну торгівлю.
+2. Програма визнання авторизованих економічних операторів.
+3. Про Ортоцький митний комітет.
+4. Про дослідження, стандартизацію та сертифікацію.
+5. Авіаційна та космічна угода.
+6. Протокол про співпрацю ще з 2009 року.
+7. Молодіжна політика.
+8. Про співробітництво у податковій сфері.</t>
         </is>
       </c>
       <c r="G628" s="3" t="inlineStr"/>
@@ -24981,23 +25024,22 @@
       </c>
       <c r="B646" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C646" s="3" t="inlineStr">
         <is>
-          <t>2022-11-05</t>
+          <t>2023-06-07</t>
         </is>
       </c>
       <c r="D646" s="3" t="n">
-        <v>3369</v>
+        <v>17545</v>
       </c>
       <c r="E646" s="3" t="inlineStr"/>
       <c r="F646" s="3" t="inlineStr">
         <is>
-          <t>«**Укроборонпром» налагодив виробництво 122-мм і 152-мм снарядів.
-**Про це під час брифінгу повідомив [https://youtu.be/IctqdWYPeKw] міністр оборони України Олексій Резніков.
-Нові артилерійські снаряди до радянських систем вже пройшли випробування.</t>
+          <t>Вулиці Владивостока (рф) затопило коричневою гарячою рідиною через аварію на теплотрасі. Без води залишились ~23 000 людей, – РИА «Новости».
+__Миттєва карма.</t>
         </is>
       </c>
       <c r="G646" s="3" t="inlineStr"/>
@@ -25245,21 +25287,23 @@
       </c>
       <c r="B653" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C653" s="3" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="D653" s="3" t="n">
-        <v>4903</v>
+        <v>777</v>
       </c>
       <c r="E653" s="3" t="inlineStr"/>
       <c r="F653" s="3" t="inlineStr">
         <is>
-          <t>Зеленский, Ахметов, Коломойский и другие политики уже давно подписаны на Администрацию Президента, а ты еще нет? [https://t.me/AP_UA]</t>
+          <t>У Харкові відбувся "Марш Єдності", який закликаний показати, що Харків українське місто і люди готові його захищати. 
+За даними ЗМІ [https://t.me/novinach] у акції взяли учать близько 5000 людей 💪🏻
+Ну що, сходку підписників робимо у Дніпрі ?)</t>
         </is>
       </c>
       <c r="G653" s="3" t="inlineStr"/>
@@ -25592,18 +25636,16 @@
       </c>
       <c r="C662" s="3" t="inlineStr">
         <is>
-          <t>2021-03-29</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="D662" s="3" t="n">
-        <v>3405</v>
+        <v>18514</v>
       </c>
       <c r="E662" s="3" t="inlineStr"/>
       <c r="F662" s="3" t="inlineStr">
         <is>
-          <t>Президент Зеленский настаивает на введении "паспортов вакцинации" в Украине
-Как заявил Владимир Зеленский, Украина не должна отставать от многих развитых стран, которых уже начали разработку "ковид-паспортов". 
-В Минцифры отметили, что все данные и так записываются, но сейчас в Украине пока рано вводить "паспорта".</t>
+          <t>До кінця війни** ****тарифи на воду** [https://t.me/c/1431180517/18426]** залишаться незмінними, **— прем’єр-міністр Денис Шмигаль. Місцеві бюджети зібрали понад 150 млрд грн на своїх рахунках, тому спроможні фінансувати водоканали.</t>
         </is>
       </c>
       <c r="G662" s="3" t="inlineStr"/>
@@ -26258,18 +26300,17 @@
       </c>
       <c r="C680" s="3" t="inlineStr">
         <is>
-          <t>2024-12-07</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="D680" s="3" t="n">
-        <v>43575</v>
+        <v>28314</v>
       </c>
       <c r="E680" s="3" t="inlineStr"/>
       <c r="F680" s="3" t="inlineStr">
         <is>
-          <t>❗️Під ліміт переказів з картки на картку в 150 тисяч **можуть потрапити й перекази через IBAN**, — джерела «Інтерфакс».
-Видання пише, що з 1 липня обмеження взагалі **буде знижено з 150 до 100 тис грн на місяць**.
-__Нагадаємо, з 1 жовтня на півроку Нацбанк __**__встановив__** [https://t.me/c/1431180517/39156]__ __ [https://t.me/c/1431180517/39156]**__ліміт у 150 тисяч грн на місяць__** [https://t.me/c/1431180517/39156]__ для переказів фізичних осіб "з карти на карту". Таке обмеження деякі українці **обходили, надсилаючи кошти через IBAN**. Тепер і цю можливість можуть **скоро забрати**.</t>
+          <t>**Україна почала збивати «шахеди» лазерними ****антидроновими системами Vampire,** [https://t.me/c/1431180517/12339]** **— Defense Express.
+Аналітики вважають, що саме цією системою збивали ворожі дрони в ніч на 11 лютого на Одещині. Кадри збиття опублікували ВМС. «Спочатку наші зенітники беруть БПЛА рф на приціл, використовуючи невідому оптико-електронну станцію, після цього у російський дрон-камікадзе влучає реактивний снаряд, а далі «шахед» зривається в піке і падає».</t>
         </is>
       </c>
       <c r="G680" s="3" t="inlineStr"/>
@@ -26485,11 +26526,11 @@
       </c>
       <c r="C686" s="3" t="inlineStr">
         <is>
-          <t>2022-01-20</t>
+          <t>2022-01-27</t>
         </is>
       </c>
       <c r="D686" s="3" t="n">
-        <v>312</v>
+        <v>530</v>
       </c>
       <c r="E686" s="3" t="inlineStr">
         <is>
@@ -26498,7 +26539,7 @@
       </c>
       <c r="F686" s="3" t="inlineStr">
         <is>
-          <t>В ВОЗ рекомендовали мировому сообществу отменить или ослабить ограничения на международные поездки, констатировав их неэффективность [https://www.pravda.com.ua/rus/news/2022/01/20/7321033/index.amp]</t>
+          <t>**Президент Турции Реджеп Тайип Эрдоган заявил, что для России "глупо нападать на Украину", и что Турция будет действовать как **член НАТО. [https://www.pravda.com.ua/rus/news/2022/01/27/7321833/]</t>
         </is>
       </c>
       <c r="G686" s="3" t="inlineStr"/>
@@ -26555,16 +26596,16 @@
       </c>
       <c r="B688" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C688" s="3" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="D688" s="3" t="n">
-        <v>17048</v>
+        <v>61551</v>
       </c>
       <c r="E688" s="3" t="inlineStr">
         <is>
@@ -26573,7 +26614,7 @@
       </c>
       <c r="F688" s="3" t="inlineStr">
         <is>
-          <t>**Адміністрація Байдена оголосить про ще один пакет зброї для України на 1 мільярд доларів**, — Reuters.</t>
+          <t>⚡** Майже повністю вкрились льодом вікна **у людей в Києві: [https://t.me/kyiv_times_official] така ситуація зараз на лівому березі. У квартирах майже **0°C, **— місцеві ЗМІ.</t>
         </is>
       </c>
       <c r="G688" s="3" t="inlineStr"/>
@@ -26812,24 +26853,22 @@
       </c>
       <c r="B695" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C695" s="3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2022-01-18</t>
         </is>
       </c>
       <c r="D695" s="3" t="n">
-        <v>21409</v>
+        <v>222</v>
       </c>
       <c r="E695" s="3" t="inlineStr"/>
       <c r="F695" s="3" t="inlineStr">
         <is>
-          <t>«Охрен*ть прилёты!» — у Донецьку «бавовна» у будівлі окупаційної адміністрації ватажка «ДНР» Дениса Пушиліна, — Z-канали.
-**UPD:** без загиблих та постраждалих, — гауляйтер прокоментував вибухи.
-__Агов, у вас пропущений. 
-На відео присутнє лихослівʼя.__</t>
+          <t>Молдова обновит сотрудничество с НАТО. Хотят вывода российских войск из Приднестровья
+источник: liganet [https://news.liga.net/politics/news/moldova-obnovit-sotrudnichestvo-s-nato-hotyat-vyvoda-rossiyskih-voysk-iz-pridnestrovya]</t>
         </is>
       </c>
       <c r="G695" s="3" t="inlineStr"/>
@@ -26885,22 +26924,21 @@
       </c>
       <c r="B697" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C697" s="3" t="inlineStr">
         <is>
-          <t>2023-01-10</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="D697" s="3" t="n">
-        <v>12377</v>
+        <v>9802</v>
       </c>
       <c r="E697" s="3" t="inlineStr"/>
       <c r="F697" s="3" t="inlineStr">
         <is>
-          <t>Колаборантів та держзрадників Віктора Медведчука [https://t.me/c/1431180517/12070], Тараса Козака, Андрія Деркача і Рената Кузьміна позбавили громадянства України. Також у них планують забрати мандати народних депутатів, – «Українська правда» з посиланням на ОП. 
-**UPD:** президент України Володимир Зеленський у своєму вечірньому зверненні підтвердив припинення громадянства вищезгаданих чотирьох осіб.</t>
+          <t>Російська влада почала закривати [https://www.epravda.com.ua/news/2022/04/24/686171/] інформацію про основні економічні показники, щоб приховати проблеми, з якими РФ стикається через санкції, пише WSJ</t>
         </is>
       </c>
       <c r="G697" s="3" t="inlineStr"/>
@@ -27764,17 +27802,22 @@
       </c>
       <c r="C720" s="3" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2022-09-24</t>
         </is>
       </c>
       <c r="D720" s="3" t="n">
-        <v>47061</v>
+        <v>37989</v>
       </c>
       <c r="E720" s="3" t="inlineStr"/>
       <c r="F720" s="3" t="inlineStr">
         <is>
-          <t>Трухин написал заявление  [https://t.me/UaOnlii/47021]**о сложении депутатского мандата —  нардеп Железняк
-UPD: **Верховная Рада поддержала прекращение депутатских полномочий Трухина. "За" проголосовали 288 депутатов.</t>
+          <t>❗️**ПОГРАНИЧНИКИ ИЗБИЛИ СТУДЕНТА?
+**Вот такое видео распространяется по социальным сетям. Человек на видео утверждает, что студента иностранного вуза, ехавшего на обучение, цинично избили и унизили работники Погранслужбы Украины 🤬
+23.09.2022 года один из студентов иностранных вузов осуществлял пересечение государственной границы на КПП «Шегини». По словам парня, за несогласие в подписании отказа в пересечении границы, работники Пограничной службы начали его избивать, после чего выбросили на улицу, где продолжали наносить удары по телу:
+«начали меня под колено бить, в живот бить, по шее… подбили ноги и я потерял контроль…».
+Во время происшествия парень обратился в полицию, а сразу после него направился в Госудраственное Бюро Расследований во Львове, где получил отказ в рассмотрении своего обращения по причине военного положения. ДБР фактически отрезало возможность получения записей с камер наблюдения на КПП «Шегини».
+Студенты создали петицию [https://petition.president.gov.ua/petition/158664] чтобы достучаться до Президента:
+https://petition.president.gov.ua/petition/158664</t>
         </is>
       </c>
       <c r="G720" s="3" t="inlineStr"/>
@@ -27800,17 +27843,19 @@
       </c>
       <c r="C721" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2022-06-18</t>
         </is>
       </c>
       <c r="D721" s="3" t="n">
-        <v>25018</v>
+        <v>7750</v>
       </c>
       <c r="E721" s="3" t="inlineStr"/>
       <c r="F721" s="3" t="inlineStr">
         <is>
-          <t>**Кібератака на «Київстар» жодним чином не вплинула на роботу військових та Нацбанку**, — речник командування Сухопутних військ Володимир Фітьо. Бійці користуються іншими видами звʼязку.
-Але до Борисполя та Сум доєдналися ще Дніпро, Ірпінь і Буча. Там також через проблеми зі звʼязком не працюють системи оповіщення про повітряну тривогу.</t>
+          <t>⚡️**Херсона закликала місцевих жителів покинути Херсонську область, щоб полегшити роботу Збройним Силам України, - повідомив голова Херсонської облради Олександр Самойленко**
+За його словами, всі бачили, якою була агонія окупантів перед виходом із Бучі та Ірпеня, або як рашисти "звільняли" Маріуполь, повністю зруйнувавши 400-тисячне місто.
+"Для Херсона такий варіант звільнення неприйнятний. І це розуміють президент, головнокомандувач ЗСУ та міністр оборони — якщо знести місто, то навіщо його звільняти?" , - Відзначив Самойленко.
+**__Info Україна 🇺🇦__** [https://t.me/+SRWsVjpx0-dhYzMy]</t>
         </is>
       </c>
       <c r="G721" s="3" t="inlineStr"/>
@@ -27836,20 +27881,17 @@
       </c>
       <c r="C722" s="3" t="inlineStr">
         <is>
-          <t>2024-01-11</t>
+          <t>2024-02-03</t>
         </is>
       </c>
       <c r="D722" s="3" t="n">
-        <v>67569</v>
+        <v>69092</v>
       </c>
       <c r="E722" s="3" t="inlineStr"/>
       <c r="F722" s="3" t="inlineStr">
         <is>
-          <t>**З кінця січня боржників почнуть відключати від електрики, — ****Yasno** [https://www.epravda.com.ua/news/2024/01/11/708646/]
-Перші відключення почнуться 29 числа. Є два типи попереджень для боржників:
-📍"Перше - ми називаємо це сповіщення, коли компанія усіма методами, починаючи від СМС, від розсилок у Viber і чатах, закінчуючи дзвінками до людей, сповіщає про те, що є борг, будь ласка, сплатіть", - зазначив генеральний директор компанії.
-📍Другий тип попередження, за його словами, вже передує безпосередньо відключенню споживача.
-Сергій Коваленко наголосив, що відключення відбудеться після отримання саме попередження. "10 днів, і проводиться відключення", - сказав керівник Yasno.</t>
+          <t>**Із 9 до 15 лютого в Україні очікується аномальне тепло, стовпчики термометрів підіймуться до +20 градусів, — ****прогноз синоптиків ** [https://apostrophe.ua/ua/news/society/2024-02-02/v-fevrale-v-ukraine-vozmojna-anomalnaya-pogoda-potepleet-do-20/313276?amp]
+Після цього очікується похолодання до 0 градусів.</t>
         </is>
       </c>
       <c r="G722" s="3" t="inlineStr"/>
@@ -28561,25 +28603,22 @@
       </c>
       <c r="B741" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C741" s="3" t="inlineStr">
         <is>
-          <t>2024-02-09</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="D741" s="3" t="n">
-        <v>69530</v>
+        <v>56076</v>
       </c>
       <c r="E741" s="3" t="inlineStr"/>
       <c r="F741" s="3" t="inlineStr">
         <is>
-          <t>**У Львові відкриють перший в Україні центр рекрутингу до армії, — ****РБК** [https://www.rbc.ua/rus/news/lvovi-vidkriyut-pershiy-ukrayini-tsentr-rekrutingu-1707489268.html?utm_source=telegram&amp;utm_medium=post]
-В центрі рекрутери:
-📍надаватимуть консультацію й інформацію щодо вакансій;
-📍допоможуть пройти профорієнтаційний тест;
-📍супроводжуватимуть кандидатів на шляху до призначення на обрану посаду в армії.</t>
+          <t>❗️**Закарпаття, будьте готові до удару**: «Минулого разу після фіксації невідомих дронів — стався** приліт по ****заводу «Флекс» у Мукачево** [https://t.me/times_ukraina/54347]», [https://t.me/times_ukraina/54347] — голова Центру радіотехнологій **Сергій «Флеш»**.
+«Улітку тут якраз і літали незрозумілі БПЛА, **але нам ніхто не повірив: які дрони над ****Закарпаттям?** [https://t.me/+S3OIZ_MWw0Q0ZGZi] Тепер Президент сьогодні оголосив офіційно, що там зʼявилися угорські БПЛА. [https://t.me/times_ukraina/56059] **Випадковостей немає**», — пише він.</t>
         </is>
       </c>
       <c r="G741" s="3" t="inlineStr"/>
@@ -28961,18 +29000,17 @@
       </c>
       <c r="C752" s="3" t="inlineStr">
         <is>
-          <t>2023-12-23</t>
+          <t>2023-01-11</t>
         </is>
       </c>
       <c r="D752" s="3" t="n">
-        <v>25459</v>
+        <v>12400</v>
       </c>
       <c r="E752" s="3" t="inlineStr"/>
       <c r="F752" s="3" t="inlineStr">
         <is>
-          <t>**Естонія може почати шукати і депортувати українських чоловіків призовного віку**, — голова МВС Лаури Ляенеметс.
-У найближчий час міністр запропонує письмову угоду між країнами. Наразі екстрадиція можлива, якщо людина була притягнута до кримінальні відповідальності. 
-«Ми знаємо, де ці люди перебувають, чим займаються. Більшість ходять на роботу, мають місце проживання в країні», — додав посадовець. Наразі в Естонії мешкає ~7500 українців, які підлягають мобілізації.</t>
+          <t>**Мемопад** [https://t.me/c/1431180517/12187] на тему сьогоднішньої погоди в рф. В Новосибірську вночі термометр центрального вокзалу показав -51°C, – РИА «Новости». Синоптики говорять, що було холодно, але не настільки «всього -31°C». В Якутську -55°C, у автівок лопаються шини. В Дагестані через потужний снігопад 45 000 мешканців залишилось без світла. 
+__Десь ридає «заморожена» Європа.__</t>
         </is>
       </c>
       <c r="G752" s="3" t="inlineStr"/>
@@ -29074,17 +29112,18 @@
       </c>
       <c r="C755" s="3" t="inlineStr">
         <is>
-          <t>2024-05-18</t>
+          <t>2024-03-20</t>
         </is>
       </c>
       <c r="D755" s="3" t="n">
-        <v>33615</v>
+        <v>30465</v>
       </c>
       <c r="E755" s="3" t="inlineStr"/>
       <c r="F755" s="3" t="inlineStr">
         <is>
-          <t>⚡️**Два тижні тому на ****Сумщині** [https://t.me/+KhEqiyRMYWU0MzQy]** завершувалося будівництво фортифікаційних споруд, тому на вʼїзді можна побачити звалені «зуби дракона»,** — голова ОВА Володимир Артюх пояснив гори бетонних трикутників, фотопруфи яких вчора розлетілися мережею. 
-**Невикористані «зуби» помітили у Великописарівській громаді. **За даними «Кордон.Медіа», 849 млн грн виділили на оборону області у 2023-2024 рр + 1,3 млрд грн у лютому цього року з резервного фонду держбюджету для зміцнення регіону.</t>
+          <t>**⚡️Жива, здорова, купує мʼясо: британець Нельсон Сільва стояв у черзі в магазині біля ****принцеси Кейт** [https://t.me/c/1431180517/30006]** ****Міддлтон, яка від початку року не зʼявлялась на публіці** [https://t.me/c/1431180517/30006], [https://t.me/c/1431180517/30006] — The Sun.
+Чоловік розповідає, що зустріч сталася у Віндзорі, де вона шопилась на фермерському ринку. Народний папарацці навіть встиг зробити відеопруф. Але прискіпливі фани королівської родини вважають, що це двійник, бо дружина принца Уельського не така висока. Також є версія, що кадри взагалі зняті у грудні, адже на фоні видніються різдвяні прикраси.
+Водночас приватна лондонська клініка, де у січні прооперували Кетрін, потрапила у скандал. Один з працівників медзакладу намагався отримати доступ до її особистих даних. Триває розслідування, — Daily Mail.</t>
         </is>
       </c>
       <c r="G755" s="3" t="inlineStr"/>
@@ -29721,18 +29760,17 @@
       </c>
       <c r="C772" s="3" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="D772" s="3" t="n">
-        <v>77922</v>
+        <v>82119</v>
       </c>
       <c r="E772" s="3" t="inlineStr"/>
       <c r="F772" s="3" t="inlineStr">
         <is>
-          <t>**❗️Працівників аграрного сектору бронюватимуть від мобілізації на рік з метою створення умов безпечного збору урожаю, — ****в.о. міністра аграрної політики Висоцький** [https://suspilne.media/odesa/769219-pracivnikiv-agrosektoru-na-rik-bronuvatimut-vid-mobilizacii-ministr/]
-Він зазначив, що загальна норма бронювання — до 50%, проте за певними професіями можна подати клопотання з обґрунтуванням збільшення цієї кількості. 
-"Перше — це автоматично пролонговані існуючі бронювання на три місяці без необхідності подавання жодного пакета документів. Друге — подальше бронювання буде надаватись на 12 місяців, до цього було шість. Третє, по певних професіях, наприклад, трактористи, агрономи, ветеринарні лікарі, є можливість бронювати ту кількість працівників, яка критично необхідна, при цьому отримуючи погодження від військових", — зазначив Тарас Висоцький.</t>
+          <t>**Гарріс обрала губернатора Міннесоти Тіма Волца на роль кандидата у віцепрезиденти**,** — ****CNN ** [https://www.cnn.com/politics/live-news/kamala-harris-trump-election-08-06-24#h_a1cb3a353c1e0655524a827af0197796]
+Він є жорстким антитрампістом та називав Трампа і Венса — «чудилами». Також він виступає за посилення допомоги Україні.</t>
         </is>
       </c>
       <c r="G772" s="3" t="inlineStr"/>
@@ -29917,17 +29955,17 @@
       </c>
       <c r="C777" s="3" t="inlineStr">
         <is>
-          <t>2023-04-25</t>
+          <t>2022-12-30</t>
         </is>
       </c>
       <c r="D777" s="3" t="n">
-        <v>16174</v>
+        <v>11857</v>
       </c>
       <c r="E777" s="3" t="inlineStr"/>
       <c r="F777" s="3" t="inlineStr">
         <is>
-          <t>Важливість Бахмуту [https://t.me/c/1431180517/16128] в тому, що ЗСУ не дають ворогу збільшувати фронт і знищують найкращі підрозділи та техніку окупантів, – генерал-полковник Олександр Сирський.
-__На відео 79-а бригада ДШВ підриває росіян на Донецькому напрямку.</t>
+          <t>Ворог може кинути на Київ 30 000 солдатів, – Генштаб.
+Зараз угрупування росвійськ у Білорусі складає близько 20 000 осіб. Для наступу на Київ у лютому рф задіяла 45 500.</t>
         </is>
       </c>
       <c r="G777" s="3" t="inlineStr"/>
@@ -29948,22 +29986,22 @@
       </c>
       <c r="B778" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C778" s="3" t="inlineStr">
         <is>
-          <t>2022-02-04</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="D778" s="3" t="n">
-        <v>750</v>
+        <v>14818</v>
       </c>
       <c r="E778" s="3" t="inlineStr"/>
       <c r="F778" s="3" t="inlineStr">
         <is>
-          <t>**Поки чимало країн ЄС та Штати активно передають Україні озброєння та військову допомогу, Німеччина досі не надала підтвердження про передання обіцяних військових захисних **шоломів [https://24tv.ua/nimechchina-dosi-ofitsiyno-ne-pidtverdila-nadannya-ukrayini-boday_n1859237].
-Вже місяць не п’ю німецьке пиво та й не збираюсь, це мої санкції до Німеччини</t>
+          <t>**❗️Мобілізацію буде посилено.**
+«Зараз додаткова потреба в ресурсах знадобиться і через втрату особового складу, і через необхідність сформувати нові з'єднання, бригади» – вважає [https://tsn.ua/ukrayina/lyudi-vtomleni-chomu-na-fronti-problemi-z-rotaciyeyu-i-yak-yih-virishiti-poyasnennya-nardepa-2437198.html] член комітету Верховної Ради з питань нацбезпеки Сергій Рахманін.</t>
         </is>
       </c>
       <c r="G778" s="3" t="inlineStr"/>
@@ -29984,22 +30022,22 @@
       </c>
       <c r="B779" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C779" s="3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2022-01-24</t>
         </is>
       </c>
       <c r="D779" s="3" t="n">
-        <v>33784</v>
+        <v>444</v>
       </c>
       <c r="E779" s="3" t="inlineStr"/>
       <c r="F779" s="3" t="inlineStr">
         <is>
-          <t>**⚡ССО знищили пів дивізіону «Бук»: **три ЗРК було уражено наприкінці квітня-початку травня, четвертий — воїни мінуснули днями,** **— пресслужба Сил спеціальних операцій. 
-Оборонці поцілили у російське залізяччя ударним дроном новітньої розробки.</t>
+          <t>⚡️Зеленский созывает заседание СНБО. Начало заседания запланировано на 17:00
+источник: pravdaua [https://www.pravda.com.ua/rus/news/2022/01/24/7321488/]</t>
         </is>
       </c>
       <c r="G779" s="3" t="inlineStr"/>
@@ -30064,18 +30102,17 @@
       </c>
       <c r="C781" s="3" t="inlineStr">
         <is>
-          <t>2023-02-28</t>
+          <t>2023-02-24</t>
         </is>
       </c>
       <c r="D781" s="3" t="n">
-        <v>27209</v>
+        <v>27084</v>
       </c>
       <c r="E781" s="3" t="inlineStr"/>
       <c r="F781" s="3" t="inlineStr">
         <is>
-          <t>**Німеччина передасть Україні дві системи ППО Skynex**, – генеральний директор німецького концерну Rheinmetall AG.
-Дві системи Skynex, які будуть виготовлені його компанією, були замовлені німецьким урядом. Їх вартість становить 212 млн доларів.
-👹👹👹</t>
+          <t>**Країни G7 погодили виділення $39 млрд як фінансової допомоги для підтримки України**, — канцлер ФРН Шольц.
+🫡</t>
         </is>
       </c>
       <c r="G781" s="3" t="inlineStr"/>
@@ -30251,18 +30288,18 @@
       </c>
       <c r="C786" s="3" t="inlineStr">
         <is>
-          <t>2023-02-02</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="D786" s="3" t="n">
-        <v>46077</v>
+        <v>77922</v>
       </c>
       <c r="E786" s="3" t="inlineStr"/>
       <c r="F786" s="3" t="inlineStr">
         <is>
-          <t>**Американские военные последние несколько дней отслеживают предположительно китайский разведывательный воздушный шар над северной частью США, — СМИ
-**Шар в небе над США не угрожает людям и летит выше уровня коммерческих самолетов заявили в Пентагоне. 
-К - креативно</t>
+          <t>**❗️Працівників аграрного сектору бронюватимуть від мобілізації на рік з метою створення умов безпечного збору урожаю, — ****в.о. міністра аграрної політики Висоцький** [https://suspilne.media/odesa/769219-pracivnikiv-agrosektoru-na-rik-bronuvatimut-vid-mobilizacii-ministr/]
+Він зазначив, що загальна норма бронювання — до 50%, проте за певними професіями можна подати клопотання з обґрунтуванням збільшення цієї кількості. 
+"Перше — це автоматично пролонговані існуючі бронювання на три місяці без необхідності подавання жодного пакета документів. Друге — подальше бронювання буде надаватись на 12 місяців, до цього було шість. Третє, по певних професіях, наприклад, трактористи, агрономи, ветеринарні лікарі, є можливість бронювати ту кількість працівників, яка критично необхідна, при цьому отримуючи погодження від військових", — зазначив Тарас Висоцький.</t>
         </is>
       </c>
       <c r="G786" s="3" t="inlineStr"/>
@@ -30405,22 +30442,22 @@
       </c>
       <c r="C790" s="3" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2021-09-24</t>
         </is>
       </c>
       <c r="D790" s="3" t="n">
-        <v>27723</v>
+        <v>5241</v>
       </c>
       <c r="E790" s="3" t="inlineStr"/>
       <c r="F790" s="3" t="inlineStr">
         <is>
-          <t>💙 Сон вже ходить коло вікон. Але перш ніж лягти спати, перегляньте відеопідсумки дня. Нам є що вам розповісти. 
-• Обстріл Харківщини: [https://t.me/c/1431180517/27675] 4 поранених. 
-• «Ивановец» пішов на дно: на борту катера було ~40 моряків. [https://t.me/c/1431180517/27703] 
-• €50 млрд від ЄС: перший транш допомоги отримаємо за місяць. [https://t.me/c/1431180517/27702] 
-• Дубінський лишається в СІЗО: суд не змінив запобіжний захід. [https://t.me/c/1431180517/27706] 
-• Статки Умєрова: [https://t.me/c/1431180517/27693] міністр оборони у 2023-му заробив 5,5 млн грн. 
-• Рекорд Магучіх: стрибнула на 2,04 м.  [https://t.me/c/1431180517/27699]</t>
+          <t>**Нардепа будут судить за неуплату налогов
+**Государственное бюро расследований (ГБР) передает в суд дело против депутата Виктора Мялика.
+Он обвиняется в уклонении от уплаты налогов на 97 млн гривен.
+Доходы от продажи квартир и нежилых помещений нардеп декларировал, как доходы физлица от продажи собственного имущества, а не от предпринимательской деятельности. 
+При этом применялась ставка налога в размере 5% вместо необходимых 18%.
+"__Предварительно, по данным экспертизы, таким образом народный депутат уклонился от уплаты налога на доходы физических лиц и налога на добавленную стоимость на общую сумму более 97 млн   грн__", - пояснила генпрокурор.
+"По делу Мялика завершено досудебное расследование и ознакомление с материалами. Обвинительный акт передается в суд", - сообщил он.</t>
         </is>
       </c>
       <c r="G790" s="3" t="inlineStr"/>
@@ -31162,18 +31199,23 @@
       </c>
       <c r="C810" s="3" t="inlineStr">
         <is>
-          <t>2022-06-01</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="D810" s="3" t="n">
-        <v>30099</v>
+        <v>57911</v>
       </c>
       <c r="E810" s="3" t="inlineStr"/>
       <c r="F810" s="3" t="inlineStr">
         <is>
-          <t>**На брифинге Госсекретарь США Энтони Блинкен объявил о новой военной помощи Украине на $700 млн
-**В новый пакет военной помощи вошли, в частности, ракетные системы большой дальности, а также, по данным американских СМИ, другое крупнокалиберное оружие.
-При этом, как заявил Блинкен, системы большой дальности Украина обязалась не использовать для ударов по территории России.</t>
+          <t>**З початку війни ЗСУ збили більше 3500 повітряних цілей, — Ігнат
+**Серед них: 
+📍1200 крилатих, 
+📍24 балістичні ракети 
+📍13 гіперзвукових «Кинджалів»
+📍більше 20 «Іскандерів» та С-400.
+На сьогодні українська система протиповітряної оборони є однією із найунікальніших в світі – змішана, оскільки в нас зосереджені засоби ППО від різних виробників, різного типу та від різних постачальників. Також і досі є радянські зразки, котрі теж збивають ворожі ракети.
+Стосовно статистики збиття крилатих ракет, то, за словами речника Повітряних сил ЗСУ, нині ППО збиває 70-80% ракет. Аналогічна ситуація по дронах.</t>
         </is>
       </c>
       <c r="G810" s="3" t="inlineStr"/>
@@ -32491,23 +32533,23 @@
       </c>
       <c r="B845" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C845" s="3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="D845" s="3" t="n">
-        <v>38991</v>
+        <v>80102</v>
       </c>
       <c r="E845" s="3" t="inlineStr"/>
       <c r="F845" s="3" t="inlineStr">
         <is>
-          <t>⚡ **Ого! На ****Полтавщині** [https://t.me/+lMD1Y11V9TkxM2Yy]** сьогодні помітили смерч**, — очевидці.
-Місцеві кажуть, що міні-торнадо гуляло полем, згодом пройшлось по дорозі і вже з меншою силою почало кружляти над іншою ділянкою.
-Метеорологи зазначають, пилові вихори виникають влітку, коли сонце досить добре прогріває земну поверхню. Саме за таких умов утворюються висхідні потоки повітря.</t>
+          <t>**У Запоріжжі чоловік звернувся до поліції, через те, що повія відмовила йому в сексі, — ****ТСН** [https://tsn.ua/amp/ukrayina/u-zaporizhzhi-cholovik-zvernuvsya-do-policiyi-bo-zhinka-vidmovila-yomu-v-seksi-2617308.html]
+Жінка розмістила  оголошення про надання інтимних послуг, взяла у чоловіка кошти, і відмовилась спати з ним. Чоловік виграв суд, а жінку засудили до 200 годин громадських робіт.
+Ситуація..</t>
         </is>
       </c>
       <c r="G845" s="3" t="inlineStr"/>
@@ -32569,20 +32611,18 @@
       </c>
       <c r="C847" s="3" t="inlineStr">
         <is>
-          <t>2021-01-13</t>
+          <t>2021-10-24</t>
         </is>
       </c>
       <c r="D847" s="3" t="n">
-        <v>2817</v>
+        <v>5570</v>
       </c>
       <c r="E847" s="3" t="inlineStr"/>
       <c r="F847" s="3" t="inlineStr">
         <is>
-          <t>🇺🇦Info Украuна [https://t.me/ua_info_news]**
-Facebook удалила десятки связанных с Евросолидарностью аккаунтов
-**Администрация Facebook сообщила, что в декабре 2020 года удалила десятки профилей, связанных с партией Европейская солидарность и общественной организацией Справа громад, а также общественной организацией Антикоррупционный блокпост. 
-"Они распространяли контент с официальных страниц политических партий и политиков, ставили лайки и комментировали под текстами других людей, чтобы показать их (партии и политиков) более популярными, чем они есть на самом деле. Эта сеть размещала сообщение на украинском и русском языках о новостях и политике в Украине, включая одобрительные комментарии о Европейской солидарности и ее кандидатах, общественной организации Справа громад, экс-президенте Порошенко и с критикой президента Зеленского. Этот контент был оценен, как фальшивый", - говорится в сообщении Facebook.
-В партии Европейская солидарность и указанных общественных организациях пока не комментировали информацию Facebook.</t>
+          <t>Владимир Александрович прокомментировал расследование по поводу своих оффшоров. Спустя две недели после показа фильма. 
+Говорит, сюжет так себе…
+Администрация Президента [https://t.me/AP_UA]</t>
         </is>
       </c>
       <c r="G847" s="3" t="inlineStr"/>
@@ -32787,16 +32827,16 @@
       </c>
       <c r="B853" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C853" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2023-03-29</t>
         </is>
       </c>
       <c r="D853" s="3" t="n">
-        <v>87812</v>
+        <v>15279</v>
       </c>
       <c r="E853" s="3" t="inlineStr">
         <is>
@@ -32805,8 +32845,7 @@
       </c>
       <c r="F853" s="3" t="inlineStr">
         <is>
-          <t>**Якщо б Україні запропонували членство в НАТО в обмін на окуповані території, "я б точно зробив дуже погані речі", — Умєров**
-👀</t>
+          <t>Долетить до бункера. В Україні з‘являться ударні БПЛА з дальністю 3000 км, – секретар РНБО Олексій Данілов. Це будуть «десятки нових моделей та тисячі самих дронів».</t>
         </is>
       </c>
       <c r="G853" s="3" t="inlineStr"/>
@@ -32909,17 +32948,17 @@
       </c>
       <c r="C856" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2022-02-14</t>
         </is>
       </c>
       <c r="D856" s="3" t="n">
-        <v>54408</v>
+        <v>1028</v>
       </c>
       <c r="E856" s="3" t="inlineStr"/>
       <c r="F856" s="3" t="inlineStr">
         <is>
-          <t>🇪🇺 ЄС найближчим часом затвердить 19-й пакет санкцій проти РФ, а також обговорить, як можна використати найкращим чином російські заморожені активи для військової підтримки України та її відбудови, — президентка Єврокомісії на нічні удари по Києву.
-РФ вночі завдала цілеспрямованого удару по будинку, що розташований поруч з представництвом Євросоюзу в Україні, додала посол ЄС у Києві.</t>
+          <t>Секретарь СНБО Украины Данилов заявил, что **не видит предпосылок «вторжения» РФ в Украину в ближайшие дни.** 
+«Ситуация находится абсолютно под контролем. Мы на сегодняшний день не видим предпосылок, что широкомасштабное вторжение Российской Федерации может происходить 16-го или 17-го числа», — заявил Данилов.</t>
         </is>
       </c>
       <c r="G856" s="3" t="inlineStr"/>
@@ -32940,35 +32979,24 @@
       </c>
       <c r="B857" s="3" t="inlineStr">
         <is>
-          <t>vanek_nikolaev</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C857" s="3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-08-14</t>
         </is>
       </c>
       <c r="D857" s="3" t="n">
-        <v>39929</v>
+        <v>4757</v>
       </c>
       <c r="E857" s="3" t="inlineStr"/>
       <c r="F857" s="3" t="inlineStr">
         <is>
-          <t>**__Птахами СБС та ГУР знищено 4 борти та базу ППП тяжких БПЛА «Оріон», літак АН-72П та РЛС «Меч» на АЕ Кіровське у Криму.__**
-**В ніч на 2 квітня 2026 року Птахами 1 оц СБС та 9 деп ГУР нанесено візит ввічливості на базу та пункт передполітної підготовки новітніх та високовартісних ударно-розвідувальних БПЛА «Оріон».**
-**•Оріон- дрон, здатний 24 години перебувати у повітрі на глибині до 250-300км, розвідує та несе до 250 кг озброєння (ракети або бомби) на висоті до 7,5 км. **
-**Це лігво знищене вщент на АЕ Кіровське у р-ні нп Красносільське, АР Крим.**
-**🔥🔥🔥🔥Підтверджено знищення 4 одиниць БПЛА «Оріон».**
-**Там-же виявлено та знищено транспортний літак-доходягу Ан-72П 🔥та совкову рухому двокоординатну радіолокаційну станцію кругового огляду П-37 «Меч»🔥**
-**Ураження здійснено засобами middle strike FP-2 українського в-ва з бч 60-100кг.**
-**Далі буде…**
-**Слідкувати результати СБС наживо:**
-**Онлайн-табло СБС «ПІДРАХУЙКА»**
-**https://sbs-group.army/**
-**МАДЯР🇺🇦**
-**02.04.26**
-**🔵****МАДЯР** [https://t.me/robert_magyar]**🎞****МАДЯР** [https://youtube.com/@MAGYARBIRDS]**👥****МАДЯР** [https://www.facebook.com/Brovdi.Art]** ****👥****RB** [https://www.facebook.com/profile.php?id=100004808732741]**📷****МАДЯР** [https://www.instagram.com/robert_madyar?igsh=MXYzZHdtMmNtMWd1eg==]** ****🇺🇦****СБС** [https://usforces.army/?utm_source=tg_magyar#application-form]
-**онлайн«ПІДРАХУЙКА»СБС** [https://sbs-group.army/?utm_source=t]</t>
+          <t>​​ [https://telegra.ph/file/2c5432647bf7500fda75f.jpg]Младшие акционеры Globalmoney Стрелковский и Мищенко в истерике от страха, что из-за скандала [https://news.obozrevatel.com/society/v-kieve-aktivistyi-prizvali-nbu-lishit-litsenzii-platezhnuyu-sistemu-globalmoney.htm] вокруг их сотрудничества [https://apostrophe.ua/ua/news/business/2021-07-28/globalmoney-udalila-svoyu-stranicu-vkonakte-posle-oglaski-v-smi/239633] с РФ и ЛДНР [https://golos.ua/news/ohota-na-vedm-v-lnr-vstupylys-za-globalmoney] им могут аннулировать лицензию. Ребята начали заливать баблом украинские СМИ, и за любой прайс снимать информацию о том, что Globalmoney занимается рублевым обналом своих кошельков в Луганске и работает с российскими банками и платежными системами. И за в 10-20 раз большую цену у изданий покупается «блок» по публикациям работы «глобалов» с ЛДНР и РФ по акции против «глобалов» ветеранских организаций, которая прошла сегодня под НБУ. По нашим данным, в блоки уже влито более 20 млн грн.
+В пакет, который Globalmoney оплачивает редакциям, входит постановка палевного пресс-релиза [https://lb.ua/economics/2021/08/12/491513_globalmoney_zaklikaie_zmi.html] «глобалов», в котором они призывают СМИ «не фейковать».  Изданиям, которые не постыдились поставить (за бабки, конечно же) этот релиз, нужно понимать, что они публично выставили у себя на сайте чек «уплочено» для Юры Енакиевского и экс-министра Януковича Колобова, старших акционеров Globalmoney.
+А сам этот «антифейковый» релиз по сути - явка с повинной. Поскольку никаких пояснений относительно обнала кошелков Глобал24 через сепарский «Первый коммерческий центр» в Луганске, совместных проектов с ВТБ после введения санкций СНБО, страницы Глобал24 в «Вконтакте» и рекламы работы с «любым банком РФ» - «глобалы» так и не дали. И не дадут.
+И главный вопрос – откуда у полумертвой системы, которая не в состоянии даже обновить свой кошелек, бабки на такие операционные затраты – 20 млн грн на «работу со СМИ»? Причем кэше, собранном за пару дней? Ответ очень простой – это личный ресурс старших акционеров, которым конкретно вставили российские кураторы. Потому что после запрета российских банков в Украине – один из последних работающих финансовых механизмов, обслуживающих подсанкционный российский бизнес в Украине.</t>
         </is>
       </c>
       <c r="G857" s="3" t="inlineStr"/>
@@ -33024,21 +33052,22 @@
       </c>
       <c r="B859" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C859" s="3" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2024-04-21</t>
         </is>
       </c>
       <c r="D859" s="3" t="n">
-        <v>674</v>
+        <v>32312</v>
       </c>
       <c r="E859" s="3" t="inlineStr"/>
       <c r="F859" s="3" t="inlineStr">
         <is>
-          <t>⚡️Создавая угрозы для России, Украина **создаёт их и для себя** — Путин</t>
+          <t>Україною вирує негода: у Львові [https://t.me/+OvDtK0UtMjlkMWNi] випав величезний град, — місцеві тг-канали.
+У Києві [https://t.me/+0Evrr_TToPZmYzli] сильний вітер повалив дерева: гілки попадали на автівки та дороги. У Одесі [https://t.me/+IVEQ--aykm0yNjdi] також понівечені машини.</t>
         </is>
       </c>
       <c r="G859" s="3" t="inlineStr"/>
@@ -33477,11 +33506,11 @@
       </c>
       <c r="C871" s="3" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="D871" s="3" t="n">
-        <v>19665</v>
+        <v>22397</v>
       </c>
       <c r="E871" s="3" t="inlineStr">
         <is>
@@ -33490,8 +33519,8 @@
       </c>
       <c r="F871" s="3" t="inlineStr">
         <is>
-          <t>Сьогодні росіяни били «Кинджалами», «Калібрами» по нашій «Мотор Січі», Хмельниччині. Частину ракет збили, — президент Володимир Зеленський. 
-Місцева влада Запоріжжя повідомила, що вибухи лунали у передмісті. Жертв та постраждалих поки немає. Наслідки руйнувань уточнюються.</t>
+          <t>Україна готує термінову евакуацію своїх громадян із Сектора Газа, — «Суспільне» посилаючись на посла Євгена Корнійчука. Планують все зробити до 12 жовтня через єдиний відкритий прикордонний пункт: наразі формують списки. Вже відомо про 150 співгромадян, які не можуть виїхати.
+Українським дипломатам також вдалось розшукати 7 українців на півдні Ізраїлю, які вважались зниклими.</t>
         </is>
       </c>
       <c r="G871" s="3" t="inlineStr"/>
@@ -33967,19 +33996,18 @@
       </c>
       <c r="C884" s="3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="D884" s="3" t="n">
-        <v>52954</v>
+        <v>46077</v>
       </c>
       <c r="E884" s="3" t="inlineStr"/>
       <c r="F884" s="3" t="inlineStr">
         <is>
-          <t>**Мер Києва Кличко та міністр Камишін другий день перевіряють стан укриттів, з військової адміністрації - нікого 
-**Другий день ходимо з міністром Олександром Камишіним оглядаємо укриття. Сьогодні - в Голосіївському районі. В складі групи знову, на жаль, немає представників Київської міської військової адміністрації.  Питання стану укриттів – це зона відповідальності саме військових адміністрацій та голів районів Києва, - повідомив [https://t.me/vitaliy_klitschko/2070] мер Києва Віталій Кличко. 
-Як відомо, у 2022-2023 р.р. з міського бюджету на облаштування укриттів районам було виділено 1, 2 млрд гривень. Наразі прокуратура та поліція Києва розслідують розкрадання грошей на ремонті укриттів, до яких можуть бути причетні голови райдержадміністрацій (РДА) Києва. Як повідомлялось раніше, 9 з 10 голів РДА Києва - представники партії "Слуга народу".
-Також, стало відомо, що 3 червня відбулися перевірки стану укриттів Оболонського району Києва за участі Олександра Камишіна та Віталія Кличка. Представників КМВА під час перевірки також не було.</t>
+          <t>**Американские военные последние несколько дней отслеживают предположительно китайский разведывательный воздушный шар над северной частью США, — СМИ
+**Шар в небе над США не угрожает людям и летит выше уровня коммерческих самолетов заявили в Пентагоне. 
+К - креативно</t>
         </is>
       </c>
       <c r="G884" s="3" t="inlineStr"/>
@@ -34423,17 +34451,19 @@
       </c>
       <c r="C896" s="3" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021-02-23</t>
         </is>
       </c>
       <c r="D896" s="3" t="n">
-        <v>4651</v>
+        <v>3090</v>
       </c>
       <c r="E896" s="3" t="inlineStr"/>
       <c r="F896" s="3" t="inlineStr">
         <is>
-          <t>**Зеленского заметили в магазине покупающим вино
-**Очевидцы сообщают, что президент зашел в Le Silpo на Бессарабке за продуктами, рядом была охрана, а сам Зеленский купил 3 бутылки вина.</t>
+          <t>Кулеба заявил о наращивании ядерного потенциала РФ в Крыму
+По словам главы МИД, РФ продолжает наращивать ядерный потенциал на территории оккупированного Крыма. Это подрывает безъядерный статус полуострова и грозит мировой безопасности.
+Он также заявил, что агрессию РФ по отношению к Украине можно рассматривать как угрозу ее военной экспансии Европы.
+🇺🇦 Info Украuна [https://t.me/joinchat/VU4U5Vm2-Lh8tVC2]</t>
         </is>
       </c>
       <c r="G896" s="3" t="inlineStr"/>
@@ -34494,21 +34524,22 @@
       </c>
       <c r="B898" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C898" s="3" t="inlineStr">
         <is>
-          <t>2024-04-26</t>
+          <t>2022-05-13</t>
         </is>
       </c>
       <c r="D898" s="3" t="n">
-        <v>32570</v>
+        <v>11460</v>
       </c>
       <c r="E898" s="3" t="inlineStr"/>
       <c r="F898" s="3" t="inlineStr">
         <is>
-          <t>⏺КР на Хмельниччині у західному напрямку, — ПС.</t>
+          <t>**Глава МЗС Британії анонсувала зростання поставок зброї Україні та посилення санкцій проти Росії**, — Reuters
+👹👹👹</t>
         </is>
       </c>
       <c r="G898" s="3" t="inlineStr"/>
@@ -34945,16 +34976,16 @@
       </c>
       <c r="B910" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C910" s="3" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="D910" s="3" t="n">
-        <v>1934</v>
+        <v>81462</v>
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
@@ -34963,11 +34994,7 @@
       </c>
       <c r="F910" s="3" t="inlineStr">
         <is>
-          <t>Japan Airlines перестанет использовать фразу "ladies and gentlemen"
-**Фразу “дамы и господа” JAL заменит на слово “все”
-“Бортпроводники, например, будут говорить - “Добрый день всем” или “Внимание, всем пассажирам””, - объясняют представители компании.
-В формулировки на японском языке изменения не внесут, поскольку в них уже используются гендерно-нейтральные термины: okyaku-sama, что означает “клиенты”, mina-sama - “все” и ryokaku no mina-sama - “все пассажиры”.
-JAL объяснила, что изменение вносится “для того, чтобы представителям сексуальных меньшинств не было неловко”.</t>
+          <t>**Терпіння, підтримка і дипломатичний тиск — це три фактори справедливого припинення війни, — Зеленський**</t>
         </is>
       </c>
       <c r="G910" s="3" t="inlineStr"/>
@@ -35285,21 +35312,23 @@
       </c>
       <c r="B919" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C919" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="D919" s="3" t="n">
-        <v>120201</v>
+        <v>32870</v>
       </c>
       <c r="E919" s="3" t="inlineStr"/>
       <c r="F919" s="3" t="inlineStr">
         <is>
-          <t>❗️**Ракети на Полтавщині курсом на Київщину, — ПС**</t>
+          <t>**⚡️PornHub зареєструвався платником ПДВ в Україні, **—** **голова** **парламентського фінкомітету Данило Гетманцев.
+Компанія приєналася до іншого сервісу для дорослих OnlyFans, який вже поповнив наш бюджет на $0,7 млн за перший квартал. 
+Нагадаємо, у грудні 2023 року PornHub оштрафували на $5000+ [https://t.me/c/1431180517/25246] за ухилення від сплати податків в Україні. Відомо, що серед споживачів контенту на сайті наша країна займає 14 місце у світі.</t>
         </is>
       </c>
       <c r="G919" s="3" t="inlineStr"/>
@@ -35560,11 +35589,11 @@
       </c>
       <c r="C926" s="3" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-05-17</t>
         </is>
       </c>
       <c r="D926" s="3" t="n">
-        <v>21626</v>
+        <v>16893</v>
       </c>
       <c r="E926" s="3" t="inlineStr">
         <is>
@@ -35573,19 +35602,13 @@
       </c>
       <c r="F926" s="3" t="inlineStr">
         <is>
-          <t>⚡️**Ворог почав знову бити по енергосистемі і є ризики, що будуть проблеми зі світлом, тому збережіть свою електроніку та залишайтесь завжди зі світлом!
-**Прямий постачальник
-тел. 0976611613
-Телеграм: https://t.me/product_energy
-В наявності:
-**Генератори інверторні** (пряма синусоїда)
-• 220V 50Hz 2.2-2.4kw 97.7cc- 19000грн;
-• 220V 50Hz 2.5-2.8kw 120сс- 20900грн.
-**Перетворювачі Інверторні** (пряма синусоїда)
-• 12v-230v 1000w - 5300грн;
-• 12v-230v 2000w - 8400грн;
-• 12v-230v 3000w - 10600грн.
-🎁Діють знижки та розігруються подарунки, підпишіться та поділіться з друзями.</t>
+          <t>💛 Особисте від редакції. Найдорожчі наші читачі, вас щодня більшає, а нас це дуже тішить. Давайте знайомитись 👋
+Times of Ukraine – це найважливіші, актуальні, цікаві та деколи кумедні новини України та світу. Якісно, швидко, перевірено. Ми – ЗМІ, створене професійними незалежними журналістами. 
+__Нам набридли фейки, треш, дописи російською в українських пабліках. Хочемо підняти якість новин в телеграмі на новий рівень. Та додати краплю інтелектуального гумору і корисностей.
+__Наша команда щодня (а іноді й ночами) працює для вас. Ми набираємо обертів. 😉
+Тож, надсилайте новини, спілкуйтесь у чаті [https://t.me/+P45BvBhjmTw3NGFi] (там весело, цікаво і гаряче), ставтесь з розумінням до реклами (вона дає нам можливість розвиватися), критикуйте та рекомендуйте. 
+Дякуємо за довіру. Будемо дружити 🍀
+• Чат [https://t.me/+P45BvBhjmTw3NGFi] • Головний канал [https://t.me/+bQKdtczFEn40YTE6] • Для рекламодавців [https://t.me/tu_reklama] • Відправити новину [https://t.me/TUnewsBot]</t>
         </is>
       </c>
       <c r="G926" s="3" t="inlineStr"/>
@@ -35645,23 +35668,28 @@
       </c>
       <c r="B928" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>vanek_nikolaev</t>
         </is>
       </c>
       <c r="C928" s="3" t="inlineStr">
         <is>
-          <t>2022-12-02</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="D928" s="3" t="n">
-        <v>4263</v>
+        <v>8241</v>
       </c>
       <c r="E928" s="3" t="inlineStr"/>
       <c r="F928" s="3" t="inlineStr">
         <is>
-          <t>**Росіяни планували захопити Україну за 10 днів**, але не вийшло через надмірну секретність – RUSI [https://www.pravda.com.ua/news/2022/12/2/7378937/]
-На думку експертів, план Росії полягав у тому, щоб вторгнутися в Україну протягом 10 днів, а потім окупувати країну та здійснити анексію до серпня 2022 року.
-Крім того, під Києвом росіяни досягли переваги у співвідношенні сил - 12:1.</t>
+          <t>Створили штаб для вирішення проблем херсонців, які потребують допомоги внаслідок окупації регіону. 
+Задачі штабу - це виявлення та аналіз проблем мешканців Херсона, які виникли в окупації і можуть з'явитися в процесі звільнення міста, збір інформації про критичні потреби мешканців, які знаходяться у місті, забезпечення оперативної допомоги щодо вирішення нагальних питань.
+Юридична допомога, консультації загального характеру, допомога соціально-вразливим верствам населення.  Експертиза пошкодженого майна для відшкодування державою її вартості. 
+Допомога у вирішенні інших потреб, які виникли у херсонців, внаслідок окупації регіону російською федерацією. 
+Для того, аби записатись на отримання допомоги при деокупації міста, заповніть, будь-ласка, форму, де необхідно вказати, яку саме допомогу ви потребуєте. Автомобіль не подаруємо, але, якщо це в межах наших сил, обов’язково допоможемо. 
+https://forms.gle/ZovhAihBeeocVQXS9
+Для отримання консультації щодо юридичних та інших питань, пишіть мені в особисті повідомлення https://t.me/Roman_golovnya.
+Раді вітати всіх, хто має бажання долучитися до нашої команди і зможе допомагати безпосередньо у Херсоні і поза його межами, заповніть, будь-ласка, цю форму https://forms.gle/KyznV73fNoLDsDvs7</t>
         </is>
       </c>
       <c r="G928" s="3" t="inlineStr"/>
@@ -36172,22 +36200,24 @@
       </c>
       <c r="B942" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C942" s="3" t="inlineStr">
         <is>
-          <t>2023-12-05</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="D942" s="3" t="n">
-        <v>16084</v>
+        <v>54924</v>
       </c>
       <c r="E942" s="3" t="inlineStr"/>
       <c r="F942" s="3" t="inlineStr">
         <is>
-          <t>«До речі, Зеленський не зміг долучитись до нашого брифінгу о 15:00 (22:00 за Києвом) – **щось сталось в останню хвилину**», – додав Шумер.
-Він, однак, **зазначив** [https://www.eurointegration.com.ua/news/2023/12/5/7174982/], [https://www.eurointegration.com.ua/news/2023/12/5/7174982/] що перед сенаторами виступить сенатор-демократ Марк Ворнер, «який чудово знає, наскільки відчайдушно Україна потребує допомоги, запит на яку надіслав президент (Джо Байден. – Ред.)».</t>
+          <t>“Укрпошта” під загрозою банкрутства [https://www.rbc.ua/rus/news/uryadi-poperedili-mozhliviy-defolt-zbitkovoyi-1758005588.html]
+Державна компанія за 2022–2024 роки отримала 2,5 млрд грн збитків, а її капіталізація впала з 2,8 млрд до 0,2 млрд грн. 
+У 2024-му збиток склав 413 млн грн, боргове навантаження досягло 98% активів, а ліквідність впала до критичного рівня. 
+Для уникнення дефолту “Укрпошті” необхідна докапіталізація щонайменше 826 млн грн.</t>
         </is>
       </c>
       <c r="G942" s="3" t="inlineStr"/>
@@ -36326,21 +36356,21 @@
       </c>
       <c r="B946" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C946" s="3" t="inlineStr">
         <is>
-          <t>2023-06-16</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="D946" s="3" t="n">
-        <v>17839</v>
+        <v>54219</v>
       </c>
       <c r="E946" s="3" t="inlineStr"/>
       <c r="F946" s="3" t="inlineStr">
         <is>
-          <t>$205 млн додатково виділить США на гуманітарну допомогу для українців, – держсекретар Ентоні Блінкен. Гроші спрямують на продовольство, чисту питну воду, житло, охорону здоровʼя через міжнародні та неурядові організації.</t>
+          <t>Подивимося, чи будуть Путін і Зеленський працювати разом. Знаєте, вони трохи як олія та оцет. Вони не дуже добре ладнають з очевидних причин. Я б волів не бути там, — Трамп.</t>
         </is>
       </c>
       <c r="G946" s="3" t="inlineStr"/>
@@ -36402,20 +36432,18 @@
       </c>
       <c r="C948" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="D948" s="3" t="n">
-        <v>53918</v>
+        <v>50658</v>
       </c>
       <c r="E948" s="3" t="inlineStr"/>
       <c r="F948" s="3" t="inlineStr">
         <is>
-          <t>**Як українським родинам облаштувати дім з нуля без кабали**
-Через війну тисячі сімей втратили житло й почали життя заново — без заощаджень, але з надією. Родина Коваленків, яка переїхала зі Слов’янська до Києва, змогла швидко облаштувати квартиру без довгих кредитів і паперової тяганини.
-Холодильник і диван на 65 тис. грн оформили онлайн за 2 хвилини через «Легку розстрочку» [https://sensebank.ua/legka-rozstrochka] в Sense Bank — без довідок, підписів і з переплатою 0,01%. Перший платіж — лише через місяць.
-«Платимо потроху й просто живемо, а не відкладаємо життя на потім», — кажуть Коваленки.
-Як це працює та хто може скористатися — дізнавайтеся за посиланням. [https://sensebank.ua/legka-rozstrochka]</t>
+          <t>**‼️Україна повинна віддати РФ територію площею з Люксембург — близько 2300 км²: це зумовлює мирний план США**, — AFP [https://www.barrons.com/news/us-plan-sees-ukraine-ceding-territory-same-size-as-luxembourg-afp-analysis-of-isw-data-8813bc7a]
+Натомість Москва має повернути лише **меншу частину території**, яку вона повністю або частково контролює у Харківській, Дніпропетровській, Сумській та Чернігівській областях.
+Таким чином Україна поступиться **приблизно 20% своєї території, щоб повернути менше ніж 0,5%**.</t>
         </is>
       </c>
       <c r="G948" s="3" t="inlineStr"/>
@@ -36598,22 +36626,23 @@
       </c>
       <c r="B953" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C953" s="3" t="inlineStr">
         <is>
-          <t>2022-05-15</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="D953" s="3" t="n">
-        <v>7558</v>
+        <v>81842</v>
       </c>
       <c r="E953" s="3" t="inlineStr"/>
       <c r="F953" s="3" t="inlineStr">
         <is>
-          <t>**❗️Окупанти підтверджують, що використовують в Україні фосфорні та касетні види озброєння, - перехоплення СБУ.
-****Info Україна 🇺🇦** [https://t.me/+SRWsVjpx0-dhYzMy]</t>
+          <t>**Тим часом Кіпр зупиняє всі польоти у небі з 17:00, а Британські бази на острові приведені в стан повної бойової готовності, — ЗМІ **
+Нагадаю, що США відправлять додаткові літаки для допомоги Ізраїлю. 
+Ми, які отримали їх лише на третьому році повномасштабного вторгнення 😕</t>
         </is>
       </c>
       <c r="G953" s="3" t="inlineStr"/>
@@ -36755,17 +36784,18 @@
       </c>
       <c r="C957" s="3" t="inlineStr">
         <is>
-          <t>2025-03-28</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="D957" s="3" t="n">
-        <v>97855</v>
+        <v>90607</v>
       </c>
       <c r="E957" s="3" t="inlineStr"/>
       <c r="F957" s="3" t="inlineStr">
         <is>
-          <t>**У ТЦК та військових навчальних центрах працюватимуть юристи, психологи та волонтери, — ЗМІ **
-Це експериментальний проект, його мета — підтримка мобілізованих на початковому етапі служби.</t>
+          <t>**Ціни на каву знову бʼють рекорди: на 70% зросли ціни з початку року, — ****Bloomberg** [https://www.bloomberg.com/news/articles/2024-11-27/coffee-gets-even-pricier-as-futures-rally-to-highest-since-1977]** **
+Ціни на арабіку зросли до найвищого рівня за понад 40 років. Слідом за глобальними тенденціями вартість чашки кави зростає й в Україні.
+А за якою ціною купуєте ви каву?</t>
         </is>
       </c>
       <c r="G957" s="3" t="inlineStr"/>
@@ -36822,23 +36852,29 @@
       </c>
       <c r="B959" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C959" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="D959" s="3" t="n">
-        <v>11532</v>
+        <v>64398</v>
       </c>
       <c r="E959" s="3" t="inlineStr"/>
       <c r="F959" s="3" t="inlineStr">
         <is>
-          <t>❗️**ЦЕ ТРЕШ! П'яний українець у Польщі збив на смерть 21-річну дівчину.
-У крові 24-річного водія з України виявили [https://today.politeka.net/uk/410568-pyanyy-ukrainec-v-polshe-natvoril-bedy-kadry-za-chto-emu-grozit-12-let] два проміле алкоголю. У поліції додали, що водій був нетверезим і намагався втекти від поліції.
-Чоловікові йому загрожує **до 12 років** позбавлення волі.</t>
+          <t>Рух «Чесна мобілізація» пропонує **заборонити блогерам-ухилянтам балотуватися в депутати**.**
+****«**Поки одні захищають країну 24/7, ризикуючи життям, **різні блогери та активісти ухиляються від свого обов’язку** за допомогою різноманітних корупційних схем.  А потім ці «тигри» масово підуть в депутати як «патріоти», «антикорупціонери» та «волонтери», які начебто захищали Україну», — говорять в громадській організації.
+Зараз вся країна спостерігає за ниттям цих **ухилянтів, які тримають «ютюбний фронт»:** 
+⭕️ За Шабуніним, **який "воює" в київських ресторанах. **
+⭕️ За Мокриком, я**кий оформив фіктивну інвалідність. **
+⭕️ За Ніколовим,** який не може захищати державу, бо він різко став опікуном**;
+⭕️За Жернаковим з його **фейковою довідкою викладача та десятками інших.**
+«Люди, які відмовляються захищати країну і лише паразитують на ній, **не мають права вирішувати долю держави!** Треба чітко визначити: ховався від служби— **не маєш права бути обраним навіть в сільраду!»**, — заявив [https://t.me/ua_stalker/6388] представник руху «Чесна мобілізація», **ветеран російсько-української війни Олексій «Сталкер».**
+⭕️Нагадаємо, рух  [https://t.me/trulymob/98]« [https://t.me/trulymob/98]Чесна мобілізація [https://t.me/trulymob/98]» [https://t.me/trulymob/98] викриває** «заброньованих» ухилянтів — «активістів» та «мажорів».** Його створили військові та цивільні, які **виступають за справедливу мобілізацію**, зокрема, за прозору систему бронювання від служби в армії. Рух вже оприлюднив ряд **досьє на блогерів та активістів, які ухиляються від служби через різні схеми.**</t>
         </is>
       </c>
       <c r="G959" s="3" t="inlineStr"/>
@@ -37013,16 +37049,18 @@
       </c>
       <c r="C964" s="3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2022-11-25</t>
         </is>
       </c>
       <c r="D964" s="3" t="n">
-        <v>57956</v>
+        <v>42188</v>
       </c>
       <c r="E964" s="3" t="inlineStr"/>
       <c r="F964" s="3" t="inlineStr">
         <is>
-          <t>**Польща очікує від США постачання ударних вертольотів Apache, які у поєднанні з танками Abrams зміцнять оборону на кордоні з Білоруссю, — міністр оборони Польщі Маріуш Блащак</t>
+          <t>**Нет никакого полного блэкаута, — Подоляк 
+В результате российских обстрелов была разорвана энергетическая система. Ее восстановили в течение 24 часов. 
+Украина в любом случае будет проводить ремонты, а не кричать, что "все пропало". Также свою помощь в восстановлении и приобретении дополнительных частей для энергосистемы Украины предложили страны Евросоюза.</t>
         </is>
       </c>
       <c r="G964" s="3" t="inlineStr"/>
@@ -37234,11 +37272,11 @@
       </c>
       <c r="C970" s="3" t="inlineStr">
         <is>
-          <t>2023-02-09</t>
+          <t>2023-06-06</t>
         </is>
       </c>
       <c r="D970" s="3" t="n">
-        <v>46360</v>
+        <v>53149</v>
       </c>
       <c r="E970" s="3" t="inlineStr">
         <is>
@@ -37247,9 +37285,8 @@
       </c>
       <c r="F970" s="3" t="inlineStr">
         <is>
-          <t>**В Украину завезли опасный напиток, — Госпродслужба
-**В Украину привезли концентрированный напиток Bitter Apéritif – Monin с огромным количеством красителя E124, который является сильным аллергеном. 
-Он может вызвать анафилактический шок или приступ удушья у астматиков и людей с непереносимостью аспирина.</t>
+          <t>**Зеленський заявив, що отримав від деяких європейських партнерів "розуміння за кількістю" західних літаків, які отримає Україна
+**"Я коли отримав цю інформацію, то я мав день щастя. Була потужна пропозиція", — прокоментував президент.</t>
         </is>
       </c>
       <c r="G970" s="3" t="inlineStr"/>
@@ -37836,11 +37873,11 @@
       </c>
       <c r="C986" s="3" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2022-12-13</t>
         </is>
       </c>
       <c r="D986" s="3" t="n">
-        <v>35966</v>
+        <v>11049</v>
       </c>
       <c r="E986" s="3" t="inlineStr">
         <is>
@@ -37849,8 +37886,10 @@
       </c>
       <c r="F986" s="3" t="inlineStr">
         <is>
-          <t>**21/22 «шехедів» збито силами ППО над Україною**, — ПС. Ворог запускав дрони із Курської області рф. Протиповітряна оборона активно працювала на півночі країни.
-Є влучання БПЛА** **в один з обʼєктів Чернігівської області, [https://t.me/+emKY7B-TGhRlNjcy] — ОВА. Без електропостачання залишаються 5963 споживача.</t>
+          <t>Допомога Україні:
+• Єврокомісія профінансує 30 млн LED-ламп, – президентка ЄК Урсула фон дер Ляйєн.
+• В Італії ухвалили рішення щодо постачання зброї для ЗСУ, – La Reppublica. 
+• Канада надасть $115 млн для відновлення електропостачання, – міністерка фінансів Христя Фріланд.</t>
         </is>
       </c>
       <c r="G986" s="3" t="inlineStr"/>
@@ -38174,18 +38213,18 @@
       </c>
       <c r="C995" s="3" t="inlineStr">
         <is>
-          <t>2023-11-08</t>
+          <t>2022-03-28</t>
         </is>
       </c>
       <c r="D995" s="3" t="n">
-        <v>63487</v>
+        <v>24352</v>
       </c>
       <c r="E995" s="3" t="inlineStr"/>
       <c r="F995" s="3" t="inlineStr">
         <is>
-          <t>**РФ просить інші країни повернути продане їм озброєння через величезні втрати в Україні, — WSJ з посиланням на джерела**
-Постачальник вертолітних двигунів "ОДК-Климов", що діє, не справляється із заміщенням масштабних втрат техніки. Через це РФ веде переговори з такими країнами як Пакистан, Єгипет, Білорусь та Бразилія щодо повернення важливих запчастин.
-Вже у квітні делегація РФ просила президента Єгипту повернути двигуни для гелікоптерів Мі-8 та Мі-17.</t>
+          <t>**Роман Абрамович выступает в роли «миротворца» в войне россии в Украине, — Daily Mail
+**По данным британского таблоида, Абрамович выступая в качестве посредника между Зеленским и Путиным. Он "летал между Стамбулом, Москвой и Киевом" и встретился с членом украинской переговорной группы Умеровым и пресс-серетарем Эрдогана Калыном, который выдвинул идею о том, что Крым и Донбасс должны находиться в долгосрочной аренде у РФ.
+После этого, по данным Daily Mail Абрамович и Умеров транзитом через Польшу прибыли в Киев, где встретились з Зеленским.</t>
         </is>
       </c>
       <c r="G995" s="3" t="inlineStr"/>
@@ -39216,17 +39255,16 @@
       </c>
       <c r="C1022" s="3" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D1022" s="3" t="n">
-        <v>43351</v>
+        <v>61256</v>
       </c>
       <c r="E1022" s="3" t="inlineStr"/>
       <c r="F1022" s="3" t="inlineStr">
         <is>
-          <t>Ірина Фаріон померла у лікарні. 
-Попри всі зусилля медиків, врятувати її не вдалося, повідомляє голова ОВА.</t>
+          <t>Київ – це наступне місто, де буде запущений пілот 5G. Є домовленість з операторами про чіткий дедлайн: 3G повністю вимкнуть (замінять) до 1 січня 2031 року, заявив заступник Мінцифри.</t>
         </is>
       </c>
       <c r="G1022" s="3" t="inlineStr"/>
@@ -39363,16 +39401,17 @@
       </c>
       <c r="C1026" s="3" t="inlineStr">
         <is>
-          <t>2022-03-01</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="D1026" s="3" t="n">
-        <v>19660</v>
+        <v>55360</v>
       </c>
       <c r="E1026" s="3" t="inlineStr"/>
       <c r="F1026" s="3" t="inlineStr">
         <is>
-          <t>**Советник главы офиса президента Украины заявил, что РФ окончательно сбросила макси</t>
+          <t>**Суд Києва призначив співачці Інні Вороновій — дружині наркодилера, яка знімала роботу ППО, покарання у вигляді одного року умовно, — ЗМІ
+**Таке рішення пояснюється тим, що вона пішла на угоду зі слідством та визнала свою провину.</t>
         </is>
       </c>
       <c r="G1026" s="3" t="inlineStr"/>
@@ -39504,16 +39543,16 @@
       </c>
       <c r="B1030" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1030" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2023-05-25</t>
         </is>
       </c>
       <c r="D1030" s="3" t="n">
-        <v>110589</v>
+        <v>17133</v>
       </c>
       <c r="E1030" s="3" t="inlineStr">
         <is>
@@ -39522,10 +39561,8 @@
       </c>
       <c r="F1030" s="3" t="inlineStr">
         <is>
-          <t>**Верховна Рада вже сьогодні може проголосувати за "тютюновий закон" №13628, який посилить корупцію та підвищить ціни на сигарети — ****економіст** [https://www.facebook.com/neskhod/posts/pfbid02rnHVxNpG9zrSqHcrARpbctey42RJbhMBWbEpNhD98kbzJWG3pJGzZsTF1bxXBfJKl]
-Депутати хочуть, щоб тютюнові компанії використовували в сигаретах український тютюн без жодних вимог до його якості та ціни. Економіст Ілля Несходовський вже охрестив законопроект "**економічний нонсенсом**, який призведе до **подорожчання сигарет, зниження якості та підвищення корупції**"
-"Коли держава гарантує комусь частку ринку, в Україні це перетворює на корупційні можливості. Створення "**залізної**" квоти, контроль за якою в руках чиновників— це **ідеальний інструмент для заробляння**", — написав Несходовський.
-Цей законопроект нагадує "**соєві правки**", коли речне регулювання і квоти підривають конкуренцію, **зупиняють економіку** та призводять до **вищих цін для споживачів**. Експерт закликав депутатів "**не наступати на соєві граблі знову**".</t>
+          <t>Мінськ і москва підписали документ про розміщення ядерної зброї в Білорусі: [https://t.me/c/1431180517/15758] росія планує побудувати сховище. Контролює «червону кнопку» рф, – DW.
+__Лукашенко: «Я нічого не чув, але подякував». __</t>
         </is>
       </c>
       <c r="G1030" s="3" t="inlineStr"/>
@@ -39973,19 +40010,18 @@
       </c>
       <c r="C1042" s="3" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="D1042" s="3" t="n">
-        <v>100344</v>
+        <v>87589</v>
       </c>
       <c r="E1042" s="3" t="inlineStr"/>
       <c r="F1042" s="3" t="inlineStr">
         <is>
-          <t>**❗️Банки знизять ліміти за грошовими операціями для українців з 1 червня 2025 року. Це стосується не тільки карткових переказів, а й платежів через IBAN — «РБК-Україна» з посиланням на меморандум банків**
-📍Ліміт для клієнтів «середнього» та «низького» рівня ризику буде знижений **до 100 тис. грн на місяць. **
-📍Для клієнтів «високого» рівня ризику ліміт залишиться таким самим — **50 тис. грн.**
-Ліміти **не стосуються клієнтів з підтвердженими джерелами доходів**, зокрема зарплатних клієнтів.</t>
+          <t>**МСЕК можуть розформувати, передавши їхні функції кластерним медустановам, — ****законопроєкт** [https://moz.gov.ua/uk/reforma-msek-moz-rozrobilo-zakonoproyekt-ta-rozpochalo-konsultaciyi-z-gromadskistyu]** від МОЗ
+**Плановані функції: встановлення інвалідності, направлення на додаткові обстеження, повторні огляди. Медичний висновок про тимчасову непрацездатність буде формуватися на весь період хвороби.
+Що думаєте з цього приводу?</t>
         </is>
       </c>
       <c r="G1042" s="3" t="inlineStr"/>
@@ -40046,24 +40082,21 @@
       </c>
       <c r="B1044" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1044" s="3" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2022-03-20</t>
         </is>
       </c>
       <c r="D1044" s="3" t="n">
-        <v>2354</v>
+        <v>6246</v>
       </c>
       <c r="E1044" s="3" t="inlineStr"/>
       <c r="F1044" s="3" t="inlineStr">
         <is>
-          <t>Киев усиливает контроль масочного режима в метро
-**Об этом на брифинге заявил мэр Киева Виталий Кличко.
-По его словам, в наземном транспорте дисциплина среди пассажиров лучше, и они в основном соблюдают масочный режим.
-"В метрополитене много людей, к сожалению, пренебрегают правилами безопасности. Поэтому мы силами муниципальной охраны усиливаем контроль и без масок пассажиров в метро не будут пропускать. Мы будем принуждать всех соблюдать жестких правил", - заявил Кличко.</t>
+          <t>Азов сообщает, что Мариуполь обстреляли из 4 кораблей военно-морского флота россии</t>
         </is>
       </c>
       <c r="G1044" s="3" t="inlineStr"/>
@@ -40089,24 +40122,16 @@
       </c>
       <c r="C1045" s="3" t="inlineStr">
         <is>
-          <t>2022-02-01</t>
+          <t>2022-05-07</t>
         </is>
       </c>
       <c r="D1045" s="3" t="n">
-        <v>685</v>
+        <v>10993</v>
       </c>
       <c r="E1045" s="3" t="inlineStr"/>
       <c r="F1045" s="3" t="inlineStr">
         <is>
-          <t>**"Это мой кент. Никаких претензий не будет!": **УП обнародовало видео с Трухиным после ДТП [https://youtu.be/86uzoruHMgM]
-__- Дай, я тихонечко в лес уйду. 
-- Не получится
-- Я с Денисом поговорю
-- Каким?
-- Монастырским
-- Принеси мне сумку из багажника. Обычная спортивная сумка. Там 150 тысяч
-__По данным СМИ, 23 августа народный депутат фракции "Слуга народа" Александр Трухин, будучи выпившим, создал ДТП по дороге из Полтавы в Киев.
-Впоследствии около 30 медиа почистили [https://www.pravda.com.ua/news/2021/08/30/7305437/] сообщение об этой аварии, в которой пострадали шесть человек.</t>
+          <t>Снова бабахи в Белгороде пишут местные тг</t>
         </is>
       </c>
       <c r="G1045" s="3" t="inlineStr"/>
@@ -40480,18 +40505,18 @@
       </c>
       <c r="C1055" s="3" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="D1055" s="3" t="n">
-        <v>59846</v>
+        <v>63839</v>
       </c>
       <c r="E1055" s="3" t="inlineStr"/>
       <c r="F1055" s="3" t="inlineStr">
         <is>
-          <t>**В Україні запустили перше онлайн-опитування про безробіття, щоб дізнатися реальний рівень і причини безробіття в країні, — Михайло Федоров
-**Зібрані дані покажуть ким працюють громадяни і яким чином ведуть пошуки роботи. Пройти опитування можна за посиланням: https://survey.stat.gov.ua/ 
-Узяти участь можуть усі українці від 15 років з будь-якого куточка світу. Для цього необхідний лише смартфон, планшет або комп'ютер і застосунок Дія або BankID.</t>
+          <t>**Українські**  [https://t.me/+PrLok3ySBnljZWMy]**кабани**  [https://t.me/+PrLok3ySBnljZWMy]**"вполювали" рашиста-диверсанта у Чорнобильській зоні, —**** ФОКУС** [https://focus.ua/voennye-novosti/605804-ukrainskij-kaban-pojmal-rossijskuyu-drg-na-granice-s-belarusyu-est-zhertvy-socseti]
+Ворожа диверсійна група проходила лісом та зіткнулася зі стадом диких кабанів. Стріляти у тварин диверсанти не змогли, через ризик "засвітитися".
+Кабанам вдалося наздогнати одного з окупантів. Після зіткнення із однією з тварин він невдало впав і вдарився головою об камінь. Загинув на місці.</t>
         </is>
       </c>
       <c r="G1055" s="3" t="inlineStr"/>
@@ -40625,22 +40650,24 @@
       </c>
       <c r="B1059" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1059" s="3" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-11-14</t>
         </is>
       </c>
       <c r="D1059" s="3" t="n">
-        <v>11728</v>
+        <v>8994</v>
       </c>
       <c r="E1059" s="3" t="inlineStr"/>
       <c r="F1059" s="3" t="inlineStr">
         <is>
-          <t>Генпрокурор Украины заявила об аресте активов на $420 млн, которые связывают с Михаилом Фридманом
-)))))))</t>
+          <t>**Окупанти найближчими тижнями активізують наступальні дії на Донеччині**, – ISW
+Наступальні операції окупантів активізуються, коли на Донеччину прибудуть мобілізовані та сили, які були виведені з Херсона. 
+Але навряд чи це їм допоможе!
+__The Times of Ukraine [https://t.me/UA_TU]</t>
         </is>
       </c>
       <c r="G1059" s="3" t="inlineStr"/>
@@ -40737,18 +40764,16 @@
       </c>
       <c r="C1062" s="3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="D1062" s="3" t="n">
-        <v>83974</v>
+        <v>98256</v>
       </c>
       <c r="E1062" s="3" t="inlineStr"/>
       <c r="F1062" s="3" t="inlineStr">
         <is>
-          <t>**Збиття крилатої ракети на межі Закарпатської та Львівської областей, — ОВА**
-Дуже спокійно та професійно🤝 
-**UPD: **крилату ракету збив не кулеметник, її догнала «ППОшка», — Ігнат.</t>
+          <t>**❗️НАТО не братиме участі в мирних переговорах щодо України, — ****Рютте** [https://nv.ua/ukr/world/geopolitics/mirni-peregovori-ta-vstup-ukrajini-v-nato-ryutte-v-interv-yu-nv-rozpoviv-pro-rol-alyansu-50503720.html]</t>
         </is>
       </c>
       <c r="G1062" s="3" t="inlineStr"/>
@@ -41002,21 +41027,22 @@
       </c>
       <c r="B1069" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1069" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="D1069" s="3" t="n">
-        <v>62146</v>
+        <v>50257</v>
       </c>
       <c r="E1069" s="3" t="inlineStr"/>
       <c r="F1069" s="3" t="inlineStr">
         <is>
-          <t>⚡️**Світло більше не вимикатимуть сьогодні на Заході**: відключення до кінця доби вже скасовано на Івано-Франківщина [https://t.me/ivano_frankivsk_times] та Львівщина [https://t.me/times_lviv], — місцеві обленерго.</t>
+          <t>Британський Принц Гаррі сьогодні без анонса приїхав [https://www.telegraph.co.uk/royal-family/2025/04/10/prince-harry-ukraine-war-victims-surprise-visit/] в Україну, пише The Telegraph.
+Він відвідав поранених солдат, які проходять лікування в одному з Львівських шпиталів.</t>
         </is>
       </c>
       <c r="G1069" s="3" t="inlineStr"/>
@@ -41083,19 +41109,20 @@
       </c>
       <c r="C1071" s="3" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2024-01-22</t>
         </is>
       </c>
       <c r="D1071" s="3" t="n">
-        <v>99363</v>
+        <v>68285</v>
       </c>
       <c r="E1071" s="3" t="inlineStr"/>
       <c r="F1071" s="3" t="inlineStr">
         <is>
-          <t>**Кличко в інтерв'ю BBC про мир в обмін на території: «Це несправедливо, українці ніколи не приймуть окупацію» 
-Український народ ніколи не прийме окупацію росією частини українських територій. Тому варіант мирної угоди, який змушує Україну віддати росії частину територій заради припинення військових дій, може бути **лише** **тимчасовим рішенням**, заявив [https://www.bbc.com/news/articles/cp348ygjgy3o] мер Києва Віталій Кличко в інтерв’ю BBC. 
-«Один зі сценаріїв – це віддати частину території. Це не справедливо. Заради миру, тимчасового миру, можливо, це може бути рішенням, тимчасовим. Але український народ ніколи не прийме окупацію територій Росією», 
-— упевнений Кличко.</t>
+          <t>**Екс-мер Ірпеня Карплюк постав перед судом за розкрадання грошей на будівництві вже збудованого парку**
+Сьогодні відбулося чергове засідання Вишгородського суду над колишнім мером Ірпеня Володимиром Карплюком. Бізнесмена-забудовника, політика та екс-чиновника судять за те, що він підписав договір з комунальним підприємством “Ірпіньжилінвестбуд” про створення проектної документації на будівництво парку, який уже було збудовано.
+Карплюк пішов під суд із обвинувальним актом за ч.4 ст.191 КК (розтрата майна шляхом зловживання посадовою особою своїм службовим становищем у великих розмірах). Йому загрожує від 5 до 8 років ув'язнення.
+Це не перша справа, за яку судять Карплюка. Попередню, про розкрадання [https://hromadske.ua/posts/bezsmertnyi-fop-iak-chynovnyky-na-kyivshchyni-ukladaly-uhody-z-pomerlym-pidpryiemtsem] бюджетних коштів через фірми, зареєстровані на покійника, закрив [https://reyestr.court.gov.ua/Review/109233274] Ірпінський суд – через закінчення термінів.
+У січні стало відомо, що учаснику пропутінської секти «АллатРа» [https://t.me/UaOnlii/63569] Карплюку скасували [https://t.me/UaOnlii/67917] візи до США – через масштабну корупцію.</t>
         </is>
       </c>
       <c r="G1071" s="3" t="inlineStr"/>
@@ -41156,22 +41183,21 @@
       </c>
       <c r="C1073" s="3" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2021-10-27</t>
         </is>
       </c>
       <c r="D1073" s="3" t="n">
-        <v>47084</v>
+        <v>5617</v>
       </c>
       <c r="E1073" s="3" t="inlineStr"/>
       <c r="F1073" s="3" t="inlineStr">
         <is>
-          <t>Більше 65% українців вважають** санкції проти Порошенка і Медведчука заслуженим покаранням, **— результати дослідження.
-⭕️65,2% українців впевнені, що **Порошенко, Коломойський, Медведчук** та інші олігархи й держзрадники отримали санкції заслужено. Більшість впевнена, що підсанкційні мають **повернути державі все вкрадене**.
- ⭕️«Окрім того, **50,1% українців** переконані, що зняття санкцій можливе лише після відбування вказаними політиками та олігархами юридичної **відповідальності**, а також — кримінальної. 
-⭕️Водночас **лише 6% опитаних** – не проти скасування санкцій. Проти участі підсанкційних політиків у виборах у майбутньому висловилися **68,9% українців**», — йдеться в результатах [https://activegroup.com.ua/2025/03/07/bilshist-ukra%d1%97nciv-viryat-shho-kra%d1%97na-zmozhe-prodovzhiti-borotbu-navit-bez-amerikansko%d1%97-dopomogi/] нацсоцдослідження.
- ⭕️Цікаво, що кожен 5-й українець **не готовий пробачити Порошенку, Медведчуку і Коломойському** заподіяну шкоду та вважає **недопустимим зняття санкцій** навіть за умови понесення ними кримінальної відповідальності. 
- ⭕️Відомо, що 13 лютого були запроваджені санкції **проти низки олігархів та політиків**. Зокрема, Порошенка звинувачували [https://www.unian.ua/politics/proti-poroshenka-iniciyovani-sankciji-za-torgivlyu-z-rf-u-viynu-peticiya-12896805.html] в: лобіюванні Харківських угод, фінансуванні терористів (купівля вугілля з ОРДЛО), торгівлі у війну з росією (Липецька фабрика, завод «Богдан» в рф), спільному з Медведчуком та рф незаконному відчуженні нафтопроводу в держави тощо.
- ⭕️Раніше стало відомо, що Порошенко **потрапив у скандал**: його спіймали на тому, що підозрюваний у держзраді політик лише за два тижні 2025 року виві [https://www.unian.ua/politics/poroshenko-vstig-vivesti-za-kordon-milyard-i-shche-stilki-zh-podaruvati-a-potim-yogo-zupinili-sankciji-ekspert-12935715.html]з [https://www.unian.ua/politics/poroshenko-vstig-vivesti-za-kordon-milyard-i-shche-stilki-zh-podaruvati-a-potim-yogo-zupinili-sankciji-ekspert-12935715.html] із України **1 млрд 48 млн грн та ще 986 млн грн переписав на синів-ухилянтів**, які переховуються в Лондоні від ЗСУ. Потім Порошенка зупинили санкції.</t>
+          <t>**Для справки - перечень Слуг, кто взял себе в помощники родственников коллег:
+Cупруга нардепа от Слуги народа Александра Мережко Виктория Улиганец работает помощницей у «слуги» Игоря Марчука;
+Супруга Алексея Кузнецова (СН) Алина - помощница у «слуги» Александра Кабанова
+Сын Андрея Задорожного (нардеп от СН) Иван - помощник у «слуги» Андрея Костина, а 
+дочь Костина Анастасия - помощница у Задорожного.
+Администрация Президента [https://t.me/AP_UA]</t>
         </is>
       </c>
       <c r="G1073" s="3" t="inlineStr"/>
@@ -41654,18 +41680,18 @@
       </c>
       <c r="C1086" s="3" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>2024-06-22</t>
         </is>
       </c>
       <c r="D1086" s="3" t="n">
-        <v>67189</v>
+        <v>78506</v>
       </c>
       <c r="E1086" s="3" t="inlineStr"/>
       <c r="F1086" s="3" t="inlineStr">
         <is>
-          <t>**Українці створили робота D-21-11, який може виконувати бойові завдання: проводити розвідку, штурмувати або обороняти позиції, — Федоров**
-Ще його можна використовувати для безпечного доставляння боєприпасів або провізії для бійців у гарячі точки. 
-"Бойова, повністю знімна частина робота, D-11, уже пройшла успішні випробування і має позитивні відгуки від військових. У планах розробників - інтегрувати в робота натовські види озброєння та посилити стійкість до ворожого РЕБу", - зазначили у Мінцифри.</t>
+          <t>**В Сумській області депутат облради з карабіну застрелив людину, — ****РБК** [https://t.me/prokuraturasumy/3240]
+Інцидент, як з'ясувало слідство, стався вчора в селі Заріччя на території мисливського господарства "Північний ліс" близько 19-ї години.
+"Під час пристрілки власного мисливського карабіна депутат, замість встановленої мішені, вистрілив у працівника лісництва, який перебував у зоні ведення вогню. Від отриманого вогнепального поранення 46-річний потерпілий помер на місці події", - розповіли в місцевій прокуратурі.</t>
         </is>
       </c>
       <c r="G1086" s="3" t="inlineStr"/>
@@ -42022,24 +42048,22 @@
       </c>
       <c r="B1096" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1096" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="D1096" s="3" t="n">
-        <v>47013</v>
+        <v>29908</v>
       </c>
       <c r="E1096" s="3" t="inlineStr"/>
       <c r="F1096" s="3" t="inlineStr">
         <is>
-          <t>Президент США Дональд Трамп —** у пошуках «партнера для миру».**
-⭕️Його команда шукає «партнера для миру» серед досвідчених українських політиків, які допоможуть відновити добрі відносини між Україною та США, а також розпочнуть серйозну роботу з пошуку ефективних** шляхів для встановлення стабільного миру.**
-⭕️Як пише видання Politico, помічники Трампа** вже провели таємні переговори з членами партії Петра Порошенка, **безпосереднього попередника Зеленського на посаді президента. Також команда президента США контактувала з лідеркою української опозиції Юлією Тимошенко. Журналісти видання називають її **«безжалісно амбітним колишнім прем’єр-міністром». **
-⭕️Сама лідерка «Батьківщини» підтвердила [https://www.facebook.com/share/p/152kbRmBzt/?mibextid=wwXIfr], що її команда «веде перемовини з усіма нашими союзниками», проте ідею проведення виборів під час воєнного стану **категорично відкинула.**</t>
+          <t>**Норвегія надасть Україні п'ятирічну програму військової допомоги загальним обсягом приблизно €7 мільярдів,** — МЗС Норвегії.
+🫂🫂🫂</t>
         </is>
       </c>
       <c r="G1096" s="3" t="inlineStr"/>
@@ -42245,17 +42269,17 @@
       </c>
       <c r="C1102" s="3" t="inlineStr">
         <is>
-          <t>2023-09-11</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="D1102" s="3" t="n">
-        <v>59843</v>
+        <v>47061</v>
       </c>
       <c r="E1102" s="3" t="inlineStr"/>
       <c r="F1102" s="3" t="inlineStr">
         <is>
-          <t>**Після спецоперації з ****російським Мі-8** [https://t.me/UaOnlii/59416]** на 70% зросла кількість військових РФ, охочих здатися у полон, — представник ГУР Юсов
-**«Є дуже стрибок по лінії «Хочу жить» окремо і по інших каналах зв’язку. Після успішної операції «Синиця» з Мі-8 і пілотом, скажімо, збільшилась кількість військовослужбовців армії РФ, які розглядають для себе подібний сценарій. Звернення на державний проєкт «Хочу жить» – стрибок відбувся приблизно на 70 відсотків за день», – заявив Андрій Юсов.</t>
+          <t>Трухин написал заявление  [https://t.me/UaOnlii/47021]**о сложении депутатского мандата —  нардеп Железняк
+UPD: **Верховная Рада поддержала прекращение депутатских полномочий Трухина. "За" проголосовали 288 депутатов.</t>
         </is>
       </c>
       <c r="G1102" s="3" t="inlineStr"/>
@@ -42507,20 +42531,16 @@
       </c>
       <c r="C1109" s="3" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2022-08-05</t>
         </is>
       </c>
       <c r="D1109" s="3" t="n">
-        <v>13310</v>
+        <v>17048</v>
       </c>
       <c r="E1109" s="3" t="inlineStr"/>
       <c r="F1109" s="3" t="inlineStr">
         <is>
-          <t>До Києва прибули ще 52 загиблих з «Азовсталі». Поки що можемо припускати належність лише чотирьох з них до ОЗСП «Азов». Попередньо, решта загиблих належать до інших родів і видів військ.
-Об‘єктивних даних, які дають можливість ідентифікувати загиблих, поки що дуже мало. Інформація у відкритих джерелах – ЗМІ, телеграм-каналах – не є достовірною.
-Патронатна служба буде оперативно інформувати рідних стосовно судово-медичної експертизи і ДНК-досліджень.
-Закликаємо медіа користуватися перевіреними джерелами інформації та не використовувати домисли та «вкиди» стосовно обміну тілами загиблих між українською і російською сторонами та їх ідентифікації.
-@azovangels [https://t.me/azovangels]</t>
+          <t>**Адміністрація Байдена оголосить про ще один пакет зброї для України на 1 мільярд доларів**, — Reuters.</t>
         </is>
       </c>
       <c r="G1109" s="3" t="inlineStr"/>
@@ -42678,23 +42698,22 @@
       </c>
       <c r="B1113" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1113" s="3" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="D1113" s="3" t="n">
-        <v>53935</v>
+        <v>31385</v>
       </c>
       <c r="E1113" s="3" t="inlineStr"/>
       <c r="F1113" s="3" t="inlineStr">
         <is>
-          <t>**Журналіст:** Ми бачили, що вчора ввечері Росія продовжила свої насильницькі дії в Україні, запустивши ще більше безпілотників. Що ви про це думаєте?
-**Трамп:** Я думаю, вони намагаються вести переговори.
-🐒</t>
+          <t>**❗️Якщо в Україні знизять мобілізаційний вік, новобранці будуть повністю забезпечені спорядженням. Про це попереджений був Київ,** — представник Держдепу США Метью Міллер
+«Зрештою, рішення про склад збройних сил мають ухвалити українці. Ми чітко дали зрозуміти: якщо вони нададуть додаткові сили для участі в боях, ми і наші союзники будемо готові екіпірувати і навчити ці сили», — додав він.</t>
         </is>
       </c>
       <c r="G1113" s="3" t="inlineStr"/>
@@ -42715,23 +42734,26 @@
       </c>
       <c r="B1114" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1114" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="D1114" s="3" t="n">
-        <v>80102</v>
+        <v>53305</v>
       </c>
       <c r="E1114" s="3" t="inlineStr"/>
       <c r="F1114" s="3" t="inlineStr">
         <is>
-          <t>**У Запоріжжі чоловік звернувся до поліції, через те, що повія відмовила йому в сексі, — ****ТСН** [https://tsn.ua/amp/ukrayina/u-zaporizhzhi-cholovik-zvernuvsya-do-policiyi-bo-zhinka-vidmovila-yomu-v-seksi-2617308.html]
-Жінка розмістила  оголошення про надання інтимних послуг, взяла у чоловіка кошти, і відмовилась спати з ним. Чоловік виграв суд, а жінку засудили до 200 годин громадських робіт.
-Ситуація..</t>
+          <t>«**Це чергова політична помста** центральної влади киянам», — Віталій Кличко про плани **вилучити в Києва ще 8 млрд грн**. 
+⭕️Завтра планується «протягнути» через ВР **законопроєкт №13439-3** у другому читанні, який передбачає **вилучення з бюджету Києва ще 8 млрд грн**. 
+Без жодного обґрунтування хочуть забрати у столиці гроші, **які закладені на допомогу військовим**, виплати вчителям і медикам, компенсації вартості проїзду киян у комунальному транспорті, **ремонти шкіл, садочків і лікарень тощо**.  
+Це робиться, щоб позбавити місто ресурсів і тиснути на Київ. **Це чергова політична помста центральної влади киянам**. 
+Через цей черговий крок у бік згортання децентралізації Україна **може втратити підтримку партнерів на шляху до Євросоюзу**. Через згортання реформ ЄС вже **призупинив фінансування **допомоги Україні, заявив [https://t.me/vitaliy_klitschko/5066] мер Києва Віталій Кличко. 
+⭕️Мер столиці звернувся [https://t.me/vitaliy_klitschko/5067] до нардепів із закликом **не допустити чергової стратегічної помилки**, як це вже відбулося під час голосування за фактичне **обмеження незалежності антикорупційних органів**. Ціна подібних «рішень» — надто висока **для майбутнього України**, наголосив він.</t>
         </is>
       </c>
       <c r="G1114" s="3" t="inlineStr"/>
@@ -42877,18 +42899,18 @@
       </c>
       <c r="C1118" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2024-03-25</t>
         </is>
       </c>
       <c r="D1118" s="3" t="n">
-        <v>104738</v>
+        <v>72610</v>
       </c>
       <c r="E1118" s="3" t="inlineStr"/>
       <c r="F1118" s="3" t="inlineStr">
         <is>
-          <t>**❗️Сьогодні Трамп оголосить про передачу Україні наступальної зброї та ракет великої дальності, які можуть бити вглиб рф, — Axios
-**📍Видання також пише, що Путін повідомив Трампу, що протягом 2 місяців рф планує великий наступ: план «максимум» — повна окупація Запорізької, Херсонської, Донецької й Луганської областей.
-📍Трамп заявив, що **США надішлють Україні системи Patriot. **Він** **додав, що ЗРК Україні «вкрай потрібні», бо «путін гарно говорить, а потім увечері всіх бомбить».</t>
+          <t>**Ураження десантного корабля рф «Ямал» в Севастополі — критичні — ГУР**
+За даними розвідки, пробоїна у верхній палубі корабля зумовила крен на правий борт. Відтак, окупанти безперервно відкачують воду із ураженого «Ямала», який брав участь в анексії Криму, а з 2017 по 2023 рік перебував на ремонті.
+Подробиці щодо втрат росіян внаслідок ракетної атаки СБУ проти російських ВДК уточнюються.</t>
         </is>
       </c>
       <c r="G1118" s="3" t="inlineStr"/>
@@ -43523,24 +43545,18 @@
       </c>
       <c r="C1135" s="3" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="D1135" s="3" t="n">
-        <v>65692</v>
+        <v>41962</v>
       </c>
       <c r="E1135" s="3" t="inlineStr"/>
       <c r="F1135" s="3" t="inlineStr">
         <is>
-          <t>❗️**Які наслідки для США і Європи матиме програш та повна окупація України — ISW **
-Якщо Україна зазнає поразки у війні, то:
-📍Російські бази будуть у Львові на кордоні з НАТО 
-📍США доведеться відправляти свої війська, зброю і літаки-невидимки (які потрібні були для війни з Китаєм) до Польщі, а це витрати в сотні мільярдів на рік.
-📍виникне масштабна криза і паніка мирного населення
-📍буде нова хвиля мільйонів біженців з України
-📍росія у прямому сенсі загрожуватиме НАТО
-📍США в терміновому порядку будуть вимушені перекидати війська на європейський кордон. Перемога ж України поставить найбоєздатнішу армію на європейському континенті на передову оборону НАТО.
-У світі це розуміють, тому їм простіше надати Україні потрібну для перемоги зброю, ніж потім самим починати війну з росією, тому це вагомий аргумент, щоб Україні надати допомогу. І вони її надаватимуть.</t>
+          <t>**Окупанты использовали свалку в Херсоне для сжигания трупов - вероятно, своих погибших товарищей, — The Guardian со ссылкой на заявления местных жителей
+**Собеседники издания рассказали, что видели, как на свалку приезжали грузовики, наполненные черными мешками, которые после этого сжигались. При этом в воздухе чувствовался резкий запах паленых волос.
+При въезде на свалку был установлен блокпост, и к территории местных жителей не подпускали.</t>
         </is>
       </c>
       <c r="G1135" s="3" t="inlineStr"/>
@@ -43911,21 +43927,21 @@
       </c>
       <c r="B1145" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1145" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2022-02-22</t>
         </is>
       </c>
       <c r="D1145" s="3" t="n">
-        <v>107184</v>
+        <v>1553</v>
       </c>
       <c r="E1145" s="3" t="inlineStr"/>
       <c r="F1145" s="3" t="inlineStr">
         <is>
-          <t>**«Укрпошта» закриває останнє відділення у Костянтинівці на Донеччині — занадто небезпечно працювати, — директор компанії Ігор Смілянський**</t>
+          <t>Зеленский: мы не верим в то, что будет мощная война против Украины и полномасштабная военная эскалация.</t>
         </is>
       </c>
       <c r="G1145" s="3" t="inlineStr"/>
@@ -44104,16 +44120,18 @@
       </c>
       <c r="C1150" s="3" t="inlineStr">
         <is>
-          <t>2022-01-27</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="D1150" s="3" t="n">
-        <v>530</v>
+        <v>274</v>
       </c>
       <c r="E1150" s="3" t="inlineStr"/>
       <c r="F1150" s="3" t="inlineStr">
         <is>
-          <t>**Президент Турции Реджеп Тайип Эрдоган заявил, что для России "глупо нападать на Украину", и что Турция будет действовать как **член НАТО. [https://www.pravda.com.ua/rus/news/2022/01/27/7321833/]</t>
+          <t>По состоянию на середину января возле Украины размещено 36 пусковых установок Искандер. CNN приводит сообщение Минобороны о том, что Искандеры могут поражать цели на расстоянии 500−700 км, в том числе достигнуть Киева.
+По мнению разведки, Россия может использовать ракетное оружие средней дальности для «уничтожения критически важных объектов».
+В новой оценке Минобороны также сказано, что Россия разместила на территории «Д/ЛНР» около 3 тысяч военных и поддерживает более 35 тысяч боевиков на Донбассе. Также количество разведывательных полетов у границы увеличилось в три раза по сравнению с прошлым годом.</t>
         </is>
       </c>
       <c r="G1150" s="3" t="inlineStr"/>
@@ -44213,23 +44231,23 @@
       </c>
       <c r="B1153" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1153" s="3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2021-09-22</t>
         </is>
       </c>
       <c r="D1153" s="3" t="n">
-        <v>72610</v>
+        <v>5210</v>
       </c>
       <c r="E1153" s="3" t="inlineStr"/>
       <c r="F1153" s="3" t="inlineStr">
         <is>
-          <t>**Ураження десантного корабля рф «Ямал» в Севастополі — критичні — ГУР**
-За даними розвідки, пробоїна у верхній палубі корабля зумовила крен на правий борт. Відтак, окупанти безперервно відкачують воду із ураженого «Ямала», який брав участь в анексії Криму, а з 2017 по 2023 рік перебував на ремонті.
-Подробиці щодо втрат росіян внаслідок ракетної атаки СБУ проти російських ВДК уточнюються.</t>
+          <t>**В Украине введут обязательную COVID-вакцинацию**
+Европейский суд по правам человека подтвердил положение украинского национального законодательства, что обязательная вакцинация является законной, отметил Виктор Ляшко.
+“Предлагаем начать внедрение обязательных...прививок...для работников заведений образования, министерств и других центральных органов исполнительной власти и их структурных подразделений, а также местных государственных администраций", – заявил министр здравоохранения.</t>
         </is>
       </c>
       <c r="G1153" s="3" t="inlineStr"/>
@@ -44399,18 +44417,17 @@
       </c>
       <c r="C1158" s="3" t="inlineStr">
         <is>
-          <t>2022-12-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="D1158" s="3" t="n">
-        <v>11774</v>
+        <v>18302</v>
       </c>
       <c r="E1158" s="3" t="inlineStr"/>
       <c r="F1158" s="3" t="inlineStr">
         <is>
-          <t>«Президент путін кайфує від ванни з оленячою кров‘ю і це – норм».
-Інфлюенсери з росії за $20 готові озвучити будь яку єресь та маячню, – довів експеримент The Insider.
-__Тікток головного мозку.__</t>
+          <t>Теракт в Краматорську. [https://t.me/c/1431180517/18298] Вранці з-під завалів деблоковано тіло ще однієї жертви. Російські ракети вбили 12 людей (у тому числі 3 дитини), ще 60 постраждало, врятовано 11, – ДСНС. Аварійно-рятувальні роботи завершені.
+__Редакція Times of Ukraine приносить щирі співчуття родинам загиблих.</t>
         </is>
       </c>
       <c r="G1158" s="3" t="inlineStr"/>
@@ -44549,16 +44566,20 @@
       </c>
       <c r="C1162" s="3" t="inlineStr">
         <is>
-          <t>2023-05-18</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="D1162" s="3" t="n">
-        <v>9392</v>
+        <v>34792</v>
       </c>
       <c r="E1162" s="3" t="inlineStr"/>
       <c r="F1162" s="3" t="inlineStr">
         <is>
-          <t>Тільки в Україні можуть повідомити [https://www.slovoidilo.ua/2023/03/30/novyna/polityka/nabu-sap-povidomyly-pro-pidozru-suddi-pecherskoho-rajsudu-ilyevij] про підозру судді Печерського райсуду, а вона.. продовжить працювати.</t>
+          <t>**❗️З 1 квітня 2025 року пропонують підвищити прожитковий мінімум, пенсію та «мінімалку»**, — законопроєкт [https://novyny.live/ekonomi/v-ukrayini-zaproponuvali-pidvishchiti-minimalnu-zarplatu-shcho-vidomo-232842.html]
+Згідно з документом, «мінімалку» можуть переглянути тричі:
+▪️з 1 квітня виплати зростуть — до 9 100 грн (55 грн за годину);
+▪️з 1 липня виплати зростуть ще на 1 000 грн — до 10 100 грн (61 грн за годину) ;
+▪️після фінального підвищення 1 жовтня, мінімальна зарплата в Україні становитиме — 11 184 грн (68 грн за годину).</t>
         </is>
       </c>
       <c r="G1162" s="3" t="inlineStr"/>
@@ -44621,17 +44642,18 @@
       </c>
       <c r="C1164" s="3" t="inlineStr">
         <is>
-          <t>2022-01-18</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="D1164" s="3" t="n">
-        <v>230</v>
+        <v>50445</v>
       </c>
       <c r="E1164" s="3" t="inlineStr"/>
       <c r="F1164" s="3" t="inlineStr">
         <is>
-          <t>**Россия может атаковать Украину в любой момент, - Белый дом
-**Источник [https://ru.interfax.com.ua/news/political/792415.html]</t>
+          <t>📉 Рейтинг Трампа падає: він б'є власний рекорд зі швидкого роздратування американських виборців, пише [https://www.economist.com/united-states/2025/04/16/donald-trumps-approval-rating-is-dropping] The Economist.
+Його рейтинг схвалення впав на 14 пунктів з моменту вступу на посаду, що перевищує падіння на п'ять пунктів за аналогічний період першого терміну. Майже кожен п'ятий з його виборців 2024 року не схвалює підхід до інфляції та цін.
+Серед іспаномовних виборців чисте схвалення Трампа складає мінус 37 пунктів, а серед молоді до 30 років — мінус 25. Ті самі, які забезпечили йому перемогу, тепер  обертаються проти нього.</t>
         </is>
       </c>
       <c r="G1164" s="3" t="inlineStr"/>
@@ -44734,16 +44756,18 @@
       </c>
       <c r="C1167" s="3" t="inlineStr">
         <is>
-          <t>2022-04-04</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="D1167" s="3" t="n">
-        <v>25192</v>
+        <v>66046</v>
       </c>
       <c r="E1167" s="3" t="inlineStr"/>
       <c r="F1167" s="3" t="inlineStr">
         <is>
-          <t>**Очень больно смотреть на то, что сделали с нашими людьми оккупанты. Им придется ответить за каждое военное преступление и все страдания, которые они принесли на нашу землю, — Зеленский опубликовал кадры поездки в Бучу</t>
+          <t>**«Полетять на голови ворога», — бійці 47 бригади показали велику партію дронів від братів Кличків 
+«Ми – бійці 47 Окремої механізованої бригади «Маґура». І сьогодні у нас надзвичайно приємна новина. З міста Києва від братів Кличків до нас прийшов надзвичайний подарунок – 100 FPV-дронів. Дякуємо міському голові Києва та усім українцям за потужну підтримку наших воїнів! Наближаємо перемогу разом!
+Наша бригада виконує бойові завдання на одній з найскладніших ділянок фронту – на Авдіївському напрямку. І для того, щоб нищити ворога, завдавати йому максимальне вогньове ураження та підтримувати нашу надзвичайну штурмову піхоту, нам потрібні засоби ураження, такі як  FPV-дрони. Кожен ворожий пес має розуміти, що на нашій українській землі його чекає тільки смерть та забуття», – йдеться у повідомленні 47 ОМБр.</t>
         </is>
       </c>
       <c r="G1167" s="3" t="inlineStr"/>
@@ -45037,19 +45061,18 @@
       </c>
       <c r="C1175" s="3" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="D1175" s="3" t="n">
-        <v>27142</v>
+        <v>35929</v>
       </c>
       <c r="E1175" s="3" t="inlineStr"/>
       <c r="F1175" s="3" t="inlineStr">
         <is>
-          <t>**Кількість постраждалих від російського ракетного терору столиці збільшилась до 7 осіб**, — мер Віталій Кличко. 
-Відбувається евакуація людей з будинку у Святошинському районі: в одній з квартир виявили не здетоновану бойову частину ракету.
-**UPD**: відомо про 1 загиблу жінку та 4 поранених, — КМВА.
-__На відео Софіївська Борщагівка.__</t>
+          <t>**⚡️Україна ****отримала $2,2 млрд від МВФ,** [https://t.me/c/1431180517/35699]** **— прем’єр-міністр Денис Шмигаль. 
+Це частина коштів, передбачених програмою EFF ($16 млрд). Для їх отримання країна виконала «важливу домашню роботу та пройшла у четвертий раунд — вперше у відносинах з МВФ».
+Перерахована сума піде на **фінансування критичних видатків бюджету, соцідопомог, зарплат медиків та учителів**.</t>
         </is>
       </c>
       <c r="G1175" s="3" t="inlineStr"/>
@@ -45105,21 +45128,24 @@
       </c>
       <c r="B1177" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1177" s="3" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>2021-11-28</t>
         </is>
       </c>
       <c r="D1177" s="3" t="n">
-        <v>50849</v>
+        <v>5964</v>
       </c>
       <c r="E1177" s="3" t="inlineStr"/>
       <c r="F1177" s="3" t="inlineStr">
         <is>
-          <t>⚡️ Україна впродовж року підготує [https://www.repubblica.it/esteri/2025/04/29/news/oleksiy_chernyshov_interview_vice_premier_ucraino-424154642/] закон, який дозволятиме мати подвійне громадянство. Емігранти матимуть такі ж права, як і ті, хто залишився в Україні, в тому числі й виборчі, — міністр національної єдності України.</t>
+          <t>**В Украине возрастет стоимость интернета**
+Серьезный рост тарифов на интернет прогнозируют в Интернет Ассоциации Украины.
+"Новый тренд – это "сотка" больше 200 грн/мес, и гигабит (1 Гбит/с) больше 300 грн/мес. И, думаю, тарифы повысятся еще у многих участников рынка", – заявили в Ассоциации.
+В ведомстве подчеркивают, что в больших городах подорожания не избежать. По данным экспертов, уже в ближайшее время провайдеры начнут уведомлять клиентов о подорожании стоимости услуг.</t>
         </is>
       </c>
       <c r="G1177" s="3" t="inlineStr"/>
@@ -45224,23 +45250,17 @@
       </c>
       <c r="C1180" s="3" t="inlineStr">
         <is>
-          <t>2024-02-20</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="D1180" s="3" t="n">
-        <v>70210</v>
+        <v>85203</v>
       </c>
       <c r="E1180" s="3" t="inlineStr"/>
       <c r="F1180" s="3" t="inlineStr">
         <is>
-          <t>**Особняк як Білий дім, годинник за $130 000, картини російських художників **— **журналісти розкрили декларацію Порошенка 
-Згідно з розслідуванням, Петро Олексійович один із небагатьох, хто добре заробив під час війни. Крім активів у 1 млрд доларів, нардеп був змушений показати елітний особняк на 1330 квадратів, який нагадує Білий дім у Вашингтоні. Також, Порошенко задекларував:
-📍з десяток годинників – вартістю від 25 до 130 тисяч доларів,
-📍предмети інтер'єру та меблів на 10 мільйонів у.о, де лише один комод коштує близько 60 тисяч доларів;
-📍колекцію картин відомих російських художників із пейзажами «великой российской империи»
-📍60 млн доларів та 300 мільйонів гривень Петро Олексійович тримає готівкою.
-Як повідомлялося, Петро Порошенко за рік війни збагатився на $226 млн і увійшов до трійки найбагатших олігархів, перескочивши з 12 на 3 позицію.
-Як зазначили [https://www.facebook.com/permalink.php?story_fbid=7865376226823680&amp;id=100000541433652] про декларацію Порошенка експерти, в Україні залишився динозавр "пшонкової ери" збагачується і любить все, що блистить.  І війна — не завада розкоші.</t>
+          <t>**❗️Нідерланди виступають за відсутність обмежень на удари по території рф, бо міжнародне право не визначає межі в 100 кілометрів для таких ударів, — міністр оборони Рубен Брекельманс**
+Країна вже передала нам свої F-16 та ракети до них.</t>
         </is>
       </c>
       <c r="G1180" s="3" t="inlineStr"/>
@@ -45744,16 +45764,20 @@
       </c>
       <c r="C1194" s="3" t="inlineStr">
         <is>
-          <t>2022-02-23</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="D1194" s="3" t="n">
-        <v>1680</v>
+        <v>278</v>
       </c>
       <c r="E1194" s="3" t="inlineStr"/>
       <c r="F1194" s="3" t="inlineStr">
         <is>
-          <t>А ещё я настоятельно прошу кидать волонтерам для помощи нашей армии [https://t.me/korotkoiyasn/1326]</t>
+          <t>Глава Госдепа Энтони Блинкен призвал украинцев «готовиться к тяжелым дня». 
+На фоне призывов [https://t.me/stranaua/23125] Зеленского не поддаваться панике это заявление смотрится на особенном контрасте.
+О тяжёлых днях, которые ждут украинцев Блинкен заявил еще до видео Зеленского - на совместной пресс-конференции с главой украинского МИД Дмитрием Кулебой.
+"Украина должна избегать каких-либо действий, которые помогут циничным усилиям России. Не позволяйте Москве разделить вас. Это значит, что лидеры внутри украинского правительства и за его пределами должны отбросить свои разногласия в пользу общего национального интереса и работать вместе, чтобы **подготовиться к тяжелым дням**", - заявил госсекретарь.
+В целом это очень антизеленское заявление. И по поводу тяжёлых дней (хотя Зе призывает не паниковать). И по поводу «отбросить разногласия». Понятно, что это намёк на уголовное преследование Порошенко.</t>
         </is>
       </c>
       <c r="G1194" s="3" t="inlineStr"/>
@@ -45774,16 +45798,16 @@
       </c>
       <c r="B1195" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1195" s="3" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="D1195" s="3" t="n">
-        <v>55713</v>
+        <v>8421</v>
       </c>
       <c r="E1195" s="3" t="inlineStr">
         <is>
@@ -45792,7 +45816,14 @@
       </c>
       <c r="F1195" s="3" t="inlineStr">
         <is>
-          <t>⚡ Під Києвом [https://t.me/+5s7ZDCzggiU2NjE6] **виявлено «рабів» із Узбекистану**: їх було загнано в експлуатаційну «вʼязницю» з нелюдськими умовами — **навіть туалет дозволявся за розкладом**, — місцева прокуратура.</t>
+          <t>💡 Ти ж сплачуєш податки. І уяви собі, що від держави можна щось та отримати. Але їм невигідно про це розповідати на широкий загал, і ти розумієш чому.
+Сиди тихо і:
+• Не отримаєш 50 тисяч податкового відрахування  які належать кожному
+• Не дізнаєшся як отримати 250 тис. грн на відкриття бізнесу
+• Ти навіть не дізнаєшся, що міг безкоштовно за 5 років у черги отримати квартиру!
+• Також не дізнаєшся як не платити кредити та мікрозайми під час війни
+Підпишись на t.me/businessua [https://t.me/+tPTOIpvA1HcxMWZi] — це канал економіста, який для громадян розкриває всі лазівки. Канал, який замінить тобі всі сайти та ресурси, про бізнес, інвестиції, IT.
+Забирай своє — t.me/businessua [https://t.me/+tPTOIpvA1HcxMWZi]</t>
         </is>
       </c>
       <c r="G1195" s="3" t="inlineStr"/>
@@ -47528,21 +47559,26 @@
       </c>
       <c r="B1241" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1241" s="3" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>2023-12-30</t>
         </is>
       </c>
       <c r="D1241" s="3" t="n">
-        <v>81910</v>
+        <v>25875</v>
       </c>
       <c r="E1241" s="3" t="inlineStr"/>
       <c r="F1241" s="3" t="inlineStr">
         <is>
-          <t>**❗️Завтра відключення світла застосовуватись не будуть, — Укренерго**</t>
+          <t>💙 Субота добігає кінця. Цей день був багатим на події і про них розкажемо вже зараз. **До марафону привітань підписників TU сьогодні долучається блогер та телеведучий** **Богдан Шелудяк.**
+• Наймасовіша ракетна атака: у 3-х містах [https://t.me/c/1431180517/25823] минув день жалоби, у Києві буде 1 січня. [https://t.me/c/1431180517/25831]
+• Ввечері ворог обстріляв Харків [https://t.me/c/1431180517/25867] — поцілив по центру міста.
+• «Бавовна» у Бєлгороді: [https://t.me/c/1431180517/25874] через роботу російської ППО загинули 18 людей.
+• 70 дронів на рф. [https://t.me/c/1431180517/25829] Сили оборони України вночі «кошмарили» великі міста ворога.
+• Ракетний скандал у Польщі: [https://t.me/c/1431180517/25842] військові не знайшли залишки ворожого залізяччя.</t>
         </is>
       </c>
       <c r="G1241" s="3" t="inlineStr"/>
@@ -47563,22 +47599,22 @@
       </c>
       <c r="B1242" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C1242" s="3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="D1242" s="3" t="n">
-        <v>30413</v>
+        <v>93427</v>
       </c>
       <c r="E1242" s="3" t="inlineStr"/>
       <c r="F1242" s="3" t="inlineStr">
         <is>
-          <t>Прикидались військовими і видурили благодійної допомоги та донатів на 1,7 млн грн, — Київська міська прокуратура. 
-Шахраї надсилали листи фондам та волонтерським організаціям від імені в/ч із запитом на отримання гуманітарки. У подальшому зловмисники одягали мілітарну форму та приїжджали на зустріч із представниками БФ. Винуватцям загрожує до 8 років позбавлення волі.</t>
+          <t>**Група банкірів на Львівщині привласнювала кошти клієнтів "Ощадбанка**"**, — Поліція та СБУ викрили схему**
+Працівники банку за вказівкою керівника змінювали фінансові номери клієнтів та перевипускали картки,** отримавши доступ до 50 рахунків і завдавши збитків понад 5 млн грн. **Фігурантам загрожує **до 6 років ув'язнення.**</t>
         </is>
       </c>
       <c r="G1242" s="3" t="inlineStr"/>
@@ -47604,17 +47640,17 @@
       </c>
       <c r="C1243" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="D1243" s="3" t="n">
-        <v>62137</v>
+        <v>64181</v>
       </c>
       <c r="E1243" s="3" t="inlineStr"/>
       <c r="F1243" s="3" t="inlineStr">
         <is>
-          <t>⚡️**У ****Києві** [https://t.me/kyiv_times_official]** гівно вже тече з вікон, але виїжджати не потрібно**: треба залишатися у столиці і рити ями для туалетів, — голова Деснянської РДА Максим Бахматов.
-«**Це неприємно, принизливо**, у столиці це неможливо, не по-європейськи — **ходити в пакети, ставити біотуалети, але треба виживати**», — додав він.</t>
+          <t>❗️**Іран погрожує Україні ударами**: «Через те, що Київ [https://t.me/kyiv_times_official] допомагає Ізраїлю, уся їхня країна — **законна ціль**», — Комісія з Нацбезпеки.
+**Підписатися на Times of Ukraine** [https://t.me/+5ExU141LNUthYjU6]</t>
         </is>
       </c>
       <c r="G1243" s="3" t="inlineStr"/>
@@ -48130,11 +48166,11 @@
       </c>
       <c r="C1257" s="3" t="inlineStr">
         <is>
-          <t>2022-04-20</t>
+          <t>2022-06-01</t>
         </is>
       </c>
       <c r="D1257" s="3" t="n">
-        <v>26632</v>
+        <v>30099</v>
       </c>
       <c r="E1257" s="3" t="inlineStr">
         <is>
@@ -48143,9 +48179,9 @@
       </c>
       <c r="F1257" s="3" t="inlineStr">
         <is>
-          <t>**Путин планирует провести принудительную мобилизацию на оккупированных территориях Запорожской и Херсонской областей — **[**ГУР
-**](https://www.facebook.com/DefenceIntelligenceofUkraine/posts/295521419425952)Псевдореферендумы на оккупированных территориях Запорожской и Херсонской областей преследуют цель объявления принудительной «мобилизации». 
-После её проведения ФСБ РФ планирует бросить «мобилизованных» украинцев на горячие участки фронта на штурм позиций ВСУ под контролем заградительных отрядов. Фактически это попытка уничтожить Украину руками украинцев.</t>
+          <t>**На брифинге Госсекретарь США Энтони Блинкен объявил о новой военной помощи Украине на $700 млн
+**В новый пакет военной помощи вошли, в частности, ракетные системы большой дальности, а также, по данным американских СМИ, другое крупнокалиберное оружие.
+При этом, как заявил Блинкен, системы большой дальности Украина обязалась не использовать для ударов по территории России.</t>
         </is>
       </c>
       <c r="G1257" s="3" t="inlineStr"/>
@@ -48693,23 +48729,23 @@
       </c>
       <c r="B1272" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1272" s="3" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2021-05-26</t>
         </is>
       </c>
       <c r="D1272" s="3" t="n">
-        <v>45642</v>
+        <v>4009</v>
       </c>
       <c r="E1272" s="3" t="inlineStr"/>
       <c r="F1272" s="3" t="inlineStr">
         <is>
-          <t>Лікар МСЕК із Вінниці володіє 13 квартирами, серед яких шестикімнатні апартаменти в центрі Києва, і трьома Tesla, стало відомо з [https://www.obozrevatel.com/ukr/ekonomika-glavnaya/analytics-and-forecasts/likar-msek-z-vinnitsi-kupiv-sobi-13-kvartir-ta-tri-tesla-na-druzhinu-pensionerku-oformiv-shestikimnatni-apratamenti-v-tsentri-kieva-rozsliduvannya-oboz-ua/amp.htm] розслідування Oboz UA.
-Лише одна з цих квартир може коштувати до $780 тис.
-Навіть враховуючи доходи від спільного бізнесу в енергетиці, масштаби їхніх статків викликають підозри, зокрема через дивно низькі ціни на деякі активи, такі як Tesla Model S, придбана за $2,1 тис., майже в 10 разів нижче її ринкової вартості.</t>
+          <t>**⚡️** **Офіційно! Кожен громадянин України може БЕЗКОШТОВНО отримати земельну ділянку
+**У статті 121 Земельного кодексу Конституції України [https://t.me/budnews_ua/396] закладено положення про те, що будь-який громадянин нашої країни має право на користування природними ресурсами.
+**Дізнавайся** як скористатися правом отримати **безкоштовно земельну ділянку** від держави – https://t.me/joinchat/OCVjOMqeUw9lMjY6 [https://t.me/budnews_ua/396]</t>
         </is>
       </c>
       <c r="G1272" s="3" t="inlineStr"/>
@@ -49559,25 +49595,24 @@
       </c>
       <c r="B1294" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1294" s="3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="D1294" s="3" t="n">
-        <v>24615</v>
+        <v>58572</v>
       </c>
       <c r="E1294" s="3" t="inlineStr"/>
       <c r="F1294" s="3" t="inlineStr">
         <is>
-          <t>**Червінський, який **вимагав [https://www.facebook.com/story.php?story_fbid=3732118063668651&amp;id=100006114824847&amp;mibextid=WUal2a&amp;rdid=Xk83JpgSGZDhKWiK]** $100 тис за контрабандні цигарки, повторить долю комбата Семенченка**
-Спроби зліпити з Червінського чергового упослідженого та використати у міжвидовій політичній боротьбі є очевидними. Згадайте Надію Савченко, яку спочатку всі разом носили на руках, а потім так само хейтили. Згадайте комбата-депутата Семена Семенченка. Так само сьогодні Порошенко та «Європейська солідарність» роблять політичного діяча вже з Червінського, намагаючись вдихнути бодай якесь життя у рейтинг, який ніяк не хоче підніматися. Саме тому заставу за нього внесла «Європейська солідарність».
-Хоча, як відомо, сам Червінський – доволі забезпечена людина. Наприклад, є фігурантом кримінального провадження про вимагання з комерсанта $100 тис за вирішення питання з контрабандними цигарками на одеській митниці - це відео облетіло інтернет.
-«Очевидно, що тепер він стає політичним боржником «ЄС». І тут знову напрошуються аналогії з Семенченком - як у стрімкому політичному злеті, так і в неминучому занепаді. Фактично Червінський повторює долю Семенченка і Ко», - зазначає блогер Сергій Іванов.
-Нагадаємо, що Червінський звинувачується у проведенні несанкціонованої «спецоперації», в результаті якої ворог отримав дані про розміщення нашої техніки на аеродромі «Канатове» і завдав по ньому ракетного удару. Через це загинув командир військової частини, поранені 17 військовослужбовців, пошкоджені кілька винищувачів та злітна смуга. У своїх свідченнях на суді Червінський заявив, що військові самі винні в тому, що постраждали від обстрілу.</t>
+          <t>**🎶Музика, що допомагає триматися.**
+89-річна фізикиня Раїса Дергачова живе одна у Києві і, інколи грає на піаніно у своїй холодній квартирі. Жінка зізнається, що переживати зиму в таких умовах дуже важко.
+«Звичайно, важко це пережити. Ми пережили Другу світову війну, а тепер знову маємо війну», — розповіла жінка.
+Джерело: vasilisastepanenko [https://www.instagram.com/vasilisastepanenko?igsh=MTNhemh2NHhxYnUzcQ%3D%3D]</t>
         </is>
       </c>
       <c r="G1294" s="3" t="inlineStr"/>
@@ -49790,19 +49825,17 @@
       </c>
       <c r="C1300" s="3" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-01-18</t>
         </is>
       </c>
       <c r="D1300" s="3" t="n">
-        <v>86222</v>
+        <v>68016</v>
       </c>
       <c r="E1300" s="3" t="inlineStr"/>
       <c r="F1300" s="3" t="inlineStr">
         <is>
-          <t>Можна скільки завгодно сміятися, чи критикувати заяви «експертів з телика», які прогнозують важку зиму, чи розповідають про можливі атаки рф на ті, чи інші енергетичні об’єкти, але є факт того, що русня дійсно готується бити по об'єктах ядерної енергетики України. Це підтверджує наша розвідка. 
-Зрозуміло, що кожен експерт має свою думку і робить власний прогноз, у багатьох випадках ці прогнози у кожного з них різні. Одні запевняють, що все буде добре, а інші, що все буде погано. Більшість з нас сприймає це за звичайні «лякалки», але є факт, проти нас воюють нікчемні російські терористи, які готові на все, аби залишити Україну без світла та тепла взимку.
-Тому кому вірити кожен з вас хай обирає сам, але готуватися до важкої зими потрібно всім і вже зараз. Ми за ці роки не були у тотальному блекауті лише фактично завдяки нашим АЕС, тому логічно, що рф хоче силою зупинити нашу атомну енергетику.
-Надіємся на краще, але готуємось до гіршого 🤝</t>
+          <t>**​США завдали нову серію ударів по об’єктах бойовиків-хуситів на території Ємену, що є четвертим таким ударом за останній тиждень**
+Цілями ударів стали пускові установки хуситів із зарядженими у них 14 ракетами, повідомило Центральне командування армії США.</t>
         </is>
       </c>
       <c r="G1300" s="3" t="inlineStr"/>
@@ -50303,21 +50336,23 @@
       </c>
       <c r="B1314" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1314" s="3" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
+          <t>2024-01-11</t>
         </is>
       </c>
       <c r="D1314" s="3" t="n">
-        <v>89375</v>
+        <v>26595</v>
       </c>
       <c r="E1314" s="3" t="inlineStr"/>
       <c r="F1314" s="3" t="inlineStr">
         <is>
-          <t>**Остін відмовився задовольнити прохання Зеленського про те, щоб Україна отримала ракету ATACMS першою, замість інших країн, які теж замовили ці ракети, — ****WSJ** [https://www.wsj.com/politics/national-security/u-s-struggles-to-rush-weapons-to-ukraine-before-trump-takes-office-dfabb1fd]** з посиланням на американських чиновників</t>
+          <t>⚡️**Кабінет Міністрів офіційно відкликав законопроєкт про мобілізацію для подальшого доопрацювання**, — представник Уряду у ВР Тарас Мельничук.
+Статус — «знято з розгляду». Ймовірно, найближчим часом його не ухвалять.
+У Міноборони підготували вже нову редакцію, — Рустем Умєров.</t>
         </is>
       </c>
       <c r="G1314" s="3" t="inlineStr"/>
@@ -50414,23 +50449,17 @@
       </c>
       <c r="C1317" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="D1317" s="3" t="n">
-        <v>52681</v>
+        <v>60660</v>
       </c>
       <c r="E1317" s="3" t="inlineStr"/>
       <c r="F1317" s="3" t="inlineStr">
         <is>
-          <t>❗️Найстрашніша ніч для Вінниці: [https://t.me/+-OsopRCAAN5mODZi] **які наслідки масованого удару**? Вибухи лунали в багатьох містах України. 
-⭕️**Вінниця** [https://t.me/+-OsopRCAAN5mODZi]: [https://t.me/+-OsopRCAAN5mODZi] місто пережило **одну з найбільших атак** БПЛА за весь час. Є влучання в цивільну інфраструктуру, пошкоджені житлові будинки — уже **7  поранених**. Місто затягнув чорний дим, людей просять **терміново позачиняти вікна**, — ОВА.
-⭕️**Кривий Ріг** [https://t.me/+iiek78uVr8dmMTcy]: [https://t.me/+iiek78uVr8dmMTcy] було **понад 20 вибухів**, на місто летіли балістична ракета і 28 дронів одночасно. Є багато пожеж, **масштабні відключення світла**, зруйновано підприємство. Відомо про 1 пораненого, — МВА.
-⭕️**Харків** [https://t.me/+je62I9ADjydhZjFi]: [https://t.me/+je62I9ADjydhZjFi] у місті лунало **мінімум 17 вибухів** вночі. Більшість ударів — по підприємству, **є постраждалі**, — місцеві ЗМІ.
-⭕️**Одещина** [https://t.me/+4zHYPnfcxOYxOGIy]: [https://t.me/+4zHYPnfcxOYxOGIy] рф атакувала дронами Ізмаїльський район, **уражено об'єкт інфраструктури**, — ОВА.
-⭕️**Суми** [https://t.me/+KhEqiyRMYWU0MzQy]: [https://t.me/+KhEqiyRMYWU0MzQy] було **влучання по підприємству**. Також пошкоджені адмінбудівля, авто і приватні будинки, — ОВА.
-⭕️**Краматорськ**: ворожий БПЛА **влучив у багатоповерхівку**. Попередньо, без постраждалих, — МВА.
-⭕️**Збито** **198/400 БПЛА** вночі над Україною, ще 145 дронів — локаційно втрачені. Є влучання **в 12 локаціях**, — ПС.</t>
+          <t>❗️План кінця війни та гарантії безпеки **тепер узгоджено на 90% і 100% (!)**, — Зеленський.
+«**Ми дуже-дуже наблизилися до кінця війни**, а всі думали, що це нереально», — Трамп.</t>
         </is>
       </c>
       <c r="G1317" s="3" t="inlineStr"/>
@@ -50578,22 +50607,22 @@
       </c>
       <c r="B1321" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>UaOnlii</t>
         </is>
       </c>
       <c r="C1321" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="D1321" s="3" t="n">
-        <v>19037</v>
+        <v>99474</v>
       </c>
       <c r="E1321" s="3" t="inlineStr"/>
       <c r="F1321" s="3" t="inlineStr">
         <is>
-          <t>В Одесі під завалами **виявили тіло загиблого**, — ОВА. Це охоронець цивільної будівлі. Йому був 21 рік.
-**UPD:** кількість постраждалих збільшилась до 8 людей.</t>
+          <t>❗️**Ми не ввели санкції проти Росії, тому що сподіваємося зблизити конфліктуючі сторони, — Рубіо **
+Тобто проти рф санкції не вводимо, а Україні зупиняємо військову допомогу ? 🗿</t>
         </is>
       </c>
       <c r="G1321" s="3" t="inlineStr"/>
@@ -50797,16 +50826,16 @@
       </c>
       <c r="B1327" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1327" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="D1327" s="3" t="n">
-        <v>42827</v>
+        <v>55040</v>
       </c>
       <c r="E1327" s="3" t="inlineStr">
         <is>
@@ -50815,7 +50844,7 @@
       </c>
       <c r="F1327" s="3" t="inlineStr">
         <is>
-          <t>❗️Увага! Можливий загальний залп з 24 ракет «Калібр»: **рф вивела 6 ракетоносіїв у Чорне море,** — ВМС.</t>
+          <t>У мене немає часу **ні на каву, ні на блоги.** Просто світла не буде, — Зеленський.</t>
         </is>
       </c>
       <c r="G1327" s="3" t="inlineStr"/>
@@ -50951,19 +50980,1306 @@
       </c>
       <c r="B1331" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1331" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2020-11-06</t>
         </is>
       </c>
       <c r="D1331" s="3" t="n">
-        <v>56574</v>
+        <v>2376</v>
       </c>
       <c r="E1331" s="3" t="inlineStr"/>
       <c r="F1331" s="3" t="inlineStr">
+        <is>
+          <t>Украине грозит уничтожение всех антикоррупционных органов
+**В Национальном антикоррупционном бюро Украины заявили о риске уничтожения любого антикоррупционного органа и потребовали немедленно урегулировать ситуацию, которая сложилась из-за решений Конституционного суда. Об этом говорится в обнародованном в пятницу, 6 ноября, заявлении НАБУ.
+В Бюро выразили обеспокоенность решениями КСУ в течение 2019-2020 годов в вопросах борьбы с коррупцией.
+"Последствиями таких решений является системное ослабление институциональной способности органов, призванных разоблачать коррупцию, и освобождение от ответственности лиц, причастных к нанесению ущерба интересам государства в особо крупных размерах", - сообщили в НАБУ.
+Отмечается, что из-за решений КСУ потеряна возможность возместить миллиарды убытков, которые были нанесены из-за коррупции.</t>
+        </is>
+      </c>
+      <c r="G1331" s="3" t="inlineStr"/>
+      <c r="H1331" s="3" t="inlineStr"/>
+      <c r="I1331" s="3" t="inlineStr"/>
+      <c r="J1331" s="3" t="inlineStr"/>
+      <c r="K1331" s="3" t="inlineStr"/>
+      <c r="L1331" s="3" t="inlineStr"/>
+      <c r="M1331" s="3" t="inlineStr"/>
+      <c r="N1331" s="3" t="inlineStr"/>
+      <c r="O1331" s="3" t="inlineStr"/>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="3" t="inlineStr">
+        <is>
+          <t>V1331</t>
+        </is>
+      </c>
+      <c r="B1332" s="3" t="inlineStr">
+        <is>
+          <t>times_ukraina</t>
+        </is>
+      </c>
+      <c r="C1332" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-30</t>
+        </is>
+      </c>
+      <c r="D1332" s="3" t="n">
+        <v>16324</v>
+      </c>
+      <c r="E1332" s="3" t="inlineStr"/>
+      <c r="F1332" s="3" t="inlineStr">
+        <is>
+          <t>«Бл*ха, він нападає! Пальця відгризе!» Наші воїни врятували рідкісну червонокнижну тварину – перегузню (мармурового тхора). Ареал поширення цього звіра в степах Донеччини, Луганщини та Запоріжжя, де ведуться найактивніші бойові дії. Таких хижих ссавців в Україні ~100 особин. Вид на межі зникнення.</t>
+        </is>
+      </c>
+      <c r="G1332" s="3" t="inlineStr"/>
+      <c r="H1332" s="3" t="inlineStr"/>
+      <c r="I1332" s="3" t="inlineStr"/>
+      <c r="J1332" s="3" t="inlineStr"/>
+      <c r="K1332" s="3" t="inlineStr"/>
+      <c r="L1332" s="3" t="inlineStr"/>
+      <c r="M1332" s="3" t="inlineStr"/>
+      <c r="N1332" s="3" t="inlineStr"/>
+      <c r="O1332" s="3" t="inlineStr"/>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="3" t="inlineStr">
+        <is>
+          <t>V1332</t>
+        </is>
+      </c>
+      <c r="B1333" s="3" t="inlineStr">
+        <is>
+          <t>batalionmonako</t>
+        </is>
+      </c>
+      <c r="C1333" s="3" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="D1333" s="3" t="n">
+        <v>2658</v>
+      </c>
+      <c r="E1333" s="3" t="inlineStr"/>
+      <c r="F1333" s="3" t="inlineStr">
+        <is>
+          <t>+ ще одна ракета.
+Всього - п’ять.
+Інформація про 12 - вброс.</t>
+        </is>
+      </c>
+      <c r="G1333" s="3" t="inlineStr"/>
+      <c r="H1333" s="3" t="inlineStr"/>
+      <c r="I1333" s="3" t="inlineStr"/>
+      <c r="J1333" s="3" t="inlineStr"/>
+      <c r="K1333" s="3" t="inlineStr"/>
+      <c r="L1333" s="3" t="inlineStr"/>
+      <c r="M1333" s="3" t="inlineStr"/>
+      <c r="N1333" s="3" t="inlineStr"/>
+      <c r="O1333" s="3" t="inlineStr"/>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="3" t="inlineStr">
+        <is>
+          <t>V1333</t>
+        </is>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
+        <is>
+          <t>batalionmonako</t>
+        </is>
+      </c>
+      <c r="C1334" s="3" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="D1334" s="3" t="n">
+        <v>45734</v>
+      </c>
+      <c r="E1334" s="3" t="inlineStr"/>
+      <c r="F1334" s="3" t="inlineStr">
+        <is>
+          <t>Реінтеграція військових та «пакет демобілізації» — що бізнес радив державі на VІІI Міжнародний ветеранський форум «Україна. Ветерани. Безпека». 
+Ветеранський форум обʼєднав перших представників держави. Зокрема й президента Володимира Зеленського, Генсека НАТО Марко Рютте, українських військових, ветеранів та представників ветеранського бізнесу.
+Одна з ключових тем форуму — реінтеграція військових. Представник волонтерсько-ветеранської компанії «Генерал Черешня» Андрій Лавренович запропонував державі сформувати «пакет демобілізації» — комплекс послуг та дій, які має отримати кожен демобілізований військовий. 
+В «пакет» мають увійти: психологічна допомога, соціальні пільги, безкоштовний доступ до навчання, обовʼязкове працевлаштування. За словами Андрія, держава має забезпечити соціальну частину, тоді як бізнес може та готовий інтегруватися в програми освіти, психологічної реабілітації та працевлаштування ветеранів. 
+В компанії «Генерал Черешня», один зі співзасновників якої є ветеран, наразі працює близько 20% ветеранів. Ще близько 40% співробітників прийшли з волонтерського руху. Андрій Лавренович вказує, [https://www.facebook.com/share/v/14ML1g7XtPL/?mibextid=wwXIfr] що саме ці категорії людей мають стати успішними та ефективними менеджерами майбутньої України.</t>
+        </is>
+      </c>
+      <c r="G1334" s="3" t="inlineStr"/>
+      <c r="H1334" s="3" t="inlineStr"/>
+      <c r="I1334" s="3" t="inlineStr"/>
+      <c r="J1334" s="3" t="inlineStr"/>
+      <c r="K1334" s="3" t="inlineStr"/>
+      <c r="L1334" s="3" t="inlineStr"/>
+      <c r="M1334" s="3" t="inlineStr"/>
+      <c r="N1334" s="3" t="inlineStr"/>
+      <c r="O1334" s="3" t="inlineStr"/>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="3" t="inlineStr">
+        <is>
+          <t>V1334</t>
+        </is>
+      </c>
+      <c r="B1335" s="3" t="inlineStr">
+        <is>
+          <t>batalionmonako</t>
+        </is>
+      </c>
+      <c r="C1335" s="3" t="inlineStr">
+        <is>
+          <t>2022-11-23</t>
+        </is>
+      </c>
+      <c r="D1335" s="3" t="n">
+        <v>3997</v>
+      </c>
+      <c r="E1335" s="3" t="inlineStr"/>
+      <c r="F1335" s="3" t="inlineStr">
+        <is>
+          <t>**У Молдові масові відключення електроенергії **внаслідок ракетних ударів РФ по Україні, — віцепремʼєр країни Спину.</t>
+        </is>
+      </c>
+      <c r="G1335" s="3" t="inlineStr"/>
+      <c r="H1335" s="3" t="inlineStr"/>
+      <c r="I1335" s="3" t="inlineStr"/>
+      <c r="J1335" s="3" t="inlineStr"/>
+      <c r="K1335" s="3" t="inlineStr"/>
+      <c r="L1335" s="3" t="inlineStr"/>
+      <c r="M1335" s="3" t="inlineStr"/>
+      <c r="N1335" s="3" t="inlineStr"/>
+      <c r="O1335" s="3" t="inlineStr"/>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="3" t="inlineStr">
+        <is>
+          <t>V1335</t>
+        </is>
+      </c>
+      <c r="B1336" s="3" t="inlineStr">
+        <is>
+          <t>lachentyt</t>
+        </is>
+      </c>
+      <c r="C1336" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="D1336" s="3" t="n">
+        <v>44720</v>
+      </c>
+      <c r="E1336" s="3" t="inlineStr"/>
+      <c r="F1336" s="3" t="inlineStr">
+        <is>
+          <t>Рятувальні роботи на місці удару по Інституту зв'язку в Полтаві завершено, — ДСНС.
+55 людей загинуло, 328 постраждало. Проводиться ідентифікація рештків тіл.</t>
+        </is>
+      </c>
+      <c r="G1336" s="3" t="inlineStr"/>
+      <c r="H1336" s="3" t="inlineStr"/>
+      <c r="I1336" s="3" t="inlineStr"/>
+      <c r="J1336" s="3" t="inlineStr"/>
+      <c r="K1336" s="3" t="inlineStr"/>
+      <c r="L1336" s="3" t="inlineStr"/>
+      <c r="M1336" s="3" t="inlineStr"/>
+      <c r="N1336" s="3" t="inlineStr"/>
+      <c r="O1336" s="3" t="inlineStr"/>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="3" t="inlineStr">
+        <is>
+          <t>V1336</t>
+        </is>
+      </c>
+      <c r="B1337" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1337" s="3" t="inlineStr">
+        <is>
+          <t>2023-03-08</t>
+        </is>
+      </c>
+      <c r="D1337" s="3" t="n">
+        <v>47772</v>
+      </c>
+      <c r="E1337" s="3" t="inlineStr"/>
+      <c r="F1337" s="3" t="inlineStr">
+        <is>
+          <t>**Грузинские власти не выполнили требований протестующих: люди окружают парламент, — СМИ
+**Во внутреннем дворе парламента уже собираются силовики. Завтра митингующие планируют пикетировать парламент и помешать работе законодательного органа.</t>
+        </is>
+      </c>
+      <c r="G1337" s="3" t="inlineStr"/>
+      <c r="H1337" s="3" t="inlineStr"/>
+      <c r="I1337" s="3" t="inlineStr"/>
+      <c r="J1337" s="3" t="inlineStr"/>
+      <c r="K1337" s="3" t="inlineStr"/>
+      <c r="L1337" s="3" t="inlineStr"/>
+      <c r="M1337" s="3" t="inlineStr"/>
+      <c r="N1337" s="3" t="inlineStr"/>
+      <c r="O1337" s="3" t="inlineStr"/>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="3" t="inlineStr">
+        <is>
+          <t>V1337</t>
+        </is>
+      </c>
+      <c r="B1338" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1338" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-10</t>
+        </is>
+      </c>
+      <c r="D1338" s="3" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E1338" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1338" s="3" t="inlineStr">
+        <is>
+          <t>Ситуация в метро 😏**Как думаете ,должны  пускать всех или выборочно⁉️
+__У «безхатченки»,кстати,был действующий билет.
+__**Киев INFO** [https://t.me/+3iBBG0L0rlM5MDU6] **| ****Прислать новость** [https://t.me/nikitos077]</t>
+        </is>
+      </c>
+      <c r="G1338" s="3" t="inlineStr"/>
+      <c r="H1338" s="3" t="inlineStr"/>
+      <c r="I1338" s="3" t="inlineStr"/>
+      <c r="J1338" s="3" t="inlineStr"/>
+      <c r="K1338" s="3" t="inlineStr"/>
+      <c r="L1338" s="3" t="inlineStr"/>
+      <c r="M1338" s="3" t="inlineStr"/>
+      <c r="N1338" s="3" t="inlineStr"/>
+      <c r="O1338" s="3" t="inlineStr"/>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="3" t="inlineStr">
+        <is>
+          <t>V1338</t>
+        </is>
+      </c>
+      <c r="B1339" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1339" s="3" t="inlineStr">
+        <is>
+          <t>2021-10-05</t>
+        </is>
+      </c>
+      <c r="D1339" s="3" t="n">
+        <v>18885</v>
+      </c>
+      <c r="E1339" s="3" t="inlineStr"/>
+      <c r="F1339" s="3" t="inlineStr">
+        <is>
+          <t>**#offtop**** 🇮🇹 💦 В Италии мощнейшее наводнение: отменили даже выборы **
+Больше всего страдает Лигурия (Северный регион). Вода затопила улицы, размыла дороги; закрыты магазины, школы и даже отменены местные выборы.
+**Мечта побывать в Италии становится более реальной 😌</t>
+        </is>
+      </c>
+      <c r="G1339" s="3" t="inlineStr"/>
+      <c r="H1339" s="3" t="inlineStr"/>
+      <c r="I1339" s="3" t="inlineStr"/>
+      <c r="J1339" s="3" t="inlineStr"/>
+      <c r="K1339" s="3" t="inlineStr"/>
+      <c r="L1339" s="3" t="inlineStr"/>
+      <c r="M1339" s="3" t="inlineStr"/>
+      <c r="N1339" s="3" t="inlineStr"/>
+      <c r="O1339" s="3" t="inlineStr"/>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="3" t="inlineStr">
+        <is>
+          <t>V1339</t>
+        </is>
+      </c>
+      <c r="B1340" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1340" s="3" t="inlineStr">
+        <is>
+          <t>2023-11-25</t>
+        </is>
+      </c>
+      <c r="D1340" s="3" t="n">
+        <v>38874</v>
+      </c>
+      <c r="E1340" s="3" t="inlineStr"/>
+      <c r="F1340" s="3" t="inlineStr">
+        <is>
+          <t>❗️КМВА: Четверта атака ворожих БПЛА на Київ за цей місяць.** Цей напад дронів став наймасованішим з початку повномасштабного вторгнення!** У столиці тривога тривала понад 6 годин. Символічно, що рашисти (нащадки тоталітарної радянського режиму) здійснили цю атаку в День пам’яті жертв голодоморів. Так вони продовжують геноцид України та українців.
+За попередніми даними противник вкотре застосував баражуючі боєприпаси типу «Shahed». БпЛА заходили на Київ хвилями, численними групами, з різних напрямків, постійно змінюючи курс за вектором руху. 
+**Силами та засобами ППО було уражено майже п'ять десятків повітряних цілей!** (остаточні підсумкові дані щодо типу та кількості оприлюднять Повітряні Сили). 
+За попередніми даними, внаслідок збиття ворожих дронів зафіксовано падіння уламків в різних районах міста: 
+-  у Солом'янському районі внаслідок падіння уламків є двоє постраждалих - в обох гостра реакція на стрес, без госпіталізації. Також в цьому районі, у 5-поверховому будинку сталося руйнування на другому поверсі, вибиті шибки з першого по п’ятий поверх. В будівлі було заблоковано дві жінки. Також в Солом'янському районі сталося загоряння на території дитячого садочку і на іншій локації – в нежитловому приміщенні на площі 100 м2..
+-  у Дніпровському районі міста уламки впали на верхні поверхи багатоповерхівки, сталося задимлення.
+-  у Голосіївському районі уламки упали на зону зелених насаджень, без потерпілих.
+-  у Печерському районі - також на незабудовану територію. Попередньо без наслідків.
+За інформацією Міненерго, в результаті атаки дронів, у Києві залишалися без світла 77 житлових будинків та 120 установ. Тривають роботи з відновлення.
+Інформація оновлюється і уточнюється.
+Дякуйте воїнам ППО. 
+Вірте в ЗСУ!
+👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
+        </is>
+      </c>
+      <c r="G1340" s="3" t="inlineStr"/>
+      <c r="H1340" s="3" t="inlineStr"/>
+      <c r="I1340" s="3" t="inlineStr"/>
+      <c r="J1340" s="3" t="inlineStr"/>
+      <c r="K1340" s="3" t="inlineStr"/>
+      <c r="L1340" s="3" t="inlineStr"/>
+      <c r="M1340" s="3" t="inlineStr"/>
+      <c r="N1340" s="3" t="inlineStr"/>
+      <c r="O1340" s="3" t="inlineStr"/>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="3" t="inlineStr">
+        <is>
+          <t>V1340</t>
+        </is>
+      </c>
+      <c r="B1341" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1341" s="3" t="inlineStr">
+        <is>
+          <t>2022-09-24</t>
+        </is>
+      </c>
+      <c r="D1341" s="3" t="n">
+        <v>61108</v>
+      </c>
+      <c r="E1341" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1341" s="3" t="inlineStr">
+        <is>
+          <t>**Российских командиров не волнуют жизни россиян –** им просто нужно заполнить пустые места, – Владимир Зеленский обратился к россиянам.
+«Кем будут заполняться эти места, вашу власть не волнует. Хоть молодыми айтишниками, которые вообще не служили, хоть пенсионерами, которые служили разве что в советской армии.
+Для вас наступил ключевой момент: именно сейчас решается, закончится ли ваша жизнь».</t>
+        </is>
+      </c>
+      <c r="G1341" s="3" t="inlineStr"/>
+      <c r="H1341" s="3" t="inlineStr"/>
+      <c r="I1341" s="3" t="inlineStr"/>
+      <c r="J1341" s="3" t="inlineStr"/>
+      <c r="K1341" s="3" t="inlineStr"/>
+      <c r="L1341" s="3" t="inlineStr"/>
+      <c r="M1341" s="3" t="inlineStr"/>
+      <c r="N1341" s="3" t="inlineStr"/>
+      <c r="O1341" s="3" t="inlineStr"/>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="3" t="inlineStr">
+        <is>
+          <t>V1341</t>
+        </is>
+      </c>
+      <c r="B1342" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1342" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="D1342" s="3" t="n">
+        <v>53305</v>
+      </c>
+      <c r="E1342" s="3" t="inlineStr"/>
+      <c r="F1342" s="3" t="inlineStr">
+        <is>
+          <t>❗️Блекаутів не уникнути: **Україна близька до відключень електроенергії**, — експерт Інституту енергетичних стратегій Юрій Корольчук.
+Через два тижні **зростатиме споживання.</t>
+        </is>
+      </c>
+      <c r="G1342" s="3" t="inlineStr"/>
+      <c r="H1342" s="3" t="inlineStr"/>
+      <c r="I1342" s="3" t="inlineStr"/>
+      <c r="J1342" s="3" t="inlineStr"/>
+      <c r="K1342" s="3" t="inlineStr"/>
+      <c r="L1342" s="3" t="inlineStr"/>
+      <c r="M1342" s="3" t="inlineStr"/>
+      <c r="N1342" s="3" t="inlineStr"/>
+      <c r="O1342" s="3" t="inlineStr"/>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="3" t="inlineStr">
+        <is>
+          <t>V1342</t>
+        </is>
+      </c>
+      <c r="B1343" s="3" t="inlineStr">
+        <is>
+          <t>vanek_nikolaev</t>
+        </is>
+      </c>
+      <c r="C1343" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-19</t>
+        </is>
+      </c>
+      <c r="D1343" s="3" t="n">
+        <v>18493</v>
+      </c>
+      <c r="E1343" s="3" t="inlineStr"/>
+      <c r="F1343" s="3" t="inlineStr">
+        <is>
+          <t>2 петуха крутятся в воздухе на левом берегу Херсонской области</t>
+        </is>
+      </c>
+      <c r="G1343" s="3" t="inlineStr"/>
+      <c r="H1343" s="3" t="inlineStr"/>
+      <c r="I1343" s="3" t="inlineStr"/>
+      <c r="J1343" s="3" t="inlineStr"/>
+      <c r="K1343" s="3" t="inlineStr"/>
+      <c r="L1343" s="3" t="inlineStr"/>
+      <c r="M1343" s="3" t="inlineStr"/>
+      <c r="N1343" s="3" t="inlineStr"/>
+      <c r="O1343" s="3" t="inlineStr"/>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="3" t="inlineStr">
+        <is>
+          <t>V1343</t>
+        </is>
+      </c>
+      <c r="B1344" s="3" t="inlineStr">
+        <is>
+          <t>times_ukraina</t>
+        </is>
+      </c>
+      <c r="C1344" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="D1344" s="3" t="n">
+        <v>58337</v>
+      </c>
+      <c r="E1344" s="3" t="inlineStr"/>
+      <c r="F1344" s="3" t="inlineStr">
+        <is>
+          <t>⚡️Будь-які спроби повʼязати мою роботу в Міноборони **з «впливом» бізнесмена Тимура Міндіча — безпідставні**, — секретар РНБО Рустем Умєров.</t>
+        </is>
+      </c>
+      <c r="G1344" s="3" t="inlineStr"/>
+      <c r="H1344" s="3" t="inlineStr"/>
+      <c r="I1344" s="3" t="inlineStr"/>
+      <c r="J1344" s="3" t="inlineStr"/>
+      <c r="K1344" s="3" t="inlineStr"/>
+      <c r="L1344" s="3" t="inlineStr"/>
+      <c r="M1344" s="3" t="inlineStr"/>
+      <c r="N1344" s="3" t="inlineStr"/>
+      <c r="O1344" s="3" t="inlineStr"/>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="3" t="inlineStr">
+        <is>
+          <t>V1344</t>
+        </is>
+      </c>
+      <c r="B1345" s="3" t="inlineStr">
+        <is>
+          <t>batalionmonako</t>
+        </is>
+      </c>
+      <c r="C1345" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="D1345" s="3" t="n">
+        <v>13069</v>
+      </c>
+      <c r="E1345" s="3" t="inlineStr"/>
+      <c r="F1345" s="3" t="inlineStr">
+        <is>
+          <t>❗️❗️**Раміна раз‘й*бує Гордона, що той до війни працював проти Президента 🤯**</t>
+        </is>
+      </c>
+      <c r="G1345" s="3" t="inlineStr"/>
+      <c r="H1345" s="3" t="inlineStr"/>
+      <c r="I1345" s="3" t="inlineStr"/>
+      <c r="J1345" s="3" t="inlineStr"/>
+      <c r="K1345" s="3" t="inlineStr"/>
+      <c r="L1345" s="3" t="inlineStr"/>
+      <c r="M1345" s="3" t="inlineStr"/>
+      <c r="N1345" s="3" t="inlineStr"/>
+      <c r="O1345" s="3" t="inlineStr"/>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="3" t="inlineStr">
+        <is>
+          <t>V1345</t>
+        </is>
+      </c>
+      <c r="B1346" s="3" t="inlineStr">
+        <is>
+          <t>vanek_nikolaev</t>
+        </is>
+      </c>
+      <c r="C1346" s="3" t="inlineStr">
+        <is>
+          <t>2024-11-25</t>
+        </is>
+      </c>
+      <c r="D1346" s="3" t="n">
+        <v>28873</v>
+      </c>
+      <c r="E1346" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1346" s="3" t="inlineStr">
+        <is>
+          <t>угроза баллистики с воронежской тупорылой республики актуальна
+Сумчата - могут быть повторные запуски!</t>
+        </is>
+      </c>
+      <c r="G1346" s="3" t="inlineStr"/>
+      <c r="H1346" s="3" t="inlineStr"/>
+      <c r="I1346" s="3" t="inlineStr"/>
+      <c r="J1346" s="3" t="inlineStr"/>
+      <c r="K1346" s="3" t="inlineStr"/>
+      <c r="L1346" s="3" t="inlineStr"/>
+      <c r="M1346" s="3" t="inlineStr"/>
+      <c r="N1346" s="3" t="inlineStr"/>
+      <c r="O1346" s="3" t="inlineStr"/>
+    </row>
+    <row r="1347">
+      <c r="A1347" s="3" t="inlineStr">
+        <is>
+          <t>V1346</t>
+        </is>
+      </c>
+      <c r="B1347" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1347" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-19</t>
+        </is>
+      </c>
+      <c r="D1347" s="3" t="n">
+        <v>3702</v>
+      </c>
+      <c r="E1347" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1347" s="3" t="inlineStr">
+        <is>
+          <t>**⚡️Смертельное ДТП:рейсовый автобус Гюнсел, следовавший по маршруту Киев-Одесса выехал на встречную полосу, снес 3 авто, дерево и влетел в магазин
+**По информации полиции, сегодня утром водитель автобуса MAN, не справился с управлением, в результате чего выехал на встречную полосу, где столкнулся с автомобилями Hyundai Tucson, Daewoo Lanos, Hyundai SantaFe, Chevrolet Aveo.
+**По инерции, продолжив движение, автобус выехал на тротуар и совершил наезд на дерево и здание.
+По словам медиков у водителя прямо за рулём случился инсульт, он скончался в карете скорой.
+**Пострадавшему водителю Chevrolet и пассажирам автобуса была оказана помощь на месте.</t>
+        </is>
+      </c>
+      <c r="G1347" s="3" t="inlineStr"/>
+      <c r="H1347" s="3" t="inlineStr"/>
+      <c r="I1347" s="3" t="inlineStr"/>
+      <c r="J1347" s="3" t="inlineStr"/>
+      <c r="K1347" s="3" t="inlineStr"/>
+      <c r="L1347" s="3" t="inlineStr"/>
+      <c r="M1347" s="3" t="inlineStr"/>
+      <c r="N1347" s="3" t="inlineStr"/>
+      <c r="O1347" s="3" t="inlineStr"/>
+    </row>
+    <row r="1348">
+      <c r="A1348" s="3" t="inlineStr">
+        <is>
+          <t>V1347</t>
+        </is>
+      </c>
+      <c r="B1348" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1348" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-01</t>
+        </is>
+      </c>
+      <c r="D1348" s="3" t="n">
+        <v>71147</v>
+      </c>
+      <c r="E1348" s="3" t="inlineStr"/>
+      <c r="F1348" s="3" t="inlineStr">
+        <is>
+          <t>❗️**Рецептам таки бути! У частині регіонів України** рецептурні препарати будуть відпускати лише так, – МОЗ [https://life.pravda.com.ua/health/2023/04/1/253625/].
+Без рецепта їх можна буде купити у зоні бойових дій, під окупацією або в оточенні. У «‎мирних»‎ областях – ні. Нова постанова КМУ коригує норму про вільний продаж [https://t.me/truexanewsua/71130] ліків під час воєнного стану.</t>
+        </is>
+      </c>
+      <c r="G1348" s="3" t="inlineStr"/>
+      <c r="H1348" s="3" t="inlineStr"/>
+      <c r="I1348" s="3" t="inlineStr"/>
+      <c r="J1348" s="3" t="inlineStr"/>
+      <c r="K1348" s="3" t="inlineStr"/>
+      <c r="L1348" s="3" t="inlineStr"/>
+      <c r="M1348" s="3" t="inlineStr"/>
+      <c r="N1348" s="3" t="inlineStr"/>
+      <c r="O1348" s="3" t="inlineStr"/>
+    </row>
+    <row r="1349">
+      <c r="A1349" s="3" t="inlineStr">
+        <is>
+          <t>V1348</t>
+        </is>
+      </c>
+      <c r="B1349" s="3" t="inlineStr">
+        <is>
+          <t>lachentyt</t>
+        </is>
+      </c>
+      <c r="C1349" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-17</t>
+        </is>
+      </c>
+      <c r="D1349" s="3" t="n">
+        <v>47213</v>
+      </c>
+      <c r="E1349" s="3" t="inlineStr"/>
+      <c r="F1349" s="3" t="inlineStr">
+        <is>
+          <t>Нардеп-втікач Куницький осів в США, — джерела УП. [https://www.pravda.com.ua/news/2024/12/17/7489526/]
+Вже 3 місяці нардеп не повертався в Україну, з моменту як у вересні виїхав у відрядження в Ізраїль, звідки потім вирушив до своєї родини у Штатах.
+Куницький повідомив про це фракцію "слуг" і зазначив, що не повернеться в Україну, "поки не будуть покарні представники поліції, які "зламали йому ребра". [https://www.pravda.com.ua/news/2022/03/11/7330542/] 
+Він також зазначив, що готовий скласти мандат, але очевидно, фракція не поспішає схвалювати таке рішення нардепа, який є мажоритарником, і втрачати ще одного представника у ВР.
+🤡🤡🤡🤡🤡</t>
+        </is>
+      </c>
+      <c r="G1349" s="3" t="inlineStr"/>
+      <c r="H1349" s="3" t="inlineStr"/>
+      <c r="I1349" s="3" t="inlineStr"/>
+      <c r="J1349" s="3" t="inlineStr"/>
+      <c r="K1349" s="3" t="inlineStr"/>
+      <c r="L1349" s="3" t="inlineStr"/>
+      <c r="M1349" s="3" t="inlineStr"/>
+      <c r="N1349" s="3" t="inlineStr"/>
+      <c r="O1349" s="3" t="inlineStr"/>
+    </row>
+    <row r="1350">
+      <c r="A1350" s="3" t="inlineStr">
+        <is>
+          <t>V1349</t>
+        </is>
+      </c>
+      <c r="B1350" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1350" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-03</t>
+        </is>
+      </c>
+      <c r="D1350" s="3" t="n">
+        <v>102903</v>
+      </c>
+      <c r="E1350" s="3" t="inlineStr"/>
+      <c r="F1350" s="3" t="inlineStr">
+        <is>
+          <t>**❗️1000 грн від держави – це спроба виявити чоловіків, які ухиляються від мобілізації, **– нардепка [https://www.radiosvoboda.org/a/news-zymova-pidtrymka-1000-hryven-oblik-naslennya-ukhylyanty/33224838.html] Василевська-Смаглюк.</t>
+        </is>
+      </c>
+      <c r="G1350" s="3" t="inlineStr"/>
+      <c r="H1350" s="3" t="inlineStr"/>
+      <c r="I1350" s="3" t="inlineStr"/>
+      <c r="J1350" s="3" t="inlineStr"/>
+      <c r="K1350" s="3" t="inlineStr"/>
+      <c r="L1350" s="3" t="inlineStr"/>
+      <c r="M1350" s="3" t="inlineStr"/>
+      <c r="N1350" s="3" t="inlineStr"/>
+      <c r="O1350" s="3" t="inlineStr"/>
+    </row>
+    <row r="1351">
+      <c r="A1351" s="3" t="inlineStr">
+        <is>
+          <t>V1350</t>
+        </is>
+      </c>
+      <c r="B1351" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1351" s="3" t="inlineStr">
+        <is>
+          <t>2022-08-20</t>
+        </is>
+      </c>
+      <c r="D1351" s="3" t="n">
+        <v>20796</v>
+      </c>
+      <c r="E1351" s="3" t="inlineStr"/>
+      <c r="F1351" s="3" t="inlineStr">
+        <is>
+          <t>**⚡️💥 На Правому березі ГОЛОСНО!**
+Жителі час від часу чують такі «бабахи». Не хвилюйтесь, **працюють наші захисники.
+UPD: **також на Святошино якийсь неадекват вирішив постріляти з вікна своєї квартири. Приїхала поліція, його затримали. 
+Станом на зараз в столиці та в області спокійно, чекаємо на бій Усика💪🏻 [https://t.me/c/1206439755/20795]</t>
+        </is>
+      </c>
+      <c r="G1351" s="3" t="inlineStr"/>
+      <c r="H1351" s="3" t="inlineStr"/>
+      <c r="I1351" s="3" t="inlineStr"/>
+      <c r="J1351" s="3" t="inlineStr"/>
+      <c r="K1351" s="3" t="inlineStr"/>
+      <c r="L1351" s="3" t="inlineStr"/>
+      <c r="M1351" s="3" t="inlineStr"/>
+      <c r="N1351" s="3" t="inlineStr"/>
+      <c r="O1351" s="3" t="inlineStr"/>
+    </row>
+    <row r="1352">
+      <c r="A1352" s="3" t="inlineStr">
+        <is>
+          <t>V1351</t>
+        </is>
+      </c>
+      <c r="B1352" s="3" t="inlineStr">
+        <is>
+          <t>batalionmonako</t>
+        </is>
+      </c>
+      <c r="C1352" s="3" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="D1352" s="3" t="n">
+        <v>25798</v>
+      </c>
+      <c r="E1352" s="3" t="inlineStr"/>
+      <c r="F1352" s="3" t="inlineStr">
+        <is>
+          <t>🗣**Потужний удар по Одесі. На місці здіймається дим.**
+ Більше інформації з місця подій в каналі **Одеси** [https://t.me/+DmeTneBhXmM1OTQy].
+**https://t.me/+DmeTneBhXmM1OTQy**</t>
+        </is>
+      </c>
+      <c r="G1352" s="3" t="inlineStr"/>
+      <c r="H1352" s="3" t="inlineStr"/>
+      <c r="I1352" s="3" t="inlineStr"/>
+      <c r="J1352" s="3" t="inlineStr"/>
+      <c r="K1352" s="3" t="inlineStr"/>
+      <c r="L1352" s="3" t="inlineStr"/>
+      <c r="M1352" s="3" t="inlineStr"/>
+      <c r="N1352" s="3" t="inlineStr"/>
+      <c r="O1352" s="3" t="inlineStr"/>
+    </row>
+    <row r="1353">
+      <c r="A1353" s="3" t="inlineStr">
+        <is>
+          <t>V1352</t>
+        </is>
+      </c>
+      <c r="B1353" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1353" s="3" t="inlineStr">
+        <is>
+          <t>2021-12-16</t>
+        </is>
+      </c>
+      <c r="D1353" s="3" t="n">
+        <v>15271</v>
+      </c>
+      <c r="E1353" s="3" t="inlineStr"/>
+      <c r="F1353" s="3" t="inlineStr">
+        <is>
+          <t>«Сумасшедший профессор», как называли Даниила Гетманцева вначале каденции, наконец начал понимать, что не все его инициативы одинаково полезны. Более того, большинство из них откровенно провальны. Свою несостоятельность Гетманцев активно признает в последних больших интервью, [https://money.comments.ua/article/economy/pochemu-bolshinstvo-iniciativ-daniila-getmanceva-ne-uvenchalis-uspehom-690115.html] например, Forbes [https://forbes.ua/news/zachem-nalogovoy-bolshe-polnomochiy-i-kakie-rezultaty-nulevoy-amnistii-intervyu-s-daniilom-getmantsevym-glavnym-30112021-2855] и Интерфаксу [https://interfax.com.ua/news/interview/785900.html].
+Журналисты проанализировали самые «популярные» прожекты  [https://money.comments.ua/article/economy/pochemu-bolshinstvo-iniciativ-daniila-getmanceva-ne-uvenchalis-uspehom-690115.html]Гетманцева - налоговую амнистию, борьбу с контрабандой и теневой экономикой, закручивание гаек ФОПам, «борьба» со «скрутками НДС. И выяснили, что практически во всех сферах главу налогового и финансового комитета Рады постигли неудачи. 
+Провалились ожидаемые поступления от игорного бизнеса, к «сомнительным победам», которые вряд ли добавляют рейтинг власти, но уж точно нагружают кошелек обычных граждан, можно отнести «налог на Google», проваленный - хотя и с помпой анонсированный - законопроект о виртуальных активах, и конечно же, законопроект 5600, который попросту выписали в интересах олигархов. 
+Впрочем, несмотря на явно сомнительные успехи, Даниил Гетманцев не собирается останавливаться и готовит новые инициативы. Например, такие как косвенные методы оценки финансового состояния, то есть контроль расходов обычных граждан, включая проверку доходов с 1995 года.
+При всех перечисленных проблемах странным остается тот факт, что Гетманцев, похоже, продолжает пользоваться доверием Офиса и руководства фракции, более того, его провалы вполне себе засчитываются в качестве «реформаторских» усилий. Вопрос лишь в том, что реальные результаты его инициатив только ухудшают ситуацию в экономике и угнетают инвестиционный климат и полностью разрушают веру обычных граждан в возможные улучшения в стране.
+©️Инсайдер UA [https://t.me/joinchat/AAAAAFCg99bpFf62A_f3yA]</t>
+        </is>
+      </c>
+      <c r="G1353" s="3" t="inlineStr"/>
+      <c r="H1353" s="3" t="inlineStr"/>
+      <c r="I1353" s="3" t="inlineStr"/>
+      <c r="J1353" s="3" t="inlineStr"/>
+      <c r="K1353" s="3" t="inlineStr"/>
+      <c r="L1353" s="3" t="inlineStr"/>
+      <c r="M1353" s="3" t="inlineStr"/>
+      <c r="N1353" s="3" t="inlineStr"/>
+      <c r="O1353" s="3" t="inlineStr"/>
+    </row>
+    <row r="1354">
+      <c r="A1354" s="3" t="inlineStr">
+        <is>
+          <t>V1353</t>
+        </is>
+      </c>
+      <c r="B1354" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1354" s="3" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="D1354" s="3" t="n">
+        <v>118266</v>
+      </c>
+      <c r="E1354" s="3" t="inlineStr"/>
+      <c r="F1354" s="3" t="inlineStr">
+        <is>
+          <t>**Тривога у Києві та низці областей через загрозу БпЛА.**
+Ситуація у столиці: https://t.me/kyiv [https://t.me/+EWmw0Cq-Os03ZGQy]</t>
+        </is>
+      </c>
+      <c r="G1354" s="3" t="inlineStr"/>
+      <c r="H1354" s="3" t="inlineStr"/>
+      <c r="I1354" s="3" t="inlineStr"/>
+      <c r="J1354" s="3" t="inlineStr"/>
+      <c r="K1354" s="3" t="inlineStr"/>
+      <c r="L1354" s="3" t="inlineStr"/>
+      <c r="M1354" s="3" t="inlineStr"/>
+      <c r="N1354" s="3" t="inlineStr"/>
+      <c r="O1354" s="3" t="inlineStr"/>
+    </row>
+    <row r="1355">
+      <c r="A1355" s="3" t="inlineStr">
+        <is>
+          <t>V1354</t>
+        </is>
+      </c>
+      <c r="B1355" s="3" t="inlineStr">
+        <is>
+          <t>truexanewsua</t>
+        </is>
+      </c>
+      <c r="C1355" s="3" t="inlineStr">
+        <is>
+          <t>2020-12-17</t>
+        </is>
+      </c>
+      <c r="D1355" s="3" t="n">
+        <v>10475</v>
+      </c>
+      <c r="E1355" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1355" s="3" t="inlineStr">
+        <is>
+          <t>**✌️Новые выборы в Харькове должны назначить депутаты Верховной Рады, а в этом случае процесс может затянуться на несколько лет 🤷🏼‍♂️**
+https://www.newsroom.kh.ua/news/po-scenariyu-lucka-vybory-v-harkove-mogut-provesti-cherez-neskolko-let</t>
+        </is>
+      </c>
+      <c r="G1355" s="3" t="inlineStr"/>
+      <c r="H1355" s="3" t="inlineStr"/>
+      <c r="I1355" s="3" t="inlineStr"/>
+      <c r="J1355" s="3" t="inlineStr"/>
+      <c r="K1355" s="3" t="inlineStr"/>
+      <c r="L1355" s="3" t="inlineStr"/>
+      <c r="M1355" s="3" t="inlineStr"/>
+      <c r="N1355" s="3" t="inlineStr"/>
+      <c r="O1355" s="3" t="inlineStr"/>
+    </row>
+    <row r="1356">
+      <c r="A1356" s="3" t="inlineStr">
+        <is>
+          <t>V1355</t>
+        </is>
+      </c>
+      <c r="B1356" s="3" t="inlineStr">
+        <is>
+          <t>times_ukraina</t>
+        </is>
+      </c>
+      <c r="C1356" s="3" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="D1356" s="3" t="n">
+        <v>1299</v>
+      </c>
+      <c r="E1356" s="3" t="inlineStr"/>
+      <c r="F1356" s="3" t="inlineStr">
+        <is>
+          <t>В Житомире грузовик сбил насмерть пятилетнего ребенка
+**23-летний водитель грузовика "СаЗ 3507" двигался по переулку Коммунальному в тот момент как у проезжей части игрались двое мальчиков. Один из них внезапно выбежал на дорогу и попал под заднее колесо автомобиля. Ребенок получил травмы несовместимые с жизнью.
+По результатам освидетельствование на употребление алкоголя водитель был трезв. Также ему назначили ряд других экспертных исследований.</t>
+        </is>
+      </c>
+      <c r="G1356" s="3" t="inlineStr"/>
+      <c r="H1356" s="3" t="inlineStr"/>
+      <c r="I1356" s="3" t="inlineStr"/>
+      <c r="J1356" s="3" t="inlineStr"/>
+      <c r="K1356" s="3" t="inlineStr"/>
+      <c r="L1356" s="3" t="inlineStr"/>
+      <c r="M1356" s="3" t="inlineStr"/>
+      <c r="N1356" s="3" t="inlineStr"/>
+      <c r="O1356" s="3" t="inlineStr"/>
+    </row>
+    <row r="1357">
+      <c r="A1357" s="3" t="inlineStr">
+        <is>
+          <t>V1356</t>
+        </is>
+      </c>
+      <c r="B1357" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1357" s="3" t="inlineStr">
+        <is>
+          <t>2022-03-24</t>
+        </is>
+      </c>
+      <c r="D1357" s="3" t="n">
+        <v>23829</v>
+      </c>
+      <c r="E1357" s="3" t="inlineStr"/>
+      <c r="F1357" s="3" t="inlineStr">
+        <is>
+          <t>**В рамках саммита НАТО на неофициальной встрече премьер Великобритании Борис Джонсон заявил руководителям стран-членов Альянса, что необходимо значительно увеличить летальную помощь Украине.** 
+"У нас есть возможность, у них есть потребность", - цитирует Джонсона The Guardian.
+Также премьер сказал лидерам НАТО, что Запад не может рассчитывать на отступление России и что история их осудит, если помощь будет недостаточной.</t>
+        </is>
+      </c>
+      <c r="G1357" s="3" t="inlineStr"/>
+      <c r="H1357" s="3" t="inlineStr"/>
+      <c r="I1357" s="3" t="inlineStr"/>
+      <c r="J1357" s="3" t="inlineStr"/>
+      <c r="K1357" s="3" t="inlineStr"/>
+      <c r="L1357" s="3" t="inlineStr"/>
+      <c r="M1357" s="3" t="inlineStr"/>
+      <c r="N1357" s="3" t="inlineStr"/>
+      <c r="O1357" s="3" t="inlineStr"/>
+    </row>
+    <row r="1358">
+      <c r="A1358" s="3" t="inlineStr">
+        <is>
+          <t>V1357</t>
+        </is>
+      </c>
+      <c r="B1358" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1358" s="3" t="inlineStr">
+        <is>
+          <t>2024-01-06</t>
+        </is>
+      </c>
+      <c r="D1358" s="3" t="n">
+        <v>67252</v>
+      </c>
+      <c r="E1358" s="3" t="inlineStr"/>
+      <c r="F1358" s="3" t="inlineStr">
+        <is>
+          <t>**Понад 10 людей загинули внаслідок російського ракетного удару по Покровську на Донеччині, серед них є діти, — Зеленський у вечірньому звернені
+**Готуємо нові лінії співпраці з партнерами, зокрема, щодо посилення наших можливостей у застосуванні дронів та в протидії російським дронам, у посиленні РЕБ – засобів радіоелектронної боротьби.
+Працюємо максимально, щоб цього року наші Сили оборони й безпеки могли базуватись у значній частині своїх дій саме на українському виробництві. І щоб ворог це відчував – реальну силу української зброї».</t>
+        </is>
+      </c>
+      <c r="G1358" s="3" t="inlineStr"/>
+      <c r="H1358" s="3" t="inlineStr"/>
+      <c r="I1358" s="3" t="inlineStr"/>
+      <c r="J1358" s="3" t="inlineStr"/>
+      <c r="K1358" s="3" t="inlineStr"/>
+      <c r="L1358" s="3" t="inlineStr"/>
+      <c r="M1358" s="3" t="inlineStr"/>
+      <c r="N1358" s="3" t="inlineStr"/>
+      <c r="O1358" s="3" t="inlineStr"/>
+    </row>
+    <row r="1359">
+      <c r="A1359" s="3" t="inlineStr">
+        <is>
+          <t>V1358</t>
+        </is>
+      </c>
+      <c r="B1359" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1359" s="3" t="inlineStr">
+        <is>
+          <t>2023-09-21</t>
+        </is>
+      </c>
+      <c r="D1359" s="3" t="n">
+        <v>36953</v>
+      </c>
+      <c r="E1359" s="3" t="inlineStr"/>
+      <c r="F1359" s="3" t="inlineStr">
+        <is>
+          <t>📡❗️З Київської області на Черкаську, та Вінницьку області. Доречі на Черкащині є ВЛУЧАННЯ 😰 внаслідок збиття 🚀 
+Канал про Вінницю 👉🏽 **ТУТ** [https://t.me/+1bppRNOLsKo1Zjgy]
+Ситуація з Черкащини 👉🏽 **ТУТ** [https://t.me/+jx2KB3sRFTM3OTgy]**
+**Детально про АТАКУ читайте вище в каналі☝ [https://t.me/+aAaZ8kQkkpo2ZjRi]🏽
+👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
+        </is>
+      </c>
+      <c r="G1359" s="3" t="inlineStr"/>
+      <c r="H1359" s="3" t="inlineStr"/>
+      <c r="I1359" s="3" t="inlineStr"/>
+      <c r="J1359" s="3" t="inlineStr"/>
+      <c r="K1359" s="3" t="inlineStr"/>
+      <c r="L1359" s="3" t="inlineStr"/>
+      <c r="M1359" s="3" t="inlineStr"/>
+      <c r="N1359" s="3" t="inlineStr"/>
+      <c r="O1359" s="3" t="inlineStr"/>
+    </row>
+    <row r="1360">
+      <c r="A1360" s="3" t="inlineStr">
+        <is>
+          <t>V1359</t>
+        </is>
+      </c>
+      <c r="B1360" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1360" s="3" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="D1360" s="3" t="n">
+        <v>21208</v>
+      </c>
+      <c r="E1360" s="3" t="inlineStr"/>
+      <c r="F1360" s="3" t="inlineStr">
+        <is>
+          <t>**Ситуация на территории аэропорта вблизи с. Гавришевка Винницкого района по состоянию на 7 марта 7:00**
+Из-под завалов достали 15 человек, из них 9 погибших (5 гражданских, 4 военных), поисковые работы продолжаются.
+В целом к проведению аварийно-спасательных работ от ГСЧС были привлечены 143 человека личного состава и 23 единицы спецтехники.
+**🇺🇦**Украина Online [https://t.me/UkrainaOnlline] | Прислать новость [http://t.me/anonimnoua]</t>
+        </is>
+      </c>
+      <c r="G1360" s="3" t="inlineStr"/>
+      <c r="H1360" s="3" t="inlineStr"/>
+      <c r="I1360" s="3" t="inlineStr"/>
+      <c r="J1360" s="3" t="inlineStr"/>
+      <c r="K1360" s="3" t="inlineStr"/>
+      <c r="L1360" s="3" t="inlineStr"/>
+      <c r="M1360" s="3" t="inlineStr"/>
+      <c r="N1360" s="3" t="inlineStr"/>
+      <c r="O1360" s="3" t="inlineStr"/>
+    </row>
+    <row r="1361">
+      <c r="A1361" s="3" t="inlineStr">
+        <is>
+          <t>V1360</t>
+        </is>
+      </c>
+      <c r="B1361" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1361" s="3" t="inlineStr">
+        <is>
+          <t>2021-04-27</t>
+        </is>
+      </c>
+      <c r="D1361" s="3" t="n">
+        <v>10975</v>
+      </c>
+      <c r="E1361" s="3" t="inlineStr"/>
+      <c r="F1361" s="3" t="inlineStr">
+        <is>
+          <t>**Зеленский посетит Польшу сразу после Пасхи **
+3 мая президент Украины Владимир Зеленский посетит Польшу с рабочим визитом. Об этом сообщили в пресс-службе президента Польши. Его визит также приурочен к празднованию 230-летия принятия Конституции Польши.
+Визит Дуды в Украину запланирован на 24 августа, сообщает пресс-служба президента Польши.</t>
+        </is>
+      </c>
+      <c r="G1361" s="3" t="inlineStr"/>
+      <c r="H1361" s="3" t="inlineStr"/>
+      <c r="I1361" s="3" t="inlineStr"/>
+      <c r="J1361" s="3" t="inlineStr"/>
+      <c r="K1361" s="3" t="inlineStr"/>
+      <c r="L1361" s="3" t="inlineStr"/>
+      <c r="M1361" s="3" t="inlineStr"/>
+      <c r="N1361" s="3" t="inlineStr"/>
+      <c r="O1361" s="3" t="inlineStr"/>
+    </row>
+    <row r="1362">
+      <c r="A1362" s="3" t="inlineStr">
+        <is>
+          <t>V1361</t>
+        </is>
+      </c>
+      <c r="B1362" s="3" t="inlineStr">
+        <is>
+          <t>kievinfo_kyiv</t>
+        </is>
+      </c>
+      <c r="C1362" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="D1362" s="3" t="n">
+        <v>37798</v>
+      </c>
+      <c r="E1362" s="3" t="inlineStr"/>
+      <c r="F1362" s="3" t="inlineStr">
+        <is>
+          <t>**❗️У Києві затримали злочинців, які за 1 BTC побили і покалічили свого товариша.
+**Бізнесмена катували в його ж квартирі і він, побоюючись за своє життя, перерахував злочинцям крипту на $28 000. Правоохоронцям вдалося встановити нападників, їм загрожує до 15 років ув'язнення з конфіскацією майна. [[Читати деталі…]](https://telegra.ph/Detalі-10-22-3) 
+👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
+        </is>
+      </c>
+      <c r="G1362" s="3" t="inlineStr"/>
+      <c r="H1362" s="3" t="inlineStr"/>
+      <c r="I1362" s="3" t="inlineStr"/>
+      <c r="J1362" s="3" t="inlineStr"/>
+      <c r="K1362" s="3" t="inlineStr"/>
+      <c r="L1362" s="3" t="inlineStr"/>
+      <c r="M1362" s="3" t="inlineStr"/>
+      <c r="N1362" s="3" t="inlineStr"/>
+      <c r="O1362" s="3" t="inlineStr"/>
+    </row>
+    <row r="1363">
+      <c r="A1363" s="3" t="inlineStr">
+        <is>
+          <t>V1362</t>
+        </is>
+      </c>
+      <c r="B1363" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1363" s="3" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="D1363" s="3" t="n">
+        <v>72963</v>
+      </c>
+      <c r="E1363" s="3" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="F1363" s="3" t="inlineStr">
+        <is>
+          <t>❗️**Мобілізаційний законопроєкт можуть винести в Раду вже 10 квітня, — нардеп Гончаренко**
+За його словами, Комітет нацбезпеки та оборони вже розглянув усі запропоновані депутатами правки й почав вносити свої.</t>
+        </is>
+      </c>
+      <c r="G1363" s="3" t="inlineStr"/>
+      <c r="H1363" s="3" t="inlineStr"/>
+      <c r="I1363" s="3" t="inlineStr"/>
+      <c r="J1363" s="3" t="inlineStr"/>
+      <c r="K1363" s="3" t="inlineStr"/>
+      <c r="L1363" s="3" t="inlineStr"/>
+      <c r="M1363" s="3" t="inlineStr"/>
+      <c r="N1363" s="3" t="inlineStr"/>
+      <c r="O1363" s="3" t="inlineStr"/>
+    </row>
+    <row r="1364">
+      <c r="A1364" s="3" t="inlineStr">
+        <is>
+          <t>V1363</t>
+        </is>
+      </c>
+      <c r="B1364" s="3" t="inlineStr">
+        <is>
+          <t>UaOnlii</t>
+        </is>
+      </c>
+      <c r="C1364" s="3" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="D1364" s="3" t="n">
+        <v>85355</v>
+      </c>
+      <c r="E1364" s="3" t="inlineStr"/>
+      <c r="F1364" s="3" t="inlineStr">
+        <is>
+          <t>**«Нужно нанести ядерный удар по странам, которые поддерживают Украину и ударить ракетами по Берлину», — радник путіна Караганов**
+Також мудак заявив, що Захід веде війну на знищення росії. путін, як президент повинен попередити НАТО, що рф готова вдарити ядерною зброєю, але перед цим може застосувати звичайні ракети для ударів по європейським країнам. 
+Цікаво, що цей рашист закликає вдарити по Німеччині, хоча сам володіє там нерухомістю 🤡</t>
+        </is>
+      </c>
+      <c r="G1364" s="3" t="inlineStr"/>
+      <c r="H1364" s="3" t="inlineStr"/>
+      <c r="I1364" s="3" t="inlineStr"/>
+      <c r="J1364" s="3" t="inlineStr"/>
+      <c r="K1364" s="3" t="inlineStr"/>
+      <c r="L1364" s="3" t="inlineStr"/>
+      <c r="M1364" s="3" t="inlineStr"/>
+      <c r="N1364" s="3" t="inlineStr"/>
+      <c r="O1364" s="3" t="inlineStr"/>
+    </row>
+    <row r="1365">
+      <c r="A1365" s="3" t="inlineStr">
+        <is>
+          <t>V1364</t>
+        </is>
+      </c>
+      <c r="B1365" s="3" t="inlineStr">
+        <is>
+          <t>lachentyt</t>
+        </is>
+      </c>
+      <c r="C1365" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="D1365" s="3" t="n">
+        <v>56574</v>
+      </c>
+      <c r="E1365" s="3" t="inlineStr"/>
+      <c r="F1365" s="3" t="inlineStr">
         <is>
           <t>Військовослужбовців 1-го окремого медичного батальйону, які врятували пораненого бійця, відзначено [https://president.gov.ua/news/prezident-vidznachiv-derzhavnimi-nagorodami-vijskovosluzhbov-101209] нагородами.
 Медалями відзначено:
@@ -50982,1292 +52298,6 @@
 🫡🫡🫡</t>
         </is>
       </c>
-      <c r="G1331" s="3" t="inlineStr"/>
-      <c r="H1331" s="3" t="inlineStr"/>
-      <c r="I1331" s="3" t="inlineStr"/>
-      <c r="J1331" s="3" t="inlineStr"/>
-      <c r="K1331" s="3" t="inlineStr"/>
-      <c r="L1331" s="3" t="inlineStr"/>
-      <c r="M1331" s="3" t="inlineStr"/>
-      <c r="N1331" s="3" t="inlineStr"/>
-      <c r="O1331" s="3" t="inlineStr"/>
-    </row>
-    <row r="1332">
-      <c r="A1332" s="3" t="inlineStr">
-        <is>
-          <t>V1331</t>
-        </is>
-      </c>
-      <c r="B1332" s="3" t="inlineStr">
-        <is>
-          <t>times_ukraina</t>
-        </is>
-      </c>
-      <c r="C1332" s="3" t="inlineStr">
-        <is>
-          <t>2023-04-30</t>
-        </is>
-      </c>
-      <c r="D1332" s="3" t="n">
-        <v>16324</v>
-      </c>
-      <c r="E1332" s="3" t="inlineStr"/>
-      <c r="F1332" s="3" t="inlineStr">
-        <is>
-          <t>«Бл*ха, він нападає! Пальця відгризе!» Наші воїни врятували рідкісну червонокнижну тварину – перегузню (мармурового тхора). Ареал поширення цього звіра в степах Донеччини, Луганщини та Запоріжжя, де ведуться найактивніші бойові дії. Таких хижих ссавців в Україні ~100 особин. Вид на межі зникнення.</t>
-        </is>
-      </c>
-      <c r="G1332" s="3" t="inlineStr"/>
-      <c r="H1332" s="3" t="inlineStr"/>
-      <c r="I1332" s="3" t="inlineStr"/>
-      <c r="J1332" s="3" t="inlineStr"/>
-      <c r="K1332" s="3" t="inlineStr"/>
-      <c r="L1332" s="3" t="inlineStr"/>
-      <c r="M1332" s="3" t="inlineStr"/>
-      <c r="N1332" s="3" t="inlineStr"/>
-      <c r="O1332" s="3" t="inlineStr"/>
-    </row>
-    <row r="1333">
-      <c r="A1333" s="3" t="inlineStr">
-        <is>
-          <t>V1332</t>
-        </is>
-      </c>
-      <c r="B1333" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1333" s="3" t="inlineStr">
-        <is>
-          <t>2022-10-19</t>
-        </is>
-      </c>
-      <c r="D1333" s="3" t="n">
-        <v>2658</v>
-      </c>
-      <c r="E1333" s="3" t="inlineStr"/>
-      <c r="F1333" s="3" t="inlineStr">
-        <is>
-          <t>+ ще одна ракета.
-Всього - п’ять.
-Інформація про 12 - вброс.</t>
-        </is>
-      </c>
-      <c r="G1333" s="3" t="inlineStr"/>
-      <c r="H1333" s="3" t="inlineStr"/>
-      <c r="I1333" s="3" t="inlineStr"/>
-      <c r="J1333" s="3" t="inlineStr"/>
-      <c r="K1333" s="3" t="inlineStr"/>
-      <c r="L1333" s="3" t="inlineStr"/>
-      <c r="M1333" s="3" t="inlineStr"/>
-      <c r="N1333" s="3" t="inlineStr"/>
-      <c r="O1333" s="3" t="inlineStr"/>
-    </row>
-    <row r="1334">
-      <c r="A1334" s="3" t="inlineStr">
-        <is>
-          <t>V1333</t>
-        </is>
-      </c>
-      <c r="B1334" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1334" s="3" t="inlineStr">
-        <is>
-          <t>2025-08-23</t>
-        </is>
-      </c>
-      <c r="D1334" s="3" t="n">
-        <v>45734</v>
-      </c>
-      <c r="E1334" s="3" t="inlineStr"/>
-      <c r="F1334" s="3" t="inlineStr">
-        <is>
-          <t>Реінтеграція військових та «пакет демобілізації» — що бізнес радив державі на VІІI Міжнародний ветеранський форум «Україна. Ветерани. Безпека». 
-Ветеранський форум обʼєднав перших представників держави. Зокрема й президента Володимира Зеленського, Генсека НАТО Марко Рютте, українських військових, ветеранів та представників ветеранського бізнесу.
-Одна з ключових тем форуму — реінтеграція військових. Представник волонтерсько-ветеранської компанії «Генерал Черешня» Андрій Лавренович запропонував державі сформувати «пакет демобілізації» — комплекс послуг та дій, які має отримати кожен демобілізований військовий. 
-В «пакет» мають увійти: психологічна допомога, соціальні пільги, безкоштовний доступ до навчання, обовʼязкове працевлаштування. За словами Андрія, держава має забезпечити соціальну частину, тоді як бізнес може та готовий інтегруватися в програми освіти, психологічної реабілітації та працевлаштування ветеранів. 
-В компанії «Генерал Черешня», один зі співзасновників якої є ветеран, наразі працює близько 20% ветеранів. Ще близько 40% співробітників прийшли з волонтерського руху. Андрій Лавренович вказує, [https://www.facebook.com/share/v/14ML1g7XtPL/?mibextid=wwXIfr] що саме ці категорії людей мають стати успішними та ефективними менеджерами майбутньої України.</t>
-        </is>
-      </c>
-      <c r="G1334" s="3" t="inlineStr"/>
-      <c r="H1334" s="3" t="inlineStr"/>
-      <c r="I1334" s="3" t="inlineStr"/>
-      <c r="J1334" s="3" t="inlineStr"/>
-      <c r="K1334" s="3" t="inlineStr"/>
-      <c r="L1334" s="3" t="inlineStr"/>
-      <c r="M1334" s="3" t="inlineStr"/>
-      <c r="N1334" s="3" t="inlineStr"/>
-      <c r="O1334" s="3" t="inlineStr"/>
-    </row>
-    <row r="1335">
-      <c r="A1335" s="3" t="inlineStr">
-        <is>
-          <t>V1334</t>
-        </is>
-      </c>
-      <c r="B1335" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1335" s="3" t="inlineStr">
-        <is>
-          <t>2022-11-23</t>
-        </is>
-      </c>
-      <c r="D1335" s="3" t="n">
-        <v>3997</v>
-      </c>
-      <c r="E1335" s="3" t="inlineStr"/>
-      <c r="F1335" s="3" t="inlineStr">
-        <is>
-          <t>**У Молдові масові відключення електроенергії **внаслідок ракетних ударів РФ по Україні, — віцепремʼєр країни Спину.</t>
-        </is>
-      </c>
-      <c r="G1335" s="3" t="inlineStr"/>
-      <c r="H1335" s="3" t="inlineStr"/>
-      <c r="I1335" s="3" t="inlineStr"/>
-      <c r="J1335" s="3" t="inlineStr"/>
-      <c r="K1335" s="3" t="inlineStr"/>
-      <c r="L1335" s="3" t="inlineStr"/>
-      <c r="M1335" s="3" t="inlineStr"/>
-      <c r="N1335" s="3" t="inlineStr"/>
-      <c r="O1335" s="3" t="inlineStr"/>
-    </row>
-    <row r="1336">
-      <c r="A1336" s="3" t="inlineStr">
-        <is>
-          <t>V1335</t>
-        </is>
-      </c>
-      <c r="B1336" s="3" t="inlineStr">
-        <is>
-          <t>lachentyt</t>
-        </is>
-      </c>
-      <c r="C1336" s="3" t="inlineStr">
-        <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="D1336" s="3" t="n">
-        <v>44720</v>
-      </c>
-      <c r="E1336" s="3" t="inlineStr"/>
-      <c r="F1336" s="3" t="inlineStr">
-        <is>
-          <t>Рятувальні роботи на місці удару по Інституту зв'язку в Полтаві завершено, — ДСНС.
-55 людей загинуло, 328 постраждало. Проводиться ідентифікація рештків тіл.</t>
-        </is>
-      </c>
-      <c r="G1336" s="3" t="inlineStr"/>
-      <c r="H1336" s="3" t="inlineStr"/>
-      <c r="I1336" s="3" t="inlineStr"/>
-      <c r="J1336" s="3" t="inlineStr"/>
-      <c r="K1336" s="3" t="inlineStr"/>
-      <c r="L1336" s="3" t="inlineStr"/>
-      <c r="M1336" s="3" t="inlineStr"/>
-      <c r="N1336" s="3" t="inlineStr"/>
-      <c r="O1336" s="3" t="inlineStr"/>
-    </row>
-    <row r="1337">
-      <c r="A1337" s="3" t="inlineStr">
-        <is>
-          <t>V1336</t>
-        </is>
-      </c>
-      <c r="B1337" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1337" s="3" t="inlineStr">
-        <is>
-          <t>2023-03-08</t>
-        </is>
-      </c>
-      <c r="D1337" s="3" t="n">
-        <v>47772</v>
-      </c>
-      <c r="E1337" s="3" t="inlineStr"/>
-      <c r="F1337" s="3" t="inlineStr">
-        <is>
-          <t>**Грузинские власти не выполнили требований протестующих: люди окружают парламент, — СМИ
-**Во внутреннем дворе парламента уже собираются силовики. Завтра митингующие планируют пикетировать парламент и помешать работе законодательного органа.</t>
-        </is>
-      </c>
-      <c r="G1337" s="3" t="inlineStr"/>
-      <c r="H1337" s="3" t="inlineStr"/>
-      <c r="I1337" s="3" t="inlineStr"/>
-      <c r="J1337" s="3" t="inlineStr"/>
-      <c r="K1337" s="3" t="inlineStr"/>
-      <c r="L1337" s="3" t="inlineStr"/>
-      <c r="M1337" s="3" t="inlineStr"/>
-      <c r="N1337" s="3" t="inlineStr"/>
-      <c r="O1337" s="3" t="inlineStr"/>
-    </row>
-    <row r="1338">
-      <c r="A1338" s="3" t="inlineStr">
-        <is>
-          <t>V1337</t>
-        </is>
-      </c>
-      <c r="B1338" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1338" s="3" t="inlineStr">
-        <is>
-          <t>2022-01-10</t>
-        </is>
-      </c>
-      <c r="D1338" s="3" t="n">
-        <v>3505</v>
-      </c>
-      <c r="E1338" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1338" s="3" t="inlineStr">
-        <is>
-          <t>Ситуация в метро 😏**Как думаете ,должны  пускать всех или выборочно⁉️
-__У «безхатченки»,кстати,был действующий билет.
-__**Киев INFO** [https://t.me/+3iBBG0L0rlM5MDU6] **| ****Прислать новость** [https://t.me/nikitos077]</t>
-        </is>
-      </c>
-      <c r="G1338" s="3" t="inlineStr"/>
-      <c r="H1338" s="3" t="inlineStr"/>
-      <c r="I1338" s="3" t="inlineStr"/>
-      <c r="J1338" s="3" t="inlineStr"/>
-      <c r="K1338" s="3" t="inlineStr"/>
-      <c r="L1338" s="3" t="inlineStr"/>
-      <c r="M1338" s="3" t="inlineStr"/>
-      <c r="N1338" s="3" t="inlineStr"/>
-      <c r="O1338" s="3" t="inlineStr"/>
-    </row>
-    <row r="1339">
-      <c r="A1339" s="3" t="inlineStr">
-        <is>
-          <t>V1338</t>
-        </is>
-      </c>
-      <c r="B1339" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1339" s="3" t="inlineStr">
-        <is>
-          <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="D1339" s="3" t="n">
-        <v>18885</v>
-      </c>
-      <c r="E1339" s="3" t="inlineStr"/>
-      <c r="F1339" s="3" t="inlineStr">
-        <is>
-          <t>**#offtop**** 🇮🇹 💦 В Италии мощнейшее наводнение: отменили даже выборы **
-Больше всего страдает Лигурия (Северный регион). Вода затопила улицы, размыла дороги; закрыты магазины, школы и даже отменены местные выборы.
-**Мечта побывать в Италии становится более реальной 😌</t>
-        </is>
-      </c>
-      <c r="G1339" s="3" t="inlineStr"/>
-      <c r="H1339" s="3" t="inlineStr"/>
-      <c r="I1339" s="3" t="inlineStr"/>
-      <c r="J1339" s="3" t="inlineStr"/>
-      <c r="K1339" s="3" t="inlineStr"/>
-      <c r="L1339" s="3" t="inlineStr"/>
-      <c r="M1339" s="3" t="inlineStr"/>
-      <c r="N1339" s="3" t="inlineStr"/>
-      <c r="O1339" s="3" t="inlineStr"/>
-    </row>
-    <row r="1340">
-      <c r="A1340" s="3" t="inlineStr">
-        <is>
-          <t>V1339</t>
-        </is>
-      </c>
-      <c r="B1340" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1340" s="3" t="inlineStr">
-        <is>
-          <t>2023-11-25</t>
-        </is>
-      </c>
-      <c r="D1340" s="3" t="n">
-        <v>38874</v>
-      </c>
-      <c r="E1340" s="3" t="inlineStr"/>
-      <c r="F1340" s="3" t="inlineStr">
-        <is>
-          <t>❗️КМВА: Четверта атака ворожих БПЛА на Київ за цей місяць.** Цей напад дронів став наймасованішим з початку повномасштабного вторгнення!** У столиці тривога тривала понад 6 годин. Символічно, що рашисти (нащадки тоталітарної радянського режиму) здійснили цю атаку в День пам’яті жертв голодоморів. Так вони продовжують геноцид України та українців.
-За попередніми даними противник вкотре застосував баражуючі боєприпаси типу «Shahed». БпЛА заходили на Київ хвилями, численними групами, з різних напрямків, постійно змінюючи курс за вектором руху. 
-**Силами та засобами ППО було уражено майже п'ять десятків повітряних цілей!** (остаточні підсумкові дані щодо типу та кількості оприлюднять Повітряні Сили). 
-За попередніми даними, внаслідок збиття ворожих дронів зафіксовано падіння уламків в різних районах міста: 
--  у Солом'янському районі внаслідок падіння уламків є двоє постраждалих - в обох гостра реакція на стрес, без госпіталізації. Також в цьому районі, у 5-поверховому будинку сталося руйнування на другому поверсі, вибиті шибки з першого по п’ятий поверх. В будівлі було заблоковано дві жінки. Також в Солом'янському районі сталося загоряння на території дитячого садочку і на іншій локації – в нежитловому приміщенні на площі 100 м2..
--  у Дніпровському районі міста уламки впали на верхні поверхи багатоповерхівки, сталося задимлення.
--  у Голосіївському районі уламки упали на зону зелених насаджень, без потерпілих.
--  у Печерському районі - також на незабудовану територію. Попередньо без наслідків.
-За інформацією Міненерго, в результаті атаки дронів, у Києві залишалися без світла 77 житлових будинків та 120 установ. Тривають роботи з відновлення.
-Інформація оновлюється і уточнюється.
-Дякуйте воїнам ППО. 
-Вірте в ЗСУ!
-👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
-        </is>
-      </c>
-      <c r="G1340" s="3" t="inlineStr"/>
-      <c r="H1340" s="3" t="inlineStr"/>
-      <c r="I1340" s="3" t="inlineStr"/>
-      <c r="J1340" s="3" t="inlineStr"/>
-      <c r="K1340" s="3" t="inlineStr"/>
-      <c r="L1340" s="3" t="inlineStr"/>
-      <c r="M1340" s="3" t="inlineStr"/>
-      <c r="N1340" s="3" t="inlineStr"/>
-      <c r="O1340" s="3" t="inlineStr"/>
-    </row>
-    <row r="1341">
-      <c r="A1341" s="3" t="inlineStr">
-        <is>
-          <t>V1340</t>
-        </is>
-      </c>
-      <c r="B1341" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1341" s="3" t="inlineStr">
-        <is>
-          <t>2022-09-24</t>
-        </is>
-      </c>
-      <c r="D1341" s="3" t="n">
-        <v>61108</v>
-      </c>
-      <c r="E1341" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1341" s="3" t="inlineStr">
-        <is>
-          <t>**Российских командиров не волнуют жизни россиян –** им просто нужно заполнить пустые места, – Владимир Зеленский обратился к россиянам.
-«Кем будут заполняться эти места, вашу власть не волнует. Хоть молодыми айтишниками, которые вообще не служили, хоть пенсионерами, которые служили разве что в советской армии.
-Для вас наступил ключевой момент: именно сейчас решается, закончится ли ваша жизнь».</t>
-        </is>
-      </c>
-      <c r="G1341" s="3" t="inlineStr"/>
-      <c r="H1341" s="3" t="inlineStr"/>
-      <c r="I1341" s="3" t="inlineStr"/>
-      <c r="J1341" s="3" t="inlineStr"/>
-      <c r="K1341" s="3" t="inlineStr"/>
-      <c r="L1341" s="3" t="inlineStr"/>
-      <c r="M1341" s="3" t="inlineStr"/>
-      <c r="N1341" s="3" t="inlineStr"/>
-      <c r="O1341" s="3" t="inlineStr"/>
-    </row>
-    <row r="1342">
-      <c r="A1342" s="3" t="inlineStr">
-        <is>
-          <t>V1341</t>
-        </is>
-      </c>
-      <c r="B1342" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1342" s="3" t="inlineStr">
-        <is>
-          <t>2024-10-23</t>
-        </is>
-      </c>
-      <c r="D1342" s="3" t="n">
-        <v>53305</v>
-      </c>
-      <c r="E1342" s="3" t="inlineStr"/>
-      <c r="F1342" s="3" t="inlineStr">
-        <is>
-          <t>❗️Блекаутів не уникнути: **Україна близька до відключень електроенергії**, — експерт Інституту енергетичних стратегій Юрій Корольчук.
-Через два тижні **зростатиме споживання.</t>
-        </is>
-      </c>
-      <c r="G1342" s="3" t="inlineStr"/>
-      <c r="H1342" s="3" t="inlineStr"/>
-      <c r="I1342" s="3" t="inlineStr"/>
-      <c r="J1342" s="3" t="inlineStr"/>
-      <c r="K1342" s="3" t="inlineStr"/>
-      <c r="L1342" s="3" t="inlineStr"/>
-      <c r="M1342" s="3" t="inlineStr"/>
-      <c r="N1342" s="3" t="inlineStr"/>
-      <c r="O1342" s="3" t="inlineStr"/>
-    </row>
-    <row r="1343">
-      <c r="A1343" s="3" t="inlineStr">
-        <is>
-          <t>V1342</t>
-        </is>
-      </c>
-      <c r="B1343" s="3" t="inlineStr">
-        <is>
-          <t>vanek_nikolaev</t>
-        </is>
-      </c>
-      <c r="C1343" s="3" t="inlineStr">
-        <is>
-          <t>2023-10-19</t>
-        </is>
-      </c>
-      <c r="D1343" s="3" t="n">
-        <v>18493</v>
-      </c>
-      <c r="E1343" s="3" t="inlineStr"/>
-      <c r="F1343" s="3" t="inlineStr">
-        <is>
-          <t>2 петуха крутятся в воздухе на левом берегу Херсонской области</t>
-        </is>
-      </c>
-      <c r="G1343" s="3" t="inlineStr"/>
-      <c r="H1343" s="3" t="inlineStr"/>
-      <c r="I1343" s="3" t="inlineStr"/>
-      <c r="J1343" s="3" t="inlineStr"/>
-      <c r="K1343" s="3" t="inlineStr"/>
-      <c r="L1343" s="3" t="inlineStr"/>
-      <c r="M1343" s="3" t="inlineStr"/>
-      <c r="N1343" s="3" t="inlineStr"/>
-      <c r="O1343" s="3" t="inlineStr"/>
-    </row>
-    <row r="1344">
-      <c r="A1344" s="3" t="inlineStr">
-        <is>
-          <t>V1343</t>
-        </is>
-      </c>
-      <c r="B1344" s="3" t="inlineStr">
-        <is>
-          <t>times_ukraina</t>
-        </is>
-      </c>
-      <c r="C1344" s="3" t="inlineStr">
-        <is>
-          <t>2025-11-11</t>
-        </is>
-      </c>
-      <c r="D1344" s="3" t="n">
-        <v>58337</v>
-      </c>
-      <c r="E1344" s="3" t="inlineStr"/>
-      <c r="F1344" s="3" t="inlineStr">
-        <is>
-          <t>⚡️Будь-які спроби повʼязати мою роботу в Міноборони **з «впливом» бізнесмена Тимура Міндіча — безпідставні**, — секретар РНБО Рустем Умєров.</t>
-        </is>
-      </c>
-      <c r="G1344" s="3" t="inlineStr"/>
-      <c r="H1344" s="3" t="inlineStr"/>
-      <c r="I1344" s="3" t="inlineStr"/>
-      <c r="J1344" s="3" t="inlineStr"/>
-      <c r="K1344" s="3" t="inlineStr"/>
-      <c r="L1344" s="3" t="inlineStr"/>
-      <c r="M1344" s="3" t="inlineStr"/>
-      <c r="N1344" s="3" t="inlineStr"/>
-      <c r="O1344" s="3" t="inlineStr"/>
-    </row>
-    <row r="1345">
-      <c r="A1345" s="3" t="inlineStr">
-        <is>
-          <t>V1344</t>
-        </is>
-      </c>
-      <c r="B1345" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1345" s="3" t="inlineStr">
-        <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="D1345" s="3" t="n">
-        <v>13069</v>
-      </c>
-      <c r="E1345" s="3" t="inlineStr"/>
-      <c r="F1345" s="3" t="inlineStr">
-        <is>
-          <t>❗️❗️**Раміна раз‘й*бує Гордона, що той до війни працював проти Президента 🤯**</t>
-        </is>
-      </c>
-      <c r="G1345" s="3" t="inlineStr"/>
-      <c r="H1345" s="3" t="inlineStr"/>
-      <c r="I1345" s="3" t="inlineStr"/>
-      <c r="J1345" s="3" t="inlineStr"/>
-      <c r="K1345" s="3" t="inlineStr"/>
-      <c r="L1345" s="3" t="inlineStr"/>
-      <c r="M1345" s="3" t="inlineStr"/>
-      <c r="N1345" s="3" t="inlineStr"/>
-      <c r="O1345" s="3" t="inlineStr"/>
-    </row>
-    <row r="1346">
-      <c r="A1346" s="3" t="inlineStr">
-        <is>
-          <t>V1345</t>
-        </is>
-      </c>
-      <c r="B1346" s="3" t="inlineStr">
-        <is>
-          <t>vanek_nikolaev</t>
-        </is>
-      </c>
-      <c r="C1346" s="3" t="inlineStr">
-        <is>
-          <t>2024-11-25</t>
-        </is>
-      </c>
-      <c r="D1346" s="3" t="n">
-        <v>28873</v>
-      </c>
-      <c r="E1346" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1346" s="3" t="inlineStr">
-        <is>
-          <t>угроза баллистики с воронежской тупорылой республики актуальна
-Сумчата - могут быть повторные запуски!</t>
-        </is>
-      </c>
-      <c r="G1346" s="3" t="inlineStr"/>
-      <c r="H1346" s="3" t="inlineStr"/>
-      <c r="I1346" s="3" t="inlineStr"/>
-      <c r="J1346" s="3" t="inlineStr"/>
-      <c r="K1346" s="3" t="inlineStr"/>
-      <c r="L1346" s="3" t="inlineStr"/>
-      <c r="M1346" s="3" t="inlineStr"/>
-      <c r="N1346" s="3" t="inlineStr"/>
-      <c r="O1346" s="3" t="inlineStr"/>
-    </row>
-    <row r="1347">
-      <c r="A1347" s="3" t="inlineStr">
-        <is>
-          <t>V1346</t>
-        </is>
-      </c>
-      <c r="B1347" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1347" s="3" t="inlineStr">
-        <is>
-          <t>2022-01-19</t>
-        </is>
-      </c>
-      <c r="D1347" s="3" t="n">
-        <v>3702</v>
-      </c>
-      <c r="E1347" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1347" s="3" t="inlineStr">
-        <is>
-          <t>**⚡️Смертельное ДТП:рейсовый автобус Гюнсел, следовавший по маршруту Киев-Одесса выехал на встречную полосу, снес 3 авто, дерево и влетел в магазин
-**По информации полиции, сегодня утром водитель автобуса MAN, не справился с управлением, в результате чего выехал на встречную полосу, где столкнулся с автомобилями Hyundai Tucson, Daewoo Lanos, Hyundai SantaFe, Chevrolet Aveo.
-**По инерции, продолжив движение, автобус выехал на тротуар и совершил наезд на дерево и здание.
-По словам медиков у водителя прямо за рулём случился инсульт, он скончался в карете скорой.
-**Пострадавшему водителю Chevrolet и пассажирам автобуса была оказана помощь на месте.</t>
-        </is>
-      </c>
-      <c r="G1347" s="3" t="inlineStr"/>
-      <c r="H1347" s="3" t="inlineStr"/>
-      <c r="I1347" s="3" t="inlineStr"/>
-      <c r="J1347" s="3" t="inlineStr"/>
-      <c r="K1347" s="3" t="inlineStr"/>
-      <c r="L1347" s="3" t="inlineStr"/>
-      <c r="M1347" s="3" t="inlineStr"/>
-      <c r="N1347" s="3" t="inlineStr"/>
-      <c r="O1347" s="3" t="inlineStr"/>
-    </row>
-    <row r="1348">
-      <c r="A1348" s="3" t="inlineStr">
-        <is>
-          <t>V1347</t>
-        </is>
-      </c>
-      <c r="B1348" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1348" s="3" t="inlineStr">
-        <is>
-          <t>2023-04-01</t>
-        </is>
-      </c>
-      <c r="D1348" s="3" t="n">
-        <v>71147</v>
-      </c>
-      <c r="E1348" s="3" t="inlineStr"/>
-      <c r="F1348" s="3" t="inlineStr">
-        <is>
-          <t>❗️**Рецептам таки бути! У частині регіонів України** рецептурні препарати будуть відпускати лише так, – МОЗ [https://life.pravda.com.ua/health/2023/04/1/253625/].
-Без рецепта їх можна буде купити у зоні бойових дій, під окупацією або в оточенні. У «‎мирних»‎ областях – ні. Нова постанова КМУ коригує норму про вільний продаж [https://t.me/truexanewsua/71130] ліків під час воєнного стану.</t>
-        </is>
-      </c>
-      <c r="G1348" s="3" t="inlineStr"/>
-      <c r="H1348" s="3" t="inlineStr"/>
-      <c r="I1348" s="3" t="inlineStr"/>
-      <c r="J1348" s="3" t="inlineStr"/>
-      <c r="K1348" s="3" t="inlineStr"/>
-      <c r="L1348" s="3" t="inlineStr"/>
-      <c r="M1348" s="3" t="inlineStr"/>
-      <c r="N1348" s="3" t="inlineStr"/>
-      <c r="O1348" s="3" t="inlineStr"/>
-    </row>
-    <row r="1349">
-      <c r="A1349" s="3" t="inlineStr">
-        <is>
-          <t>V1348</t>
-        </is>
-      </c>
-      <c r="B1349" s="3" t="inlineStr">
-        <is>
-          <t>lachentyt</t>
-        </is>
-      </c>
-      <c r="C1349" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="D1349" s="3" t="n">
-        <v>47213</v>
-      </c>
-      <c r="E1349" s="3" t="inlineStr"/>
-      <c r="F1349" s="3" t="inlineStr">
-        <is>
-          <t>Нардеп-втікач Куницький осів в США, — джерела УП. [https://www.pravda.com.ua/news/2024/12/17/7489526/]
-Вже 3 місяці нардеп не повертався в Україну, з моменту як у вересні виїхав у відрядження в Ізраїль, звідки потім вирушив до своєї родини у Штатах.
-Куницький повідомив про це фракцію "слуг" і зазначив, що не повернеться в Україну, "поки не будуть покарні представники поліції, які "зламали йому ребра". [https://www.pravda.com.ua/news/2022/03/11/7330542/] 
-Він також зазначив, що готовий скласти мандат, але очевидно, фракція не поспішає схвалювати таке рішення нардепа, який є мажоритарником, і втрачати ще одного представника у ВР.
-🤡🤡🤡🤡🤡</t>
-        </is>
-      </c>
-      <c r="G1349" s="3" t="inlineStr"/>
-      <c r="H1349" s="3" t="inlineStr"/>
-      <c r="I1349" s="3" t="inlineStr"/>
-      <c r="J1349" s="3" t="inlineStr"/>
-      <c r="K1349" s="3" t="inlineStr"/>
-      <c r="L1349" s="3" t="inlineStr"/>
-      <c r="M1349" s="3" t="inlineStr"/>
-      <c r="N1349" s="3" t="inlineStr"/>
-      <c r="O1349" s="3" t="inlineStr"/>
-    </row>
-    <row r="1350">
-      <c r="A1350" s="3" t="inlineStr">
-        <is>
-          <t>V1349</t>
-        </is>
-      </c>
-      <c r="B1350" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1350" s="3" t="inlineStr">
-        <is>
-          <t>2024-12-03</t>
-        </is>
-      </c>
-      <c r="D1350" s="3" t="n">
-        <v>102903</v>
-      </c>
-      <c r="E1350" s="3" t="inlineStr"/>
-      <c r="F1350" s="3" t="inlineStr">
-        <is>
-          <t>**❗️1000 грн від держави – це спроба виявити чоловіків, які ухиляються від мобілізації, **– нардепка [https://www.radiosvoboda.org/a/news-zymova-pidtrymka-1000-hryven-oblik-naslennya-ukhylyanty/33224838.html] Василевська-Смаглюк.</t>
-        </is>
-      </c>
-      <c r="G1350" s="3" t="inlineStr"/>
-      <c r="H1350" s="3" t="inlineStr"/>
-      <c r="I1350" s="3" t="inlineStr"/>
-      <c r="J1350" s="3" t="inlineStr"/>
-      <c r="K1350" s="3" t="inlineStr"/>
-      <c r="L1350" s="3" t="inlineStr"/>
-      <c r="M1350" s="3" t="inlineStr"/>
-      <c r="N1350" s="3" t="inlineStr"/>
-      <c r="O1350" s="3" t="inlineStr"/>
-    </row>
-    <row r="1351">
-      <c r="A1351" s="3" t="inlineStr">
-        <is>
-          <t>V1350</t>
-        </is>
-      </c>
-      <c r="B1351" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1351" s="3" t="inlineStr">
-        <is>
-          <t>2022-08-20</t>
-        </is>
-      </c>
-      <c r="D1351" s="3" t="n">
-        <v>20796</v>
-      </c>
-      <c r="E1351" s="3" t="inlineStr"/>
-      <c r="F1351" s="3" t="inlineStr">
-        <is>
-          <t>**⚡️💥 На Правому березі ГОЛОСНО!**
-Жителі час від часу чують такі «бабахи». Не хвилюйтесь, **працюють наші захисники.
-UPD: **також на Святошино якийсь неадекват вирішив постріляти з вікна своєї квартири. Приїхала поліція, його затримали. 
-Станом на зараз в столиці та в області спокійно, чекаємо на бій Усика💪🏻 [https://t.me/c/1206439755/20795]</t>
-        </is>
-      </c>
-      <c r="G1351" s="3" t="inlineStr"/>
-      <c r="H1351" s="3" t="inlineStr"/>
-      <c r="I1351" s="3" t="inlineStr"/>
-      <c r="J1351" s="3" t="inlineStr"/>
-      <c r="K1351" s="3" t="inlineStr"/>
-      <c r="L1351" s="3" t="inlineStr"/>
-      <c r="M1351" s="3" t="inlineStr"/>
-      <c r="N1351" s="3" t="inlineStr"/>
-      <c r="O1351" s="3" t="inlineStr"/>
-    </row>
-    <row r="1352">
-      <c r="A1352" s="3" t="inlineStr">
-        <is>
-          <t>V1351</t>
-        </is>
-      </c>
-      <c r="B1352" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1352" s="3" t="inlineStr">
-        <is>
-          <t>2024-08-14</t>
-        </is>
-      </c>
-      <c r="D1352" s="3" t="n">
-        <v>25798</v>
-      </c>
-      <c r="E1352" s="3" t="inlineStr"/>
-      <c r="F1352" s="3" t="inlineStr">
-        <is>
-          <t>🗣**Потужний удар по Одесі. На місці здіймається дим.**
- Більше інформації з місця подій в каналі **Одеси** [https://t.me/+DmeTneBhXmM1OTQy].
-**https://t.me/+DmeTneBhXmM1OTQy**</t>
-        </is>
-      </c>
-      <c r="G1352" s="3" t="inlineStr"/>
-      <c r="H1352" s="3" t="inlineStr"/>
-      <c r="I1352" s="3" t="inlineStr"/>
-      <c r="J1352" s="3" t="inlineStr"/>
-      <c r="K1352" s="3" t="inlineStr"/>
-      <c r="L1352" s="3" t="inlineStr"/>
-      <c r="M1352" s="3" t="inlineStr"/>
-      <c r="N1352" s="3" t="inlineStr"/>
-      <c r="O1352" s="3" t="inlineStr"/>
-    </row>
-    <row r="1353">
-      <c r="A1353" s="3" t="inlineStr">
-        <is>
-          <t>V1352</t>
-        </is>
-      </c>
-      <c r="B1353" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1353" s="3" t="inlineStr">
-        <is>
-          <t>2021-12-16</t>
-        </is>
-      </c>
-      <c r="D1353" s="3" t="n">
-        <v>15271</v>
-      </c>
-      <c r="E1353" s="3" t="inlineStr"/>
-      <c r="F1353" s="3" t="inlineStr">
-        <is>
-          <t>«Сумасшедший профессор», как называли Даниила Гетманцева вначале каденции, наконец начал понимать, что не все его инициативы одинаково полезны. Более того, большинство из них откровенно провальны. Свою несостоятельность Гетманцев активно признает в последних больших интервью, [https://money.comments.ua/article/economy/pochemu-bolshinstvo-iniciativ-daniila-getmanceva-ne-uvenchalis-uspehom-690115.html] например, Forbes [https://forbes.ua/news/zachem-nalogovoy-bolshe-polnomochiy-i-kakie-rezultaty-nulevoy-amnistii-intervyu-s-daniilom-getmantsevym-glavnym-30112021-2855] и Интерфаксу [https://interfax.com.ua/news/interview/785900.html].
-Журналисты проанализировали самые «популярные» прожекты  [https://money.comments.ua/article/economy/pochemu-bolshinstvo-iniciativ-daniila-getmanceva-ne-uvenchalis-uspehom-690115.html]Гетманцева - налоговую амнистию, борьбу с контрабандой и теневой экономикой, закручивание гаек ФОПам, «борьба» со «скрутками НДС. И выяснили, что практически во всех сферах главу налогового и финансового комитета Рады постигли неудачи. 
-Провалились ожидаемые поступления от игорного бизнеса, к «сомнительным победам», которые вряд ли добавляют рейтинг власти, но уж точно нагружают кошелек обычных граждан, можно отнести «налог на Google», проваленный - хотя и с помпой анонсированный - законопроект о виртуальных активах, и конечно же, законопроект 5600, который попросту выписали в интересах олигархов. 
-Впрочем, несмотря на явно сомнительные успехи, Даниил Гетманцев не собирается останавливаться и готовит новые инициативы. Например, такие как косвенные методы оценки финансового состояния, то есть контроль расходов обычных граждан, включая проверку доходов с 1995 года.
-При всех перечисленных проблемах странным остается тот факт, что Гетманцев, похоже, продолжает пользоваться доверием Офиса и руководства фракции, более того, его провалы вполне себе засчитываются в качестве «реформаторских» усилий. Вопрос лишь в том, что реальные результаты его инициатив только ухудшают ситуацию в экономике и угнетают инвестиционный климат и полностью разрушают веру обычных граждан в возможные улучшения в стране.
-©️Инсайдер UA [https://t.me/joinchat/AAAAAFCg99bpFf62A_f3yA]</t>
-        </is>
-      </c>
-      <c r="G1353" s="3" t="inlineStr"/>
-      <c r="H1353" s="3" t="inlineStr"/>
-      <c r="I1353" s="3" t="inlineStr"/>
-      <c r="J1353" s="3" t="inlineStr"/>
-      <c r="K1353" s="3" t="inlineStr"/>
-      <c r="L1353" s="3" t="inlineStr"/>
-      <c r="M1353" s="3" t="inlineStr"/>
-      <c r="N1353" s="3" t="inlineStr"/>
-      <c r="O1353" s="3" t="inlineStr"/>
-    </row>
-    <row r="1354">
-      <c r="A1354" s="3" t="inlineStr">
-        <is>
-          <t>V1353</t>
-        </is>
-      </c>
-      <c r="B1354" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1354" s="3" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="D1354" s="3" t="n">
-        <v>118266</v>
-      </c>
-      <c r="E1354" s="3" t="inlineStr"/>
-      <c r="F1354" s="3" t="inlineStr">
-        <is>
-          <t>**Тривога у Києві та низці областей через загрозу БпЛА.**
-Ситуація у столиці: https://t.me/kyiv [https://t.me/+EWmw0Cq-Os03ZGQy]</t>
-        </is>
-      </c>
-      <c r="G1354" s="3" t="inlineStr"/>
-      <c r="H1354" s="3" t="inlineStr"/>
-      <c r="I1354" s="3" t="inlineStr"/>
-      <c r="J1354" s="3" t="inlineStr"/>
-      <c r="K1354" s="3" t="inlineStr"/>
-      <c r="L1354" s="3" t="inlineStr"/>
-      <c r="M1354" s="3" t="inlineStr"/>
-      <c r="N1354" s="3" t="inlineStr"/>
-      <c r="O1354" s="3" t="inlineStr"/>
-    </row>
-    <row r="1355">
-      <c r="A1355" s="3" t="inlineStr">
-        <is>
-          <t>V1354</t>
-        </is>
-      </c>
-      <c r="B1355" s="3" t="inlineStr">
-        <is>
-          <t>truexanewsua</t>
-        </is>
-      </c>
-      <c r="C1355" s="3" t="inlineStr">
-        <is>
-          <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="D1355" s="3" t="n">
-        <v>10475</v>
-      </c>
-      <c r="E1355" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1355" s="3" t="inlineStr">
-        <is>
-          <t>**✌️Новые выборы в Харькове должны назначить депутаты Верховной Рады, а в этом случае процесс может затянуться на несколько лет 🤷🏼‍♂️**
-https://www.newsroom.kh.ua/news/po-scenariyu-lucka-vybory-v-harkove-mogut-provesti-cherez-neskolko-let</t>
-        </is>
-      </c>
-      <c r="G1355" s="3" t="inlineStr"/>
-      <c r="H1355" s="3" t="inlineStr"/>
-      <c r="I1355" s="3" t="inlineStr"/>
-      <c r="J1355" s="3" t="inlineStr"/>
-      <c r="K1355" s="3" t="inlineStr"/>
-      <c r="L1355" s="3" t="inlineStr"/>
-      <c r="M1355" s="3" t="inlineStr"/>
-      <c r="N1355" s="3" t="inlineStr"/>
-      <c r="O1355" s="3" t="inlineStr"/>
-    </row>
-    <row r="1356">
-      <c r="A1356" s="3" t="inlineStr">
-        <is>
-          <t>V1355</t>
-        </is>
-      </c>
-      <c r="B1356" s="3" t="inlineStr">
-        <is>
-          <t>times_ukraina</t>
-        </is>
-      </c>
-      <c r="C1356" s="3" t="inlineStr">
-        <is>
-          <t>2020-07-17</t>
-        </is>
-      </c>
-      <c r="D1356" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="E1356" s="3" t="inlineStr"/>
-      <c r="F1356" s="3" t="inlineStr">
-        <is>
-          <t>В Житомире грузовик сбил насмерть пятилетнего ребенка
-**23-летний водитель грузовика "СаЗ 3507" двигался по переулку Коммунальному в тот момент как у проезжей части игрались двое мальчиков. Один из них внезапно выбежал на дорогу и попал под заднее колесо автомобиля. Ребенок получил травмы несовместимые с жизнью.
-По результатам освидетельствование на употребление алкоголя водитель был трезв. Также ему назначили ряд других экспертных исследований.</t>
-        </is>
-      </c>
-      <c r="G1356" s="3" t="inlineStr"/>
-      <c r="H1356" s="3" t="inlineStr"/>
-      <c r="I1356" s="3" t="inlineStr"/>
-      <c r="J1356" s="3" t="inlineStr"/>
-      <c r="K1356" s="3" t="inlineStr"/>
-      <c r="L1356" s="3" t="inlineStr"/>
-      <c r="M1356" s="3" t="inlineStr"/>
-      <c r="N1356" s="3" t="inlineStr"/>
-      <c r="O1356" s="3" t="inlineStr"/>
-    </row>
-    <row r="1357">
-      <c r="A1357" s="3" t="inlineStr">
-        <is>
-          <t>V1356</t>
-        </is>
-      </c>
-      <c r="B1357" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1357" s="3" t="inlineStr">
-        <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="D1357" s="3" t="n">
-        <v>31326</v>
-      </c>
-      <c r="E1357" s="3" t="inlineStr"/>
-      <c r="F1357" s="3" t="inlineStr">
-        <is>
-          <t>**"Настоятельно призываю харьковчан по хорошему вывезти детей, потому что, боюсь это надолго — обстрелы Харькова" — Арестович
-**"В области и Харькове могут быть сложности. Возможно будет битва за Харьков", — добавил советник главы ОП и второй раз призвал вывезти детей из города.</t>
-        </is>
-      </c>
-      <c r="G1357" s="3" t="inlineStr"/>
-      <c r="H1357" s="3" t="inlineStr"/>
-      <c r="I1357" s="3" t="inlineStr"/>
-      <c r="J1357" s="3" t="inlineStr"/>
-      <c r="K1357" s="3" t="inlineStr"/>
-      <c r="L1357" s="3" t="inlineStr"/>
-      <c r="M1357" s="3" t="inlineStr"/>
-      <c r="N1357" s="3" t="inlineStr"/>
-      <c r="O1357" s="3" t="inlineStr"/>
-    </row>
-    <row r="1358">
-      <c r="A1358" s="3" t="inlineStr">
-        <is>
-          <t>V1357</t>
-        </is>
-      </c>
-      <c r="B1358" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1358" s="3" t="inlineStr">
-        <is>
-          <t>2024-01-06</t>
-        </is>
-      </c>
-      <c r="D1358" s="3" t="n">
-        <v>67252</v>
-      </c>
-      <c r="E1358" s="3" t="inlineStr"/>
-      <c r="F1358" s="3" t="inlineStr">
-        <is>
-          <t>**Понад 10 людей загинули внаслідок російського ракетного удару по Покровську на Донеччині, серед них є діти, — Зеленський у вечірньому звернені
-**Готуємо нові лінії співпраці з партнерами, зокрема, щодо посилення наших можливостей у застосуванні дронів та в протидії російським дронам, у посиленні РЕБ – засобів радіоелектронної боротьби.
-Працюємо максимально, щоб цього року наші Сили оборони й безпеки могли базуватись у значній частині своїх дій саме на українському виробництві. І щоб ворог це відчував – реальну силу української зброї».</t>
-        </is>
-      </c>
-      <c r="G1358" s="3" t="inlineStr"/>
-      <c r="H1358" s="3" t="inlineStr"/>
-      <c r="I1358" s="3" t="inlineStr"/>
-      <c r="J1358" s="3" t="inlineStr"/>
-      <c r="K1358" s="3" t="inlineStr"/>
-      <c r="L1358" s="3" t="inlineStr"/>
-      <c r="M1358" s="3" t="inlineStr"/>
-      <c r="N1358" s="3" t="inlineStr"/>
-      <c r="O1358" s="3" t="inlineStr"/>
-    </row>
-    <row r="1359">
-      <c r="A1359" s="3" t="inlineStr">
-        <is>
-          <t>V1358</t>
-        </is>
-      </c>
-      <c r="B1359" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1359" s="3" t="inlineStr">
-        <is>
-          <t>2023-09-21</t>
-        </is>
-      </c>
-      <c r="D1359" s="3" t="n">
-        <v>36953</v>
-      </c>
-      <c r="E1359" s="3" t="inlineStr"/>
-      <c r="F1359" s="3" t="inlineStr">
-        <is>
-          <t>📡❗️З Київської області на Черкаську, та Вінницьку області. Доречі на Черкащині є ВЛУЧАННЯ 😰 внаслідок збиття 🚀 
-Канал про Вінницю 👉🏽 **ТУТ** [https://t.me/+1bppRNOLsKo1Zjgy]
-Ситуація з Черкащини 👉🏽 **ТУТ** [https://t.me/+jx2KB3sRFTM3OTgy]**
-**Детально про АТАКУ читайте вище в каналі☝ [https://t.me/+aAaZ8kQkkpo2ZjRi]🏽
-👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
-        </is>
-      </c>
-      <c r="G1359" s="3" t="inlineStr"/>
-      <c r="H1359" s="3" t="inlineStr"/>
-      <c r="I1359" s="3" t="inlineStr"/>
-      <c r="J1359" s="3" t="inlineStr"/>
-      <c r="K1359" s="3" t="inlineStr"/>
-      <c r="L1359" s="3" t="inlineStr"/>
-      <c r="M1359" s="3" t="inlineStr"/>
-      <c r="N1359" s="3" t="inlineStr"/>
-      <c r="O1359" s="3" t="inlineStr"/>
-    </row>
-    <row r="1360">
-      <c r="A1360" s="3" t="inlineStr">
-        <is>
-          <t>V1359</t>
-        </is>
-      </c>
-      <c r="B1360" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1360" s="3" t="inlineStr">
-        <is>
-          <t>2022-03-07</t>
-        </is>
-      </c>
-      <c r="D1360" s="3" t="n">
-        <v>21208</v>
-      </c>
-      <c r="E1360" s="3" t="inlineStr"/>
-      <c r="F1360" s="3" t="inlineStr">
-        <is>
-          <t>**Ситуация на территории аэропорта вблизи с. Гавришевка Винницкого района по состоянию на 7 марта 7:00**
-Из-под завалов достали 15 человек, из них 9 погибших (5 гражданских, 4 военных), поисковые работы продолжаются.
-В целом к проведению аварийно-спасательных работ от ГСЧС были привлечены 143 человека личного состава и 23 единицы спецтехники.
-**🇺🇦**Украина Online [https://t.me/UkrainaOnlline] | Прислать новость [http://t.me/anonimnoua]</t>
-        </is>
-      </c>
-      <c r="G1360" s="3" t="inlineStr"/>
-      <c r="H1360" s="3" t="inlineStr"/>
-      <c r="I1360" s="3" t="inlineStr"/>
-      <c r="J1360" s="3" t="inlineStr"/>
-      <c r="K1360" s="3" t="inlineStr"/>
-      <c r="L1360" s="3" t="inlineStr"/>
-      <c r="M1360" s="3" t="inlineStr"/>
-      <c r="N1360" s="3" t="inlineStr"/>
-      <c r="O1360" s="3" t="inlineStr"/>
-    </row>
-    <row r="1361">
-      <c r="A1361" s="3" t="inlineStr">
-        <is>
-          <t>V1360</t>
-        </is>
-      </c>
-      <c r="B1361" s="3" t="inlineStr">
-        <is>
-          <t>UaOnlii</t>
-        </is>
-      </c>
-      <c r="C1361" s="3" t="inlineStr">
-        <is>
-          <t>2021-04-27</t>
-        </is>
-      </c>
-      <c r="D1361" s="3" t="n">
-        <v>10975</v>
-      </c>
-      <c r="E1361" s="3" t="inlineStr"/>
-      <c r="F1361" s="3" t="inlineStr">
-        <is>
-          <t>**Зеленский посетит Польшу сразу после Пасхи **
-3 мая президент Украины Владимир Зеленский посетит Польшу с рабочим визитом. Об этом сообщили в пресс-службе президента Польши. Его визит также приурочен к празднованию 230-летия принятия Конституции Польши.
-Визит Дуды в Украину запланирован на 24 августа, сообщает пресс-служба президента Польши.</t>
-        </is>
-      </c>
-      <c r="G1361" s="3" t="inlineStr"/>
-      <c r="H1361" s="3" t="inlineStr"/>
-      <c r="I1361" s="3" t="inlineStr"/>
-      <c r="J1361" s="3" t="inlineStr"/>
-      <c r="K1361" s="3" t="inlineStr"/>
-      <c r="L1361" s="3" t="inlineStr"/>
-      <c r="M1361" s="3" t="inlineStr"/>
-      <c r="N1361" s="3" t="inlineStr"/>
-      <c r="O1361" s="3" t="inlineStr"/>
-    </row>
-    <row r="1362">
-      <c r="A1362" s="3" t="inlineStr">
-        <is>
-          <t>V1361</t>
-        </is>
-      </c>
-      <c r="B1362" s="3" t="inlineStr">
-        <is>
-          <t>kievinfo_kyiv</t>
-        </is>
-      </c>
-      <c r="C1362" s="3" t="inlineStr">
-        <is>
-          <t>2023-10-22</t>
-        </is>
-      </c>
-      <c r="D1362" s="3" t="n">
-        <v>37798</v>
-      </c>
-      <c r="E1362" s="3" t="inlineStr"/>
-      <c r="F1362" s="3" t="inlineStr">
-        <is>
-          <t>**❗️У Києві затримали злочинців, які за 1 BTC побили і покалічили свого товариша.
-**Бізнесмена катували в його ж квартирі і він, побоюючись за своє життя, перерахував злочинцям крипту на $28 000. Правоохоронцям вдалося встановити нападників, їм загрожує до 15 років ув'язнення з конфіскацією майна. [[Читати деталі…]](https://telegra.ph/Detalі-10-22-3) 
-👉 https://t.me/+aAaZ8kQkkpo2ZjRi (натискай) [https://t.me/+aAaZ8kQkkpo2ZjRi]</t>
-        </is>
-      </c>
-      <c r="G1362" s="3" t="inlineStr"/>
-      <c r="H1362" s="3" t="inlineStr"/>
-      <c r="I1362" s="3" t="inlineStr"/>
-      <c r="J1362" s="3" t="inlineStr"/>
-      <c r="K1362" s="3" t="inlineStr"/>
-      <c r="L1362" s="3" t="inlineStr"/>
-      <c r="M1362" s="3" t="inlineStr"/>
-      <c r="N1362" s="3" t="inlineStr"/>
-      <c r="O1362" s="3" t="inlineStr"/>
-    </row>
-    <row r="1363">
-      <c r="A1363" s="3" t="inlineStr">
-        <is>
-          <t>V1362</t>
-        </is>
-      </c>
-      <c r="B1363" s="3" t="inlineStr">
-        <is>
-          <t>times_ukraina</t>
-        </is>
-      </c>
-      <c r="C1363" s="3" t="inlineStr">
-        <is>
-          <t>2020-07-30</t>
-        </is>
-      </c>
-      <c r="D1363" s="3" t="n">
-        <v>1437</v>
-      </c>
-      <c r="E1363" s="3" t="inlineStr">
-        <is>
-          <t>так</t>
-        </is>
-      </c>
-      <c r="F1363" s="3" t="inlineStr">
-        <is>
-          <t>Telegram подал антимонопольную жалобу на Apple
-**Основанный Павлом Дуровым мессенджер Telegram подал регулятору ЕС жалобу на App Store, который взимает 30% комиссию c приложений.
-Также в компании Павла Дурова заявили, что в 2016 году Apple запретила Telegram развивать игровую платформу, аргументировав это нарушением правил App Store. 
-В Telegram утверждают, что это пример способности Apple сдерживать инновации благодаря своей «монопольной власти» на рынке приложений.
-Сборы App Store приносят Apple более $1 млрд в месяц.
-Кроме Telegram антимонопольную жалобу против App Store подавали также шведский музыкальный стриминговый сервис Spotify и японская Rakuten.</t>
-        </is>
-      </c>
-      <c r="G1363" s="3" t="inlineStr"/>
-      <c r="H1363" s="3" t="inlineStr"/>
-      <c r="I1363" s="3" t="inlineStr"/>
-      <c r="J1363" s="3" t="inlineStr"/>
-      <c r="K1363" s="3" t="inlineStr"/>
-      <c r="L1363" s="3" t="inlineStr"/>
-      <c r="M1363" s="3" t="inlineStr"/>
-      <c r="N1363" s="3" t="inlineStr"/>
-      <c r="O1363" s="3" t="inlineStr"/>
-    </row>
-    <row r="1364">
-      <c r="A1364" s="3" t="inlineStr">
-        <is>
-          <t>V1363</t>
-        </is>
-      </c>
-      <c r="B1364" s="3" t="inlineStr">
-        <is>
-          <t>batalionmonako</t>
-        </is>
-      </c>
-      <c r="C1364" s="3" t="inlineStr">
-        <is>
-          <t>2025-03-19</t>
-        </is>
-      </c>
-      <c r="D1364" s="3" t="n">
-        <v>37111</v>
-      </c>
-      <c r="E1364" s="3" t="inlineStr"/>
-      <c r="F1364" s="3" t="inlineStr">
-        <is>
-          <t>⚡️**Припинення ударів має стосуватися всієї інфраструктури, а не тільки енергетики, **– спецпредставник Трампа Віткофф.</t>
-        </is>
-      </c>
-      <c r="G1364" s="3" t="inlineStr"/>
-      <c r="H1364" s="3" t="inlineStr"/>
-      <c r="I1364" s="3" t="inlineStr"/>
-      <c r="J1364" s="3" t="inlineStr"/>
-      <c r="K1364" s="3" t="inlineStr"/>
-      <c r="L1364" s="3" t="inlineStr"/>
-      <c r="M1364" s="3" t="inlineStr"/>
-      <c r="N1364" s="3" t="inlineStr"/>
-      <c r="O1364" s="3" t="inlineStr"/>
-    </row>
-    <row r="1365">
-      <c r="A1365" s="3" t="inlineStr">
-        <is>
-          <t>V1364</t>
-        </is>
-      </c>
-      <c r="B1365" s="3" t="inlineStr">
-        <is>
-          <t>lachentyt</t>
-        </is>
-      </c>
-      <c r="C1365" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-17</t>
-        </is>
-      </c>
-      <c r="D1365" s="3" t="n">
-        <v>50445</v>
-      </c>
-      <c r="E1365" s="3" t="inlineStr"/>
-      <c r="F1365" s="3" t="inlineStr">
-        <is>
-          <t>📉 Рейтинг Трампа падає: він б'є власний рекорд зі швидкого роздратування американських виборців, пише [https://www.economist.com/united-states/2025/04/16/donald-trumps-approval-rating-is-dropping] The Economist.
-Його рейтинг схвалення впав на 14 пунктів з моменту вступу на посаду, що перевищує падіння на п'ять пунктів за аналогічний період першого терміну. Майже кожен п'ятий з його виборців 2024 року не схвалює підхід до інфляції та цін.
-Серед іспаномовних виборців чисте схвалення Трампа складає мінус 37 пунктів, а серед молоді до 30 років — мінус 25. Ті самі, які забезпечили йому перемогу, тепер  обертаються проти нього.</t>
-        </is>
-      </c>
       <c r="G1365" s="3" t="inlineStr"/>
       <c r="H1365" s="3" t="inlineStr"/>
       <c r="I1365" s="3" t="inlineStr"/>
@@ -52736,11 +52766,11 @@
       </c>
       <c r="C1378" s="3" t="inlineStr">
         <is>
-          <t>2022-07-22</t>
+          <t>2023-03-09</t>
         </is>
       </c>
       <c r="D1378" s="3" t="n">
-        <v>16316</v>
+        <v>27562</v>
       </c>
       <c r="E1378" s="3" t="inlineStr">
         <is>
@@ -52749,8 +52779,8 @@
       </c>
       <c r="F1378" s="3" t="inlineStr">
         <is>
-          <t>**США вважають, що Україна знищила понад 100 «цінних» російських цілей, таких як командні пункти та склади боєприпасів**, - високопоставлений представник Міноборони США
-“Щодня росія несе сотні жертв. Серед загиблих — тисячі лейтенантів та капітанів та сотні полковників”</t>
+          <t>**В Голосіївському районі є влучання в об’єкт інфраструктури**, — КМВА.
+Всі служби працюють на місці.</t>
         </is>
       </c>
       <c r="G1378" s="3" t="inlineStr"/>
@@ -53480,16 +53510,17 @@
       </c>
       <c r="C1398" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="D1398" s="3" t="n">
-        <v>59518</v>
+        <v>34760</v>
       </c>
       <c r="E1398" s="3" t="inlineStr"/>
       <c r="F1398" s="3" t="inlineStr">
         <is>
-          <t>⚡️**7-річний хлопчик помер під час лікування зубів**: стоматологиня ввела йому препарат із прямими **протипоказаннями**, — поліція Києва. [https://t.me/kyiv_times_official]</t>
+          <t>⚡️**США схвалили передачу Україні ще однієї системи Patriot**, — AP.
+За словами чиновників, президент Джо Байден вирішив це зробити через наступ росіян на півночі Харківщини. Нібито систему розгорнуть в Україні вже за кілька днів.</t>
         </is>
       </c>
       <c r="G1398" s="3" t="inlineStr"/>
@@ -53740,19 +53771,23 @@
       </c>
       <c r="C1405" s="3" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="D1405" s="3" t="n">
-        <v>18844</v>
+        <v>62697</v>
       </c>
       <c r="E1405" s="3" t="inlineStr"/>
       <c r="F1405" s="3" t="inlineStr">
         <is>
-          <t>«У Кличка стоїть, а у путіна — впав». П’ятничний жарт від Віталія Кличка на питання чим він запам’ятається як мер Києва. 
-Очільник столиці розповів журналістці Соні Кошкіній, що **не будує зупинки-укриття як у Харкові**, бо ще досі немає затверджених буднорм від держави. 
-**Відмовився відповідати, чи піде на президентські вибори**, мовляв Володимир Зеленський починає нервувати, а у мера проходять обшуки. 
-Каже, що **пише президенту повідомлення і телефонує** з важливих питань життєдіяльності Києва, а відповіді не отримує.</t>
+          <t>⚡️Діючим військовим у частинах **дали** **можливість самим (!) мобілізувати людей. Тобто, навіть не ТЦК**. Таке було на Тернопільщині, [https://t.me/ternopil_times] — омбудсман Дмитро Лубінець.
+Ключові його тези: 
+⭕️«Працівники ТЦК **не мають права затримувати, арештовувати й утримувати громадян**. Це — порушення Конституції». 
+⭕️«Працівники ТЦК не пустили адвоката до військкомату **і зламали йому ногу**: це сталося на Харківщині». [https://t.me/kharkov_times]
+⭕️«Найкращим регіоном за якістю мобілізації **стала ****Хмельниччина** [https://t.me/khmelnytskyi_times]». [https://t.me/khmelnytskyi_times] 
+⭕️«Кількість скарг на працівників ТЦК **зросла в 333 рази з початку повномасштабної**». 
+⭕️«Жоден військовий командир **не підтримав жорстку мобілізацію**».
+⭕️«Є випадки, коли після ВЛК чоловіки не могли одягти бронежилети, **бо мають величезні проблеми з хребтом**».</t>
         </is>
       </c>
       <c r="G1405" s="3" t="inlineStr"/>
@@ -54146,16 +54181,16 @@
       </c>
       <c r="B1416" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1416" s="3" t="inlineStr">
         <is>
-          <t>2020-08-30</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="D1416" s="3" t="n">
-        <v>1672</v>
+        <v>55661</v>
       </c>
       <c r="E1416" s="3" t="inlineStr">
         <is>
@@ -54164,8 +54199,7 @@
       </c>
       <c r="F1416" s="3" t="inlineStr">
         <is>
-          <t>ЦИК определил дату начала предвыборной кампании в Украине
-**Центральная избирательная комиссия объявила с 5 сентября начало избирательного процесса местных выборов, которые состоятся 25 октября</t>
+          <t>Київ висуне Трампа на здобуття Нобелівської премії миру, якщо він надішле в Україну ракети "Томагавк" і допоможе досягти припинення вогню з РФ, — Politico цитує Зеленського.</t>
         </is>
       </c>
       <c r="G1416" s="3" t="inlineStr"/>
@@ -54223,16 +54257,16 @@
       </c>
       <c r="B1418" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1418" s="3" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="D1418" s="3" t="n">
-        <v>97131</v>
+        <v>29109</v>
       </c>
       <c r="E1418" s="3" t="inlineStr">
         <is>
@@ -54241,13 +54275,9 @@
       </c>
       <c r="F1418" s="3" t="inlineStr">
         <is>
-          <t>**На припинення вогню може знадобитися не 30 днів, а трохи більше, — Зеленський**
-📍Найголовніше для США — не йти на російське «але» в темі припинення вогню.
-📍рф хоче оточити українські війська, але на території України. Ми знаємо про ці плани.
-📍Усі вважають, що Україна перемогла (на переговорах із США у Саудівській Аравії). Усі зацікавлені не у зменшенні, а у посиленні ЗСУ.
-📍Нехай Америка тепер змусить Росію зробити перший крок, — Зеленський про 30-денне перемир'я.
-📍Україна не визнає окуповані українські території російськими.
-📍Якщо рф порушить режим тиші, то ми продовжимо захищатися, як робимо це й зараз.</t>
+          <t>**Працівник ТЦК, який заявляв, що ухилянтів треба «бити по хребту» — Віталій Михайлович Коростинський.**
+У 2023 році його дружина придбала квартиру у **Львові** [https://t.me/+eL-X-Ot60xBlNzFi]. [https://t.me/+eL-X-Ot60xBlNzFi] І це при тому, що у власності самого Віталія вже є квартира площею майже 92 м².
+Окрім того, чоловік його рідної сестри, Віктор Геннадійович Мица, 1986 р.н., з 24 лютого 2022 року не проходив службу в ЗСУ 💁‍♂️</t>
         </is>
       </c>
       <c r="G1418" s="3" t="inlineStr"/>
@@ -54862,22 +54892,27 @@
       </c>
       <c r="B1435" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>vanek_nikolaev</t>
         </is>
       </c>
       <c r="C1435" s="3" t="inlineStr">
         <is>
-          <t>2022-04-09</t>
+          <t>2023-08-24</t>
         </is>
       </c>
       <c r="D1435" s="3" t="n">
-        <v>7315</v>
+        <v>17241</v>
       </c>
       <c r="E1435" s="3" t="inlineStr"/>
       <c r="F1435" s="3" t="inlineStr">
         <is>
-          <t>**Алексей Арестович рассказал, может ли попробовать РФ снова штурмовать Киев. Он оценивает такую вероятность в 1%**.
-Тем не менее, по словам советника ОП, от путинского воинства можно ожидать любого идиотизма.</t>
+          <t>https://t.me/mykolaivskaODA/6031
+а автор сей замечательной работы 👉 Бодислав [https://t.me/khersondesigner]
+Бодислав [https://t.me/khersondesigner] - захерачу шедевр, матюкаясь, за пару часов
+__*это реклама работы просто талантливого человека, можете листать дальше__
+__**автор канала не получил за данную рекламу даже пивас, из-за чего весьма огорчен__
+__***вообще рекламой на канале не занимаюсь даже за 85 млн. $, можете даже не писать (даже пиво не рекламирую)
+****после войны рассмотрю любые предложения на рекламу пива с предварительной обязательной дегустацией__</t>
         </is>
       </c>
       <c r="G1435" s="3" t="inlineStr"/>
@@ -54903,17 +54938,16 @@
       </c>
       <c r="C1436" s="3" t="inlineStr">
         <is>
-          <t>2024-04-21</t>
+          <t>2025-10-04</t>
         </is>
       </c>
       <c r="D1436" s="3" t="n">
-        <v>32312</v>
+        <v>56414</v>
       </c>
       <c r="E1436" s="3" t="inlineStr"/>
       <c r="F1436" s="3" t="inlineStr">
         <is>
-          <t>Україною вирує негода: у Львові [https://t.me/+OvDtK0UtMjlkMWNi] випав величезний град, — місцеві тг-канали.
-У Києві [https://t.me/+0Evrr_TToPZmYzli] сильний вітер повалив дерева: гілки попадали на автівки та дороги. У Одесі [https://t.me/+IVEQ--aykm0yNjdi] також понівечені машини.</t>
+          <t>⚡ Одеса [https://t.me/+4zHYPnfcxOYxOGIy] знову йде під воду: **місто накрив затяжний дощ** — оголошено І рівень небезпеки. До зони ризику затоплення віднесено **всю міську берегову лінію**, — міськрада.</t>
         </is>
       </c>
       <c r="G1436" s="3" t="inlineStr"/>
@@ -54971,22 +55005,25 @@
       </c>
       <c r="B1438" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1438" s="3" t="inlineStr">
         <is>
-          <t>2022-03-18</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="D1438" s="3" t="n">
-        <v>6137</v>
+        <v>52189</v>
       </c>
       <c r="E1438" s="3" t="inlineStr"/>
       <c r="F1438" s="3" t="inlineStr">
         <is>
-          <t>**Польша удвоит численность армии: президент Дуда подписал закон о защите отечества
-**На армию будут тратить не меньше 3% ВВП. Также планируется создать силы теробороны численностью 50 тысяч человек [https://focus.ua/voennye-novosti/509795-polsha-udvoit-chislennost-armii-duda-podpisal-zakon-o-zashchite-otechestva].</t>
+          <t>‼️**«Орєшнік» з Білорусі до Києва тепер може долетіти за 1 хв 51 сек**, — Telegraf [https://news.telegraf.com.ua/ukraina/2025-08-13/5917797-vremeni-chtoby-spryatatsya-ne-budet-za-skolko-minut-oreshnik-mozhet-doletet-iz-belarusi-karta]
+▫️Найшвидше ракета досягне Вільнюса — **приблизно за 1 хвилину 4 секунди**.
+▫️До Рівного вона може долетіти орієнтовно **за 1 хв 40 сек**.
+▫️До Луцька — **за 1 хв 44 сек**.
+▫️До Львова — **2 хв 24 сек**.</t>
         </is>
       </c>
       <c r="G1438" s="3" t="inlineStr"/>
@@ -55007,23 +55044,22 @@
       </c>
       <c r="B1439" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1439" s="3" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2022-03-09</t>
         </is>
       </c>
       <c r="D1439" s="3" t="n">
-        <v>44592</v>
+        <v>5156</v>
       </c>
       <c r="E1439" s="3" t="inlineStr"/>
       <c r="F1439" s="3" t="inlineStr">
         <is>
-          <t>❗️Тепер у Facebook та Instagram дозволено вільно **називати представників ЛГБТК психічнохворими**: компанія Meta дала нові вказівки, — NBC News.
-Також допускається називати жінок** предметами чи власністю, **а трансгендерних людей —** «воно»**.
-__Що думаєте?</t>
+          <t>**Секретарь СНБО Алексей Данилов рассказал, что оккупанты в панике: 
+**"У них сменилось руководство, было снято порядка восьми генералов со своих должностей, потому что те не выполнили своих задач. Зато назначены новые. Мы четко понимаем, что сейчас происходит в РФ. Более того, могу сказать, что они в отчаянии".</t>
         </is>
       </c>
       <c r="G1439" s="3" t="inlineStr"/>
@@ -55049,11 +55085,11 @@
       </c>
       <c r="C1440" s="3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="D1440" s="3" t="n">
-        <v>61278</v>
+        <v>37984</v>
       </c>
       <c r="E1440" s="3" t="inlineStr">
         <is>
@@ -55062,7 +55098,13 @@
       </c>
       <c r="F1440" s="3" t="inlineStr">
         <is>
-          <t>Відключення повернулись: завтра з 07:00 до 11:00 у всіх областях діятимуть графіки відключень світла для всіх категорій споживачів, повідомили в «Укренерго».</t>
+          <t>Гринкевичі у 2023 році здійснили кілька великих покупок. Це були квартири, будинки та земельні ділянки для всіх членів родини. — джерело [https://dailylviv.com/news/kryminal/lvivskyi-biznesmen-ihor-hrynkevych-yakyi-obkradav-armiyu-ne-zaplaltyv-430-mln-hrn-zastavy-aby-vyity-z-sizo-119754] 
+Син львівського бізнесмена, 28-річний Роман Гринкевич займає посаду директора ТОВ "Будівельний Альянс МОНТАЖПРОЕКТ" і Благодійного фонду "ХОУП.ЮА" та є власником ТОВ "Електроагротехніки". 
+У травні 2023 року всього за один день він купив у селищі міського типу Козин 4 земельні ділянки та великий будинок площею 289 кв. м. 
+Теща, Ірина Федак. У 2023 році у неї з’явилася три земельні ділянки у Львівській обл та квартира у місті Лева площею 127 кв м
+Майбутня дружина Романа Гринкевича Соня Морозюк у 2023 купила PORSCHE CAYENNE 2015 р. та комерційне приміщення у столиці площею 122 кв. м. 
+Вартість останнього оцінюють у 4,6 млн грн.
+Загалом за рік, їхнім компаніям вдалося вивести понад **1 млрд грн. **Поки що триває розслідування.</t>
         </is>
       </c>
       <c r="G1440" s="3" t="inlineStr"/>
@@ -55162,21 +55204,21 @@
       </c>
       <c r="B1443" s="3" t="inlineStr">
         <is>
-          <t>batalionmonako</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1443" s="3" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="D1443" s="3" t="n">
-        <v>16319</v>
+        <v>18142</v>
       </c>
       <c r="E1443" s="3" t="inlineStr"/>
       <c r="F1443" s="3" t="inlineStr">
         <is>
-          <t>**❗️До банди рекетирів, яка ****викрадала** [https://www.pravda.com.ua/news/2023/12/12/7432720/]** людей, катувала та «вибивала» гроші, причетний депутат** **від** **партії Ляшка.</t>
+          <t>**ЗСУ розпочали наступальні дії на багатьох напрямках на півдні України**, — у коментарі "Громадському [https://hromadske.ua/posts/zsu-prorvali-pershu-liniyu-oboroni-na-hersonshini-ugrupovannya-kahovka]" керівниця об'єднаного пресцентру Сил охорони та оборони «Південь» Наталія Гуменюк.</t>
         </is>
       </c>
       <c r="G1443" s="3" t="inlineStr"/>
@@ -55197,25 +55239,23 @@
       </c>
       <c r="B1444" s="3" t="inlineStr">
         <is>
-          <t>vanek_nikolaev</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1444" s="3" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="D1444" s="3" t="n">
-        <v>17440</v>
+        <v>45962</v>
       </c>
       <c r="E1444" s="3" t="inlineStr"/>
       <c r="F1444" s="3" t="inlineStr">
         <is>
-          <t>**Штурм в лісосмузі очима бійця. **
-Десантуємось вздовж ворожих позицій в районі Бахмута. В ході бою один із бійців дістає ушкоджень, але штурм продовжується. 
-Оперативна евакуація, перегрупування, і просуваємось далі. 
-Виконують завдання бійці 1-ї роти 1-го штурмового батальйону [https://t.me/ShturmBat1] Третьої штурмової бригади.
-3ОШБр [https://t.me/+cWWdmTRjmykyZDNi] | Instagram [https://www.instagram.com/ab3.army] | Facebook [https://www.facebook.com/ab3.army] | YouTube [https://youtube.com/@ab3army] | ab3.army [https://ab3.army/] | SupportAZOV [https://t.me/AZOVsupport]🇺🇦</t>
+          <t>🇺🇸 Міністерство фінансів США оголосило [https://home.treasury.gov/news/press-releases/jy2700] нові санкції проти 275 фізичних та юридичних осіб, причетних до постачання технологій для російської воєнної промисловості.
+Під санкції потрапили компанії та особи з 17 країн, включаючи Індію, Китай, Швейцарію, Таїланд та Туреччину.
+Санкції спрямовані на мережі обходу, російських імпортерів й виробників ВПК, фінансових посередників та компанії-прокладки.</t>
         </is>
       </c>
       <c r="G1444" s="3" t="inlineStr"/>
@@ -55536,22 +55576,23 @@
       </c>
       <c r="B1453" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>times_ukraina</t>
         </is>
       </c>
       <c r="C1453" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2023-12-11</t>
         </is>
       </c>
       <c r="D1453" s="3" t="n">
-        <v>50257</v>
+        <v>24974</v>
       </c>
       <c r="E1453" s="3" t="inlineStr"/>
       <c r="F1453" s="3" t="inlineStr">
         <is>
-          <t>Британський Принц Гаррі сьогодні без анонса приїхав [https://www.telegraph.co.uk/royal-family/2025/04/10/prince-harry-ukraine-war-victims-surprise-visit/] в Україну, пише The Telegraph.
-Він відвідав поранених солдат, які проходять лікування в одному з Львівських шпиталів.</t>
+          <t>Диктатор рф не піде на мирні перемовини, — двічі президент України Леонід Кучма в інтервʼю The Guardian.
+«Путін не може підписати документ, в якому говориться, що він не отримав того, чого хотів. Йому доведеться це пояснювати російському народу».
+Водночас Леонід Данилович запевнив, що США не припинять підтримку нашої країни, інакше «втратять обличчя перед світом».</t>
         </is>
       </c>
       <c r="G1453" s="3" t="inlineStr"/>
@@ -55577,11 +55618,11 @@
       </c>
       <c r="C1454" s="3" t="inlineStr">
         <is>
-          <t>2022-03-06</t>
+          <t>2022-05-25</t>
         </is>
       </c>
       <c r="D1454" s="3" t="n">
-        <v>20992</v>
+        <v>29674</v>
       </c>
       <c r="E1454" s="3" t="inlineStr">
         <is>
@@ -55590,9 +55631,10 @@
       </c>
       <c r="F1454" s="3" t="inlineStr">
         <is>
-          <t>**6 марта, 14:00, россияне, выходите!
-Распространите
-🇺🇦**Украина Online [https://t.me/UkrainaOnlline] | Прислать новость [http://t.me/anonimnoua]</t>
+          <t>**❗️В Мариуполе погибли 22 тысячи человек, **сообщил советник мэра города Петр Андрющенко в комментарии CNN
+Цифра в 22 тысячи основана на информации чиновников, оставшихся в городе, но она может быть гораздо выше.
+Также Андющенко отметил, что есть сложности с захоронением погибших: чтобы забрать тело из морга, родственники должны сделать видеозапись с заявлением, что человека убили украинские военные.
+Советник мэра Мариуполя подчеркнул, что местные жители не могут свободно передвигаться, поскольку для любого передвижения по городу необходимы специальные пропуска, а система фильтрации не позволяет им бежать оттуда.</t>
         </is>
       </c>
       <c r="G1454" s="3" t="inlineStr"/>
@@ -56040,21 +56082,21 @@
       </c>
       <c r="B1466" s="3" t="inlineStr">
         <is>
-          <t>lachentyt</t>
+          <t>batalionmonako</t>
         </is>
       </c>
       <c r="C1466" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="D1466" s="3" t="n">
-        <v>60169</v>
+        <v>51056</v>
       </c>
       <c r="E1466" s="3" t="inlineStr"/>
       <c r="F1466" s="3" t="inlineStr">
         <is>
-          <t>Іран влучив безпілотником у злітно-посадкову смугу на базі ВПС Британії на Кіпрі, повідомили в МЗС.</t>
+          <t>**В руснявому Татарстані горить склад акумуляторів в особливій економічній зоні «Алабуга»: там виробляють «Шахеди», — ЗМІ</t>
         </is>
       </c>
       <c r="G1466" s="3" t="inlineStr"/>
@@ -56075,21 +56117,21 @@
       </c>
       <c r="B1467" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1467" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2022-01-20</t>
         </is>
       </c>
       <c r="D1467" s="3" t="n">
-        <v>63370</v>
+        <v>312</v>
       </c>
       <c r="E1467" s="3" t="inlineStr"/>
       <c r="F1467" s="3" t="inlineStr">
         <is>
-          <t>❗️**Кінцем війни навіть не пахне**: про це мені повідомили учасники переговорів. **Росіяни впевнені, що скоро дійдуть до ****Запоріжжя** [https://t.me/zaporizhzhia_times]** і захоплять усю Донеччину**, — «Миколаївський Ваньок».</t>
+          <t>В ВОЗ рекомендовали мировому сообществу отменить или ослабить ограничения на международные поездки, констатировав их неэффективность [https://www.pravda.com.ua/rus/news/2022/01/20/7321033/index.amp]</t>
         </is>
       </c>
       <c r="G1467" s="3" t="inlineStr"/>
@@ -56234,17 +56276,17 @@
       </c>
       <c r="C1471" s="3" t="inlineStr">
         <is>
-          <t>2022-12-04</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="D1471" s="3" t="n">
-        <v>42697</v>
+        <v>56405</v>
       </c>
       <c r="E1471" s="3" t="inlineStr"/>
       <c r="F1471" s="3" t="inlineStr">
         <is>
-          <t>**В Иране объявили об отмене "полиции нравов" — Alarabiya News
-**Именно деятельность "полиции нравов" привела к убийству Махсы Амини за "неправильное ношение хиджаба" и масштабным протестам [https://t.me/UAonlii/37693] в стране.</t>
+          <t>**На Кримському мосту оголосили повітряну тривогу, — росЗМі
+**"Внимание, воздушная тревога! Всем покинуть мост!", — звучить на кадрах, знятих очевидцями.</t>
         </is>
       </c>
       <c r="G1471" s="3" t="inlineStr"/>
@@ -56601,11 +56643,11 @@
       </c>
       <c r="C1481" s="3" t="inlineStr">
         <is>
-          <t>2023-04-18</t>
+          <t>2023-04-03</t>
         </is>
       </c>
       <c r="D1481" s="3" t="n">
-        <v>28508</v>
+        <v>28247</v>
       </c>
       <c r="E1481" s="3" t="inlineStr">
         <is>
@@ -56614,7 +56656,7 @@
       </c>
       <c r="F1481" s="3" t="inlineStr">
         <is>
-          <t>**Макрон за допомогою Китаю хоче посадити Україну і Росію за стіл переговорів влітку**, – Bloomberg.</t>
+          <t>**В Одесі було чутно вибух**, — місцеві ЗМІ.</t>
         </is>
       </c>
       <c r="G1481" s="3" t="inlineStr"/>
@@ -56975,19 +57017,19 @@
       </c>
       <c r="C1491" s="3" t="inlineStr">
         <is>
-          <t>2021-12-19</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="D1491" s="3" t="n">
-        <v>6168</v>
+        <v>5270</v>
       </c>
       <c r="E1491" s="3" t="inlineStr"/>
       <c r="F1491" s="3" t="inlineStr">
         <is>
-          <t>**ПЦУ заговорила о праздновании Рождества 25 декабря
-**Об этом рассказал глава ПЦУ, Митрополит Киевский и всея Украины Епифаний.
-Он поддержал празднование Рождества по юлианскому календарю и заявил, что в ближайшие 10 лет ПЦУ может перейти на празднование Рождества только 25 декабря.
-"Это больше всего связано с традициями внутри. Мы уже говорили и анализировали. Хотя в этом году я наблюдаю, что нет такой активной волны обсуждения празднования Рождества Христова. В прошедшие два года, было ли это искусственно создано, я помню, что в позапрошлом году запустили мои цитаты о том, что я не против, а я действительно не против перехода. Но чтобы это произошло правильно. Надо мудро действовать", - сказал глава ПЦУ.</t>
+          <t>**Правительство хочет перевести крымскотатарский язык на латиницу**
+Кабмин утвердил алфавит крымскотатарского языка на основе латиницы. Об этом сообщается на сайте правительства.
+Переведение крымскотатарской письменности на латиницу будет осуществляться до 1 сентября 2025 года. Это значит, что до 2025 образовательный процесс должен быть переведен на использование латиницы, но ее применение для крымскотатарского языка в других сферах жизни будет стимулироваться уже сейчас. 
+По словам главы Минреинтеграции Алексея Резникова, это создаст дополнительные возможности для Украины по взаимодействию с тюркскими странами, среди которых наши стратегические партнеры.</t>
         </is>
       </c>
       <c r="G1491" s="3" t="inlineStr"/>
@@ -57008,24 +57050,21 @@
       </c>
       <c r="B1492" s="3" t="inlineStr">
         <is>
-          <t>times_ukraina</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1492" s="3" t="inlineStr">
         <is>
-          <t>2023-12-14</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="D1492" s="3" t="n">
-        <v>25095</v>
+        <v>17358</v>
       </c>
       <c r="E1492" s="3" t="inlineStr"/>
       <c r="F1492" s="3" t="inlineStr">
         <is>
-          <t>Підірвалися на своїй же міні: **у 
-Бєлгородській області рф місцеві чиновники на «УАЗ-Патріот» наїхали на вибухівку, яку встановили російські військові**, — радник мера Маріуполя Петро Андрющенко.
-Результати — одному пасажиру відірвало ноги, в інших двох — мінно-вибухова травма, рани м'яких тканин голови та струс мозку. 
-__Від карми не втечеш.</t>
+          <t>**Тривають жорсткі бої у напрямках Пісків, Мар'їнки, Олександрополя, Красногорівки та Авдіївки,** — Генштаб.</t>
         </is>
       </c>
       <c r="G1492" s="3" t="inlineStr"/>
@@ -57046,21 +57085,22 @@
       </c>
       <c r="B1493" s="3" t="inlineStr">
         <is>
-          <t>UaOnlii</t>
+          <t>lachentyt</t>
         </is>
       </c>
       <c r="C1493" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="D1493" s="3" t="n">
-        <v>107099</v>
+        <v>19731</v>
       </c>
       <c r="E1493" s="3" t="inlineStr"/>
       <c r="F1493" s="3" t="inlineStr">
         <is>
-          <t>❗️**Попередньо, перші ракети вже над Україною: курс через Харківщину, — монітори**</t>
+          <t>**Японія запровадила заборону на експорт до рФ товарів, які можуть бути пов'язані з хімзброєю **, — Мінекономіки Японії.
+Також було внесено до списків санкцій ще 21 організацію з роzії.</t>
         </is>
       </c>
       <c r="G1493" s="3" t="inlineStr"/>
